--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834D86D5-3843-42F1-807D-99554EB81DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F658EDF-46DA-4D37-A63B-56604A0F6685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5738" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5739" uniqueCount="1536">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4648,6 +4648,14 @@
   </si>
   <si>
     <t>0 &amp; 1</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5210,10 +5218,10 @@
         <v>234</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>109</v>
+        <v>1533</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>109</v>
+        <v>1534</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>235</v>
@@ -5246,6 +5254,9 @@
       </c>
       <c r="F7" s="1" t="s">
         <v>1533</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>1535</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>237</v>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F658EDF-46DA-4D37-A63B-56604A0F6685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34815169-6DBF-44AF-88CB-63887FF57B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="32220" yWindow="3420" windowWidth="21600" windowHeight="11385" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A2B870-BD06-44C4-9416-B698FAD7C460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2AA469-845D-43AD-AA5B-7CD986B618E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
     <sheet name="sell" sheetId="3" r:id="rId2"/>
     <sheet name="buy" sheetId="4" r:id="rId3"/>
     <sheet name="npc_spawn" sheetId="5" r:id="rId4"/>
+    <sheet name="soliloquy" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5736" uniqueCount="1536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5744" uniqueCount="1540">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4655,6 +4656,22 @@
   </si>
   <si>
     <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*$npc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼잣말1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼잣말2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4726,7 +4743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4743,6 +4760,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -25848,4 +25868,57 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B925D1-5541-4FEF-A6C8-C42626081064}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2AA469-845D-43AD-AA5B-7CD986B618E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4601C6E-3773-4CE1-B782-7318ECDC95A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5744" uniqueCount="1540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5985" uniqueCount="1779">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4673,6 +4673,723 @@
   <si>
     <t>혼잣말2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>NPC_0</t>
+  </si>
+  <si>
+    <t>NPC_1</t>
+  </si>
+  <si>
+    <t>NPC_2</t>
+  </si>
+  <si>
+    <t>NPC_3</t>
+  </si>
+  <si>
+    <t>NPC_4</t>
+  </si>
+  <si>
+    <t>NPC_5</t>
+  </si>
+  <si>
+    <t>NPC_6</t>
+  </si>
+  <si>
+    <t>NPC_7</t>
+  </si>
+  <si>
+    <t>NPC_8</t>
+  </si>
+  <si>
+    <t>NPC_9</t>
+  </si>
+  <si>
+    <t>NPC_10</t>
+  </si>
+  <si>
+    <t>NPC_11</t>
+  </si>
+  <si>
+    <t>NPC_12</t>
+  </si>
+  <si>
+    <t>NPC_13</t>
+  </si>
+  <si>
+    <t>NPC_14</t>
+  </si>
+  <si>
+    <t>NPC_15</t>
+  </si>
+  <si>
+    <t>NPC_16</t>
+  </si>
+  <si>
+    <t>NPC_17</t>
+  </si>
+  <si>
+    <t>NPC_18</t>
+  </si>
+  <si>
+    <t>NPC_19</t>
+  </si>
+  <si>
+    <t>NPC_20</t>
+  </si>
+  <si>
+    <t>NPC_21</t>
+  </si>
+  <si>
+    <t>NPC_22</t>
+  </si>
+  <si>
+    <t>NPC_23</t>
+  </si>
+  <si>
+    <t>NPC_24</t>
+  </si>
+  <si>
+    <t>NPC_25</t>
+  </si>
+  <si>
+    <t>NPC_26</t>
+  </si>
+  <si>
+    <t>NPC_27</t>
+  </si>
+  <si>
+    <t>NPC_28</t>
+  </si>
+  <si>
+    <t>NPC_29</t>
+  </si>
+  <si>
+    <t>NPC_30</t>
+  </si>
+  <si>
+    <t>NPC_31</t>
+  </si>
+  <si>
+    <t>NPC_32</t>
+  </si>
+  <si>
+    <t>NPC_33</t>
+  </si>
+  <si>
+    <t>NPC_34</t>
+  </si>
+  <si>
+    <t>NPC_35</t>
+  </si>
+  <si>
+    <t>NPC_36</t>
+  </si>
+  <si>
+    <t>NPC_37</t>
+  </si>
+  <si>
+    <t>NPC_38</t>
+  </si>
+  <si>
+    <t>NPC_39</t>
+  </si>
+  <si>
+    <t>NPC_40</t>
+  </si>
+  <si>
+    <t>NPC_41</t>
+  </si>
+  <si>
+    <t>NPC_42</t>
+  </si>
+  <si>
+    <t>NPC_43</t>
+  </si>
+  <si>
+    <t>NPC_44</t>
+  </si>
+  <si>
+    <t>NPC_45</t>
+  </si>
+  <si>
+    <t>NPC_46</t>
+  </si>
+  <si>
+    <t>NPC_47</t>
+  </si>
+  <si>
+    <t>NPC_48</t>
+  </si>
+  <si>
+    <t>NPC_49</t>
+  </si>
+  <si>
+    <t>NPC_50</t>
+  </si>
+  <si>
+    <t>NPC_51</t>
+  </si>
+  <si>
+    <t>NPC_53</t>
+  </si>
+  <si>
+    <t>NPC_58</t>
+  </si>
+  <si>
+    <t>NPC_189</t>
+  </si>
+  <si>
+    <t>NPC_57</t>
+  </si>
+  <si>
+    <t>NPC_237</t>
+  </si>
+  <si>
+    <t>NPC_60</t>
+  </si>
+  <si>
+    <t>NPC_61</t>
+  </si>
+  <si>
+    <t>NPC_62</t>
+  </si>
+  <si>
+    <t>NPC_63</t>
+  </si>
+  <si>
+    <t>NPC_64</t>
+  </si>
+  <si>
+    <t>NPC_65</t>
+  </si>
+  <si>
+    <t>NPC_66</t>
+  </si>
+  <si>
+    <t>NPC_67</t>
+  </si>
+  <si>
+    <t>NPC_68</t>
+  </si>
+  <si>
+    <t>NPC_69</t>
+  </si>
+  <si>
+    <t>NPC_70</t>
+  </si>
+  <si>
+    <t>NPC_71</t>
+  </si>
+  <si>
+    <t>NPC_72</t>
+  </si>
+  <si>
+    <t>NPC_73</t>
+  </si>
+  <si>
+    <t>NPC_74</t>
+  </si>
+  <si>
+    <t>NPC_75</t>
+  </si>
+  <si>
+    <t>NPC_76</t>
+  </si>
+  <si>
+    <t>NPC_77</t>
+  </si>
+  <si>
+    <t>NPC_78</t>
+  </si>
+  <si>
+    <t>NPC_79</t>
+  </si>
+  <si>
+    <t>NPC_80</t>
+  </si>
+  <si>
+    <t>NPC_166</t>
+  </si>
+  <si>
+    <t>NPC_84</t>
+  </si>
+  <si>
+    <t>NPC_85</t>
+  </si>
+  <si>
+    <t>NPC_86</t>
+  </si>
+  <si>
+    <t>NPC_87</t>
+  </si>
+  <si>
+    <t>NPC_88</t>
+  </si>
+  <si>
+    <t>NPC_89</t>
+  </si>
+  <si>
+    <t>NPC_90</t>
+  </si>
+  <si>
+    <t>NPC_91</t>
+  </si>
+  <si>
+    <t>NPC_92</t>
+  </si>
+  <si>
+    <t>NPC_93</t>
+  </si>
+  <si>
+    <t>NPC_94</t>
+  </si>
+  <si>
+    <t>NPC_95</t>
+  </si>
+  <si>
+    <t>NPC_96</t>
+  </si>
+  <si>
+    <t>NPC_149</t>
+  </si>
+  <si>
+    <t>NPC_98</t>
+  </si>
+  <si>
+    <t>NPC_99</t>
+  </si>
+  <si>
+    <t>NPC_100</t>
+  </si>
+  <si>
+    <t>NPC_101</t>
+  </si>
+  <si>
+    <t>NPC_102</t>
+  </si>
+  <si>
+    <t>NPC_103</t>
+  </si>
+  <si>
+    <t>NPC_104</t>
+  </si>
+  <si>
+    <t>NPC_105</t>
+  </si>
+  <si>
+    <t>NPC_106</t>
+  </si>
+  <si>
+    <t>NPC_107</t>
+  </si>
+  <si>
+    <t>NPC_108</t>
+  </si>
+  <si>
+    <t>NPC_109</t>
+  </si>
+  <si>
+    <t>NPC_110</t>
+  </si>
+  <si>
+    <t>NPC_191</t>
+  </si>
+  <si>
+    <t>NPC_112</t>
+  </si>
+  <si>
+    <t>NPC_113</t>
+  </si>
+  <si>
+    <t>NPC_177</t>
+  </si>
+  <si>
+    <t>NPC_115</t>
+  </si>
+  <si>
+    <t>NPC_167</t>
+  </si>
+  <si>
+    <t>NPC_117</t>
+  </si>
+  <si>
+    <t>NPC_118</t>
+  </si>
+  <si>
+    <t>NPC_119</t>
+  </si>
+  <si>
+    <t>NPC_120</t>
+  </si>
+  <si>
+    <t>NPC_121</t>
+  </si>
+  <si>
+    <t>NPC_122</t>
+  </si>
+  <si>
+    <t>NPC_123</t>
+  </si>
+  <si>
+    <t>NPC_124</t>
+  </si>
+  <si>
+    <t>NPC_125</t>
+  </si>
+  <si>
+    <t>NPC_126</t>
+  </si>
+  <si>
+    <t>NPC_127</t>
+  </si>
+  <si>
+    <t>NPC_128</t>
+  </si>
+  <si>
+    <t>NPC_129</t>
+  </si>
+  <si>
+    <t>NPC_130</t>
+  </si>
+  <si>
+    <t>NPC_131</t>
+  </si>
+  <si>
+    <t>NPC_132</t>
+  </si>
+  <si>
+    <t>NPC_133</t>
+  </si>
+  <si>
+    <t>NPC_134</t>
+  </si>
+  <si>
+    <t>NPC_135</t>
+  </si>
+  <si>
+    <t>NPC_136</t>
+  </si>
+  <si>
+    <t>NPC_137</t>
+  </si>
+  <si>
+    <t>NPC_138</t>
+  </si>
+  <si>
+    <t>NPC_139</t>
+  </si>
+  <si>
+    <t>NPC_140</t>
+  </si>
+  <si>
+    <t>NPC_141</t>
+  </si>
+  <si>
+    <t>NPC_143</t>
+  </si>
+  <si>
+    <t>NPC_144</t>
+  </si>
+  <si>
+    <t>NPC_145</t>
+  </si>
+  <si>
+    <t>NPC_146</t>
+  </si>
+  <si>
+    <t>NPC_147</t>
+  </si>
+  <si>
+    <t>NPC_148</t>
+  </si>
+  <si>
+    <t>NPC_150</t>
+  </si>
+  <si>
+    <t>NPC_151</t>
+  </si>
+  <si>
+    <t>NPC_152</t>
+  </si>
+  <si>
+    <t>NPC_153</t>
+  </si>
+  <si>
+    <t>NPC_154</t>
+  </si>
+  <si>
+    <t>NPC_155</t>
+  </si>
+  <si>
+    <t>NPC_156</t>
+  </si>
+  <si>
+    <t>NPC_157</t>
+  </si>
+  <si>
+    <t>NPC_158</t>
+  </si>
+  <si>
+    <t>NPC_159</t>
+  </si>
+  <si>
+    <t>NPC_160</t>
+  </si>
+  <si>
+    <t>NPC_161</t>
+  </si>
+  <si>
+    <t>NPC_185</t>
+  </si>
+  <si>
+    <t>NPC_163</t>
+  </si>
+  <si>
+    <t>NPC_164</t>
+  </si>
+  <si>
+    <t>NPC_165</t>
+  </si>
+  <si>
+    <t>NPC_168</t>
+  </si>
+  <si>
+    <t>NPC_169</t>
+  </si>
+  <si>
+    <t>NPC_170</t>
+  </si>
+  <si>
+    <t>NPC_171</t>
+  </si>
+  <si>
+    <t>NPC_172</t>
+  </si>
+  <si>
+    <t>NPC_173</t>
+  </si>
+  <si>
+    <t>NPC_174</t>
+  </si>
+  <si>
+    <t>NPC_175</t>
+  </si>
+  <si>
+    <t>NPC_176</t>
+  </si>
+  <si>
+    <t>NPC_178</t>
+  </si>
+  <si>
+    <t>NPC_179</t>
+  </si>
+  <si>
+    <t>NPC_180</t>
+  </si>
+  <si>
+    <t>NPC_181</t>
+  </si>
+  <si>
+    <t>NPC_182</t>
+  </si>
+  <si>
+    <t>NPC_183</t>
+  </si>
+  <si>
+    <t>NPC_184</t>
+  </si>
+  <si>
+    <t>NPC_186</t>
+  </si>
+  <si>
+    <t>NPC_187</t>
+  </si>
+  <si>
+    <t>NPC_188</t>
+  </si>
+  <si>
+    <t>NPC_190</t>
+  </si>
+  <si>
+    <t>NPC_192</t>
+  </si>
+  <si>
+    <t>NPC_193</t>
+  </si>
+  <si>
+    <t>NPC_194</t>
+  </si>
+  <si>
+    <t>NPC_195</t>
+  </si>
+  <si>
+    <t>NPC_196</t>
+  </si>
+  <si>
+    <t>NPC_197</t>
+  </si>
+  <si>
+    <t>NPC_198</t>
+  </si>
+  <si>
+    <t>NPC_199</t>
+  </si>
+  <si>
+    <t>NPC_200</t>
+  </si>
+  <si>
+    <t>NPC_201</t>
+  </si>
+  <si>
+    <t>NPC_202</t>
+  </si>
+  <si>
+    <t>NPC_203</t>
+  </si>
+  <si>
+    <t>NPC_204</t>
+  </si>
+  <si>
+    <t>NPC_205</t>
+  </si>
+  <si>
+    <t>NPC_206</t>
+  </si>
+  <si>
+    <t>NPC_207</t>
+  </si>
+  <si>
+    <t>NPC_208</t>
+  </si>
+  <si>
+    <t>NPC_209</t>
+  </si>
+  <si>
+    <t>NPC_210</t>
+  </si>
+  <si>
+    <t>NPC_211</t>
+  </si>
+  <si>
+    <t>NPC_212</t>
+  </si>
+  <si>
+    <t>NPC_213</t>
+  </si>
+  <si>
+    <t>NPC_214</t>
+  </si>
+  <si>
+    <t>NPC_215</t>
+  </si>
+  <si>
+    <t>NPC_216</t>
+  </si>
+  <si>
+    <t>NPC_217</t>
+  </si>
+  <si>
+    <t>NPC_218</t>
+  </si>
+  <si>
+    <t>NPC_219</t>
+  </si>
+  <si>
+    <t>NPC_220</t>
+  </si>
+  <si>
+    <t>NPC_221</t>
+  </si>
+  <si>
+    <t>NPC_222</t>
+  </si>
+  <si>
+    <t>NPC_223</t>
+  </si>
+  <si>
+    <t>NPC_224</t>
+  </si>
+  <si>
+    <t>NPC_225</t>
+  </si>
+  <si>
+    <t>NPC_226</t>
+  </si>
+  <si>
+    <t>NPC_227</t>
+  </si>
+  <si>
+    <t>NPC_228</t>
+  </si>
+  <si>
+    <t>NPC_229</t>
+  </si>
+  <si>
+    <t>NPC_230</t>
+  </si>
+  <si>
+    <t>NPC_231</t>
+  </si>
+  <si>
+    <t>NPC_232</t>
+  </si>
+  <si>
+    <t>NPC_233</t>
+  </si>
+  <si>
+    <t>NPC_234</t>
+  </si>
+  <si>
+    <t>NPC_235</t>
+  </si>
+  <si>
+    <t>NPC_236</t>
+  </si>
+  <si>
+    <t>NPC_238</t>
+  </si>
+  <si>
+    <t>NPC_239</t>
+  </si>
+  <si>
+    <t>NPC_240</t>
+  </si>
+  <si>
+    <t>NPC_241</t>
+  </si>
+  <si>
+    <t>NPC_242</t>
+  </si>
+  <si>
+    <t>NPC_243</t>
+  </si>
+  <si>
+    <t>NPC_244</t>
+  </si>
+  <si>
+    <t>NPC_245</t>
+  </si>
+  <si>
+    <t>NPC_246</t>
+  </si>
+  <si>
+    <t>NPC_247</t>
+  </si>
+  <si>
+    <t>NPC_248</t>
+  </si>
+  <si>
+    <t>NPC_249</t>
+  </si>
+  <si>
+    <t>NPC_250</t>
+  </si>
+  <si>
+    <t>NPC_251</t>
   </si>
 </sst>
 </file>
@@ -5079,7 +5796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7A1E07-EEF2-4E86-80A0-A85D709C37E7}">
-  <dimension ref="A1:L243"/>
+  <dimension ref="A1:M243"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -5087,27 +5804,28 @@
     <col min="3" max="3" width="7.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="22.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="22.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1515</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1516</v>
       </c>
@@ -5124,28 +5842,31 @@
         <v>1520</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>1522</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>1523</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>1524</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>1525</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>1526</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>1513</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1527</v>
       </c>
@@ -5162,13 +5883,13 @@
         <v>1528</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>1532</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1514</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>1514</v>
@@ -5182,8 +5903,11 @@
       <c r="L4" s="1" t="s">
         <v>1514</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="1" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1161</v>
       </c>
@@ -5220,8 +5944,11 @@
       <c r="L5" s="1" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -5238,13 +5965,13 @@
         <v>234</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>1534</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>235</v>
@@ -5256,10 +5983,13 @@
         <v>235</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>110</v>
       </c>
@@ -5273,14 +6003,14 @@
         <v>110</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>1533</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>1535</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="I7" s="1" t="s">
         <v>237</v>
       </c>
@@ -5293,8 +6023,11 @@
       <c r="L7" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>112</v>
       </c>
@@ -5310,8 +6043,8 @@
       <c r="E8" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>237</v>
+      <c r="F8" s="1" t="s">
+        <v>1543</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>237</v>
@@ -5325,8 +6058,11 @@
       <c r="L8" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>119</v>
       </c>
@@ -5342,8 +6078,8 @@
       <c r="E9" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>237</v>
+      <c r="F9" s="1" t="s">
+        <v>1544</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>237</v>
@@ -5357,8 +6093,11 @@
       <c r="L9" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>114</v>
       </c>
@@ -5374,8 +6113,8 @@
       <c r="E10" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>237</v>
+      <c r="F10" s="1" t="s">
+        <v>1545</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>237</v>
@@ -5389,8 +6128,11 @@
       <c r="L10" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>107</v>
       </c>
@@ -5406,8 +6148,8 @@
       <c r="E11" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>237</v>
+      <c r="F11" s="1" t="s">
+        <v>1546</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>237</v>
@@ -5421,8 +6163,11 @@
       <c r="L11" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>116</v>
       </c>
@@ -5438,8 +6183,8 @@
       <c r="E12" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>237</v>
+      <c r="F12" s="1" t="s">
+        <v>1547</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>237</v>
@@ -5453,8 +6198,11 @@
       <c r="L12" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>121</v>
       </c>
@@ -5467,8 +6215,8 @@
       <c r="D13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>237</v>
+      <c r="F13" s="1" t="s">
+        <v>1548</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>237</v>
@@ -5482,8 +6230,11 @@
       <c r="L13" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>122</v>
       </c>
@@ -5499,8 +6250,8 @@
       <c r="E14" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>237</v>
+      <c r="F14" s="1" t="s">
+        <v>1549</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>237</v>
@@ -5514,8 +6265,11 @@
       <c r="L14" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>115</v>
       </c>
@@ -5531,8 +6285,8 @@
       <c r="E15" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>237</v>
+      <c r="F15" s="1" t="s">
+        <v>1550</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>237</v>
@@ -5546,8 +6300,11 @@
       <c r="L15" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>113</v>
       </c>
@@ -5560,8 +6317,8 @@
       <c r="D16" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>237</v>
+      <c r="F16" s="1" t="s">
+        <v>1551</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>237</v>
@@ -5575,8 +6332,11 @@
       <c r="L16" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>111</v>
       </c>
@@ -5592,8 +6352,8 @@
       <c r="E17" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>237</v>
+      <c r="F17" s="1" t="s">
+        <v>1552</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>237</v>
@@ -5607,8 +6367,11 @@
       <c r="L17" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>123</v>
       </c>
@@ -5621,8 +6384,8 @@
       <c r="D18" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>237</v>
+      <c r="F18" s="1" t="s">
+        <v>1553</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>237</v>
@@ -5636,8 +6399,11 @@
       <c r="L18" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>124</v>
       </c>
@@ -5653,8 +6419,8 @@
       <c r="E19" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>237</v>
+      <c r="F19" s="1" t="s">
+        <v>1554</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>237</v>
@@ -5668,8 +6434,11 @@
       <c r="L19" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>118</v>
       </c>
@@ -5685,8 +6454,8 @@
       <c r="E20" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>237</v>
+      <c r="F20" s="1" t="s">
+        <v>1555</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>237</v>
@@ -5700,8 +6469,11 @@
       <c r="L20" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>120</v>
       </c>
@@ -5717,8 +6489,8 @@
       <c r="E21" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>237</v>
+      <c r="F21" s="1" t="s">
+        <v>1556</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>237</v>
@@ -5732,8 +6504,11 @@
       <c r="L21" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>125</v>
       </c>
@@ -5746,8 +6521,8 @@
       <c r="D22" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>237</v>
+      <c r="F22" s="1" t="s">
+        <v>1557</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>237</v>
@@ -5761,8 +6536,11 @@
       <c r="L22" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>117</v>
       </c>
@@ -5778,8 +6556,8 @@
       <c r="E23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>237</v>
+      <c r="F23" s="1" t="s">
+        <v>1558</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>237</v>
@@ -5793,8 +6571,11 @@
       <c r="L23" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -5810,8 +6591,8 @@
       <c r="E24" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>237</v>
+      <c r="F24" s="1" t="s">
+        <v>1559</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>237</v>
@@ -5823,10 +6604,13 @@
         <v>237</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -5842,8 +6626,8 @@
       <c r="E25" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>237</v>
+      <c r="F25" s="1" t="s">
+        <v>1560</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>237</v>
@@ -5855,10 +6639,13 @@
         <v>237</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -5874,8 +6661,8 @@
       <c r="E26" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>237</v>
+      <c r="F26" s="1" t="s">
+        <v>1561</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>237</v>
@@ -5889,8 +6676,11 @@
       <c r="L26" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -5903,8 +6693,8 @@
       <c r="D27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>237</v>
+      <c r="F27" s="1" t="s">
+        <v>1562</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>237</v>
@@ -5918,8 +6708,11 @@
       <c r="L27" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>7</v>
       </c>
@@ -5935,8 +6728,8 @@
       <c r="E28" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>237</v>
+      <c r="F28" s="1" t="s">
+        <v>1563</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>237</v>
@@ -5950,8 +6743,11 @@
       <c r="L28" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -5964,8 +6760,8 @@
       <c r="D29" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>237</v>
+      <c r="F29" s="1" t="s">
+        <v>1564</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>237</v>
@@ -5979,8 +6775,11 @@
       <c r="L29" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -5996,8 +6795,8 @@
       <c r="E30" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>237</v>
+      <c r="F30" s="1" t="s">
+        <v>1565</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>237</v>
@@ -6011,8 +6810,11 @@
       <c r="L30" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -6025,8 +6827,8 @@
       <c r="D31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>237</v>
+      <c r="F31" s="1" t="s">
+        <v>1566</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>237</v>
@@ -6040,8 +6842,11 @@
       <c r="L31" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -6057,8 +6862,8 @@
       <c r="E32" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>237</v>
+      <c r="F32" s="1" t="s">
+        <v>1567</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>237</v>
@@ -6072,8 +6877,11 @@
       <c r="L32" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>8</v>
       </c>
@@ -6086,8 +6894,8 @@
       <c r="D33" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>237</v>
+      <c r="F33" s="1" t="s">
+        <v>1568</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>237</v>
@@ -6101,8 +6909,11 @@
       <c r="L33" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
@@ -6118,8 +6929,8 @@
       <c r="E34" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>237</v>
+      <c r="F34" s="1" t="s">
+        <v>1569</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>237</v>
@@ -6133,8 +6944,11 @@
       <c r="L34" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>108</v>
       </c>
@@ -6147,8 +6961,8 @@
       <c r="D35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>237</v>
+      <c r="F35" s="1" t="s">
+        <v>1570</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>237</v>
@@ -6162,8 +6976,11 @@
       <c r="L35" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -6179,8 +6996,8 @@
       <c r="E36" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>237</v>
+      <c r="F36" s="1" t="s">
+        <v>1571</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>237</v>
@@ -6194,8 +7011,11 @@
       <c r="L36" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
@@ -6211,8 +7031,8 @@
       <c r="E37" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>237</v>
+      <c r="F37" s="1" t="s">
+        <v>1572</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>237</v>
@@ -6226,8 +7046,11 @@
       <c r="L37" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
@@ -6240,8 +7063,8 @@
       <c r="D38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>237</v>
+      <c r="F38" s="1" t="s">
+        <v>1573</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>237</v>
@@ -6255,8 +7078,11 @@
       <c r="L38" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>106</v>
       </c>
@@ -6269,8 +7095,8 @@
       <c r="D39" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>237</v>
+      <c r="F39" s="1" t="s">
+        <v>1574</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>237</v>
@@ -6284,8 +7110,11 @@
       <c r="L39" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M39" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
@@ -6301,8 +7130,8 @@
       <c r="E40" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>237</v>
+      <c r="F40" s="1" t="s">
+        <v>1575</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>237</v>
@@ -6316,8 +7145,11 @@
       <c r="L40" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M40" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
@@ -6333,8 +7165,8 @@
       <c r="E41" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>237</v>
+      <c r="F41" s="1" t="s">
+        <v>1576</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>237</v>
@@ -6348,8 +7180,11 @@
       <c r="L41" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>211</v>
       </c>
@@ -6365,8 +7200,8 @@
       <c r="E42" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>237</v>
+      <c r="F42" s="1" t="s">
+        <v>1577</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>237</v>
@@ -6380,8 +7215,11 @@
       <c r="L42" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>212</v>
       </c>
@@ -6397,8 +7235,8 @@
       <c r="E43" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>237</v>
+      <c r="F43" s="1" t="s">
+        <v>1578</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>237</v>
@@ -6412,8 +7250,11 @@
       <c r="L43" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>136</v>
       </c>
@@ -6429,8 +7270,8 @@
       <c r="E44" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>237</v>
+      <c r="F44" s="1" t="s">
+        <v>1579</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>237</v>
@@ -6444,8 +7285,11 @@
       <c r="L44" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>214</v>
       </c>
@@ -6461,8 +7305,8 @@
       <c r="E45" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>237</v>
+      <c r="F45" s="1" t="s">
+        <v>1580</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>237</v>
@@ -6476,8 +7320,11 @@
       <c r="L45" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>135</v>
       </c>
@@ -6493,8 +7340,8 @@
       <c r="E46" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>237</v>
+      <c r="F46" s="1" t="s">
+        <v>1581</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>237</v>
@@ -6508,8 +7355,11 @@
       <c r="L46" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M46" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>173</v>
       </c>
@@ -6525,8 +7375,8 @@
       <c r="E47" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>237</v>
+      <c r="F47" s="1" t="s">
+        <v>1582</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>237</v>
@@ -6540,8 +7390,11 @@
       <c r="L47" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M47" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>137</v>
       </c>
@@ -6557,8 +7410,8 @@
       <c r="E48" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>237</v>
+      <c r="F48" s="1" t="s">
+        <v>1583</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>237</v>
@@ -6572,8 +7425,11 @@
       <c r="L48" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M48" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>138</v>
       </c>
@@ -6586,8 +7442,8 @@
       <c r="D49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>237</v>
+      <c r="F49" s="1" t="s">
+        <v>1584</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>237</v>
@@ -6601,8 +7457,11 @@
       <c r="L49" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M49" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
@@ -6618,8 +7477,8 @@
       <c r="E50" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>237</v>
+      <c r="F50" s="1" t="s">
+        <v>1585</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>237</v>
@@ -6633,8 +7492,11 @@
       <c r="L50" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M50" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>139</v>
       </c>
@@ -6650,8 +7512,8 @@
       <c r="E51" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>237</v>
+      <c r="F51" s="1" t="s">
+        <v>1586</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>237</v>
@@ -6665,8 +7527,11 @@
       <c r="L51" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M51" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>175</v>
       </c>
@@ -6682,8 +7547,8 @@
       <c r="E52" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>237</v>
+      <c r="F52" s="1" t="s">
+        <v>1587</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>237</v>
@@ -6697,8 +7562,11 @@
       <c r="L52" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M52" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>140</v>
       </c>
@@ -6714,8 +7582,8 @@
       <c r="E53" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>237</v>
+      <c r="F53" s="1" t="s">
+        <v>1588</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>237</v>
@@ -6729,8 +7597,11 @@
       <c r="L53" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M53" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>141</v>
       </c>
@@ -6746,8 +7617,8 @@
       <c r="E54" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>237</v>
+      <c r="F54" s="1" t="s">
+        <v>1589</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>237</v>
@@ -6761,8 +7632,11 @@
       <c r="L54" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M54" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>176</v>
       </c>
@@ -6778,8 +7652,8 @@
       <c r="E55" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>237</v>
+      <c r="F55" s="1" t="s">
+        <v>1590</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>237</v>
@@ -6793,8 +7667,11 @@
       <c r="L55" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M55" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>160</v>
       </c>
@@ -6810,8 +7687,8 @@
       <c r="E56" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>237</v>
+      <c r="F56" s="1" t="s">
+        <v>1591</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>237</v>
@@ -6825,8 +7702,11 @@
       <c r="L56" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M56" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>177</v>
       </c>
@@ -6842,8 +7722,8 @@
       <c r="E57" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>237</v>
+      <c r="F57" s="1" t="s">
+        <v>1592</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>237</v>
@@ -6857,8 +7737,11 @@
       <c r="L57" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M57" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>153</v>
       </c>
@@ -6874,8 +7757,8 @@
       <c r="E58" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>237</v>
+      <c r="F58" s="1" t="s">
+        <v>1593</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>237</v>
@@ -6889,8 +7772,11 @@
       <c r="L58" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M58" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>142</v>
       </c>
@@ -6903,8 +7789,8 @@
       <c r="D59" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>237</v>
+      <c r="F59" s="1" t="s">
+        <v>1594</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>237</v>
@@ -6918,8 +7804,11 @@
       <c r="L59" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M59" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>47</v>
       </c>
@@ -6935,8 +7824,8 @@
       <c r="E60" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>237</v>
+      <c r="F60" s="1" t="s">
+        <v>1595</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>237</v>
@@ -6950,8 +7839,11 @@
       <c r="L60" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M60" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>168</v>
       </c>
@@ -6967,8 +7859,8 @@
       <c r="E61" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>237</v>
+      <c r="F61" s="1" t="s">
+        <v>1596</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>237</v>
@@ -6982,8 +7874,11 @@
       <c r="L61" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M61" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>87</v>
       </c>
@@ -6999,8 +7894,8 @@
       <c r="E62" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>237</v>
+      <c r="F62" s="1" t="s">
+        <v>1597</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>237</v>
@@ -7014,8 +7909,11 @@
       <c r="L62" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M62" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>161</v>
       </c>
@@ -7028,8 +7926,8 @@
       <c r="D63" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>237</v>
+      <c r="F63" s="1" t="s">
+        <v>1598</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>237</v>
@@ -7043,8 +7941,11 @@
       <c r="L63" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M63" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>178</v>
       </c>
@@ -7057,8 +7958,8 @@
       <c r="D64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>237</v>
+      <c r="F64" s="1" t="s">
+        <v>1599</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>237</v>
@@ -7072,8 +7973,11 @@
       <c r="L64" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M64" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>164</v>
       </c>
@@ -7089,8 +7993,8 @@
       <c r="E65" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>237</v>
+      <c r="F65" s="1" t="s">
+        <v>1600</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>237</v>
@@ -7104,8 +8008,11 @@
       <c r="L65" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M65" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>179</v>
       </c>
@@ -7121,8 +8028,8 @@
       <c r="E66" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>237</v>
+      <c r="F66" s="1" t="s">
+        <v>1601</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>237</v>
@@ -7136,8 +8043,11 @@
       <c r="L66" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M66" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>180</v>
       </c>
@@ -7150,8 +8060,8 @@
       <c r="D67" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>237</v>
+      <c r="F67" s="1" t="s">
+        <v>1602</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>237</v>
@@ -7165,8 +8075,11 @@
       <c r="L67" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M67" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>129</v>
       </c>
@@ -7179,8 +8092,8 @@
       <c r="D68" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>237</v>
+      <c r="F68" s="1" t="s">
+        <v>1603</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>237</v>
@@ -7194,8 +8107,11 @@
       <c r="L68" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M68" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>181</v>
       </c>
@@ -7208,8 +8124,8 @@
       <c r="D69" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>237</v>
+      <c r="F69" s="1" t="s">
+        <v>1604</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>237</v>
@@ -7223,8 +8139,11 @@
       <c r="L69" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M69" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>126</v>
       </c>
@@ -7237,8 +8156,8 @@
       <c r="D70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>237</v>
+      <c r="F70" s="1" t="s">
+        <v>1605</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>237</v>
@@ -7252,8 +8171,11 @@
       <c r="L70" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M70" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>151</v>
       </c>
@@ -7266,8 +8188,8 @@
       <c r="D71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>237</v>
+      <c r="F71" s="1" t="s">
+        <v>1606</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>237</v>
@@ -7281,8 +8203,11 @@
       <c r="L71" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M71" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>182</v>
       </c>
@@ -7295,8 +8220,8 @@
       <c r="D72" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>237</v>
+      <c r="F72" s="1" t="s">
+        <v>1607</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>237</v>
@@ -7310,8 +8235,11 @@
       <c r="L72" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M72" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>127</v>
       </c>
@@ -7327,8 +8255,8 @@
       <c r="E73" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>237</v>
+      <c r="F73" s="1" t="s">
+        <v>1608</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>237</v>
@@ -7342,8 +8270,11 @@
       <c r="L73" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M73" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>190</v>
       </c>
@@ -7356,8 +8287,8 @@
       <c r="D74" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>237</v>
+      <c r="F74" s="1" t="s">
+        <v>1609</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>237</v>
@@ -7371,8 +8302,11 @@
       <c r="L74" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M74" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>165</v>
       </c>
@@ -7388,8 +8322,8 @@
       <c r="E75" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>237</v>
+      <c r="F75" s="1" t="s">
+        <v>1610</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>237</v>
@@ -7403,8 +8337,11 @@
       <c r="L75" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M75" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>191</v>
       </c>
@@ -7420,8 +8357,8 @@
       <c r="E76" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>237</v>
+      <c r="F76" s="1" t="s">
+        <v>1611</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>237</v>
@@ -7435,8 +8372,11 @@
       <c r="L76" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M76" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>166</v>
       </c>
@@ -7449,8 +8389,8 @@
       <c r="D77" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>237</v>
+      <c r="F77" s="1" t="s">
+        <v>1612</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>237</v>
@@ -7464,8 +8404,11 @@
       <c r="L77" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M77" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>134</v>
       </c>
@@ -7481,8 +8424,8 @@
       <c r="E78" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>237</v>
+      <c r="F78" s="1" t="s">
+        <v>1613</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>237</v>
@@ -7496,8 +8439,11 @@
       <c r="L78" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M78" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>192</v>
       </c>
@@ -7513,8 +8459,8 @@
       <c r="E79" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>237</v>
+      <c r="F79" s="1" t="s">
+        <v>1614</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>237</v>
@@ -7528,8 +8474,11 @@
       <c r="L79" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M79" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>155</v>
       </c>
@@ -7545,8 +8494,8 @@
       <c r="E80" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>237</v>
+      <c r="F80" s="1" t="s">
+        <v>1615</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>237</v>
@@ -7560,8 +8509,11 @@
       <c r="L80" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M80" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>149</v>
       </c>
@@ -7574,8 +8526,8 @@
       <c r="D81" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>237</v>
+      <c r="F81" s="1" t="s">
+        <v>1616</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>237</v>
@@ -7589,8 +8541,11 @@
       <c r="L81" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M81" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>193</v>
       </c>
@@ -7603,8 +8558,8 @@
       <c r="D82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>237</v>
+      <c r="F82" s="1" t="s">
+        <v>1617</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>237</v>
@@ -7618,8 +8573,11 @@
       <c r="L82" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M82" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>132</v>
       </c>
@@ -7632,8 +8590,8 @@
       <c r="D83" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>237</v>
+      <c r="F83" s="1" t="s">
+        <v>1618</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>237</v>
@@ -7647,8 +8605,11 @@
       <c r="L83" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M83" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>226</v>
       </c>
@@ -7664,8 +8625,8 @@
       <c r="E84" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>237</v>
+      <c r="F84" s="1" t="s">
+        <v>1619</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>237</v>
@@ -7679,8 +8640,11 @@
       <c r="L84" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M84" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>198</v>
       </c>
@@ -7696,8 +8660,8 @@
       <c r="E85" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>237</v>
+      <c r="F85" s="1" t="s">
+        <v>1620</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>237</v>
@@ -7711,8 +8675,11 @@
       <c r="L85" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M85" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>128</v>
       </c>
@@ -7728,8 +8695,8 @@
       <c r="E86" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>237</v>
+      <c r="F86" s="1" t="s">
+        <v>1621</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>237</v>
@@ -7743,8 +8710,11 @@
       <c r="L86" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M86" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>199</v>
       </c>
@@ -7760,8 +8730,8 @@
       <c r="E87" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>237</v>
+      <c r="F87" s="1" t="s">
+        <v>1622</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>237</v>
@@ -7775,8 +8745,11 @@
       <c r="L87" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M87" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>167</v>
       </c>
@@ -7792,8 +8765,8 @@
       <c r="E88" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>237</v>
+      <c r="F88" s="1" t="s">
+        <v>1623</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>237</v>
@@ -7807,8 +8780,11 @@
       <c r="L88" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M88" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>152</v>
       </c>
@@ -7821,8 +8797,8 @@
       <c r="D89" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>237</v>
+      <c r="F89" s="1" t="s">
+        <v>1624</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>237</v>
@@ -7836,8 +8812,11 @@
       <c r="L89" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M89" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>14</v>
       </c>
@@ -7853,8 +8832,8 @@
       <c r="E90" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>237</v>
+      <c r="F90" s="1" t="s">
+        <v>1625</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>237</v>
@@ -7868,8 +8847,11 @@
       <c r="L90" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M90" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>26</v>
       </c>
@@ -7885,8 +8867,8 @@
       <c r="E91" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>237</v>
+      <c r="F91" s="1" t="s">
+        <v>1626</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>237</v>
@@ -7900,8 +8882,11 @@
       <c r="L91" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M91" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>13</v>
       </c>
@@ -7917,8 +8902,8 @@
       <c r="E92" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>237</v>
+      <c r="F92" s="1" t="s">
+        <v>1627</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>237</v>
@@ -7932,8 +8917,11 @@
       <c r="L92" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M92" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>29</v>
       </c>
@@ -7946,8 +8934,8 @@
       <c r="D93" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>237</v>
+      <c r="F93" s="1" t="s">
+        <v>1628</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>237</v>
@@ -7961,8 +8949,11 @@
       <c r="L93" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M93" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>150</v>
       </c>
@@ -7978,8 +8969,8 @@
       <c r="E94" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>237</v>
+      <c r="F94" s="1" t="s">
+        <v>1629</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>237</v>
@@ -7993,8 +8984,11 @@
       <c r="L94" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M94" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>203</v>
       </c>
@@ -8007,8 +9001,8 @@
       <c r="D95" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>237</v>
+      <c r="F95" s="1" t="s">
+        <v>1630</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>237</v>
@@ -8022,8 +9016,11 @@
       <c r="L95" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M95" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -8039,8 +9036,8 @@
       <c r="E96" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>237</v>
+      <c r="F96" s="1" t="s">
+        <v>1631</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>237</v>
@@ -8054,8 +9051,11 @@
       <c r="L96" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M96" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>9</v>
       </c>
@@ -8071,8 +9071,8 @@
       <c r="E97" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>237</v>
+      <c r="F97" s="1" t="s">
+        <v>1632</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>237</v>
@@ -8086,8 +9086,11 @@
       <c r="L97" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M97" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>218</v>
       </c>
@@ -8100,8 +9103,8 @@
       <c r="D98" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>237</v>
+      <c r="F98" s="1" t="s">
+        <v>1633</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>237</v>
@@ -8115,8 +9118,11 @@
       <c r="L98" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M98" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>37</v>
       </c>
@@ -8132,8 +9138,8 @@
       <c r="E99" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>237</v>
+      <c r="F99" s="1" t="s">
+        <v>1634</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>237</v>
@@ -8147,8 +9153,11 @@
       <c r="L99" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M99" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>38</v>
       </c>
@@ -8161,8 +9170,8 @@
       <c r="D100" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>237</v>
+      <c r="F100" s="1" t="s">
+        <v>1635</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>237</v>
@@ -8176,8 +9185,11 @@
       <c r="L100" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M100" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>44</v>
       </c>
@@ -8193,8 +9205,8 @@
       <c r="E101" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>237</v>
+      <c r="F101" s="1" t="s">
+        <v>1636</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>237</v>
@@ -8208,8 +9220,11 @@
       <c r="L101" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M101" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>72</v>
       </c>
@@ -8225,8 +9240,8 @@
       <c r="E102" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>237</v>
+      <c r="F102" s="1" t="s">
+        <v>1637</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>237</v>
@@ -8240,8 +9255,11 @@
       <c r="L102" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M102" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>71</v>
       </c>
@@ -8257,8 +9275,8 @@
       <c r="E103" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>237</v>
+      <c r="F103" s="1" t="s">
+        <v>1638</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>237</v>
@@ -8272,8 +9290,11 @@
       <c r="L103" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M103" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>70</v>
       </c>
@@ -8289,8 +9310,8 @@
       <c r="E104" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>237</v>
+      <c r="F104" s="1" t="s">
+        <v>1639</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>237</v>
@@ -8304,8 +9325,11 @@
       <c r="L104" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M104" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>200</v>
       </c>
@@ -8321,8 +9345,8 @@
       <c r="E105" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>237</v>
+      <c r="F105" s="1" t="s">
+        <v>1640</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>237</v>
@@ -8336,8 +9360,11 @@
       <c r="L105" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M105" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>146</v>
       </c>
@@ -8353,8 +9380,8 @@
       <c r="E106" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>237</v>
+      <c r="F106" s="1" t="s">
+        <v>1641</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>237</v>
@@ -8368,8 +9395,11 @@
       <c r="L106" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M106" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>30</v>
       </c>
@@ -8385,8 +9415,8 @@
       <c r="E107" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>237</v>
+      <c r="F107" s="1" t="s">
+        <v>1642</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>237</v>
@@ -8400,8 +9430,11 @@
       <c r="L107" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M107" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>201</v>
       </c>
@@ -8417,8 +9450,8 @@
       <c r="E108" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>237</v>
+      <c r="F108" s="1" t="s">
+        <v>1643</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>237</v>
@@ -8432,8 +9465,11 @@
       <c r="L108" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M108" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>202</v>
       </c>
@@ -8449,8 +9485,8 @@
       <c r="E109" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>237</v>
+      <c r="F109" s="1" t="s">
+        <v>1644</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>237</v>
@@ -8464,8 +9500,11 @@
       <c r="L109" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M109" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>102</v>
       </c>
@@ -8478,8 +9517,8 @@
       <c r="D110" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H110" s="1" t="s">
-        <v>237</v>
+      <c r="F110" s="1" t="s">
+        <v>1645</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>237</v>
@@ -8493,8 +9532,11 @@
       <c r="L110" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M110" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>162</v>
       </c>
@@ -8507,8 +9549,8 @@
       <c r="D111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>237</v>
+      <c r="F111" s="1" t="s">
+        <v>1646</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>237</v>
@@ -8522,8 +9564,11 @@
       <c r="L111" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M111" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>67</v>
       </c>
@@ -8539,8 +9584,8 @@
       <c r="E112" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>237</v>
+      <c r="F112" s="1" t="s">
+        <v>1647</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>237</v>
@@ -8554,8 +9599,11 @@
       <c r="L112" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M112" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>49</v>
       </c>
@@ -8568,8 +9616,8 @@
       <c r="D113" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>237</v>
+      <c r="F113" s="1" t="s">
+        <v>1648</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>237</v>
@@ -8583,8 +9631,11 @@
       <c r="L113" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M113" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>50</v>
       </c>
@@ -8600,8 +9651,8 @@
       <c r="E114" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>237</v>
+      <c r="F114" s="1" t="s">
+        <v>1649</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>237</v>
@@ -8615,8 +9666,11 @@
       <c r="L114" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M114" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>184</v>
       </c>
@@ -8632,8 +9686,8 @@
       <c r="E115" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>237</v>
+      <c r="F115" s="1" t="s">
+        <v>1650</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>237</v>
@@ -8647,8 +9701,11 @@
       <c r="L115" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M115" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>48</v>
       </c>
@@ -8664,8 +9721,8 @@
       <c r="E116" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>237</v>
+      <c r="F116" s="1" t="s">
+        <v>1651</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>237</v>
@@ -8679,8 +9736,11 @@
       <c r="L116" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M116" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>225</v>
       </c>
@@ -8696,8 +9756,8 @@
       <c r="E117" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>237</v>
+      <c r="F117" s="1" t="s">
+        <v>1652</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>237</v>
@@ -8711,8 +9771,11 @@
       <c r="L117" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M117" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>63</v>
       </c>
@@ -8728,8 +9791,8 @@
       <c r="E118" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>237</v>
+      <c r="F118" s="1" t="s">
+        <v>1653</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>237</v>
@@ -8743,8 +9806,11 @@
       <c r="L118" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M118" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>65</v>
       </c>
@@ -8760,8 +9826,8 @@
       <c r="E119" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>237</v>
+      <c r="F119" s="1" t="s">
+        <v>1654</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>237</v>
@@ -8775,8 +9841,11 @@
       <c r="L119" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M119" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>64</v>
       </c>
@@ -8789,8 +9858,8 @@
       <c r="D120" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>237</v>
+      <c r="F120" s="1" t="s">
+        <v>1655</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>237</v>
@@ -8804,8 +9873,11 @@
       <c r="L120" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M120" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>66</v>
       </c>
@@ -8821,8 +9893,8 @@
       <c r="E121" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>237</v>
+      <c r="F121" s="1" t="s">
+        <v>1656</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>237</v>
@@ -8836,8 +9908,11 @@
       <c r="L121" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M121" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>229</v>
       </c>
@@ -8853,8 +9928,8 @@
       <c r="E122" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>237</v>
+      <c r="F122" s="1" t="s">
+        <v>1657</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>237</v>
@@ -8868,8 +9943,11 @@
       <c r="L122" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M122" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>21</v>
       </c>
@@ -8885,8 +9963,8 @@
       <c r="E123" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>237</v>
+      <c r="F123" s="1" t="s">
+        <v>1658</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>237</v>
@@ -8900,8 +9978,11 @@
       <c r="L123" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M123" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>230</v>
       </c>
@@ -8914,8 +9995,8 @@
       <c r="D124" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>237</v>
+      <c r="F124" s="1" t="s">
+        <v>1659</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>237</v>
@@ -8929,8 +10010,11 @@
       <c r="L124" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M124" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>55</v>
       </c>
@@ -8943,8 +10027,8 @@
       <c r="D125" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>237</v>
+      <c r="F125" s="1" t="s">
+        <v>1660</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>237</v>
@@ -8958,8 +10042,11 @@
       <c r="L125" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M125" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>18</v>
       </c>
@@ -8972,8 +10059,8 @@
       <c r="D126" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H126" s="1" t="s">
-        <v>237</v>
+      <c r="F126" s="1" t="s">
+        <v>1661</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>237</v>
@@ -8987,8 +10074,11 @@
       <c r="L126" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M126" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>231</v>
       </c>
@@ -9001,8 +10091,8 @@
       <c r="D127" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H127" s="1" t="s">
-        <v>237</v>
+      <c r="F127" s="1" t="s">
+        <v>1662</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>237</v>
@@ -9016,8 +10106,11 @@
       <c r="L127" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M127" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>23</v>
       </c>
@@ -9030,8 +10123,8 @@
       <c r="D128" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H128" s="1" t="s">
-        <v>237</v>
+      <c r="F128" s="1" t="s">
+        <v>1663</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>237</v>
@@ -9045,8 +10138,11 @@
       <c r="L128" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M128" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>53</v>
       </c>
@@ -9062,8 +10158,8 @@
       <c r="E129" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H129" s="1" t="s">
-        <v>237</v>
+      <c r="F129" s="1" t="s">
+        <v>1664</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>237</v>
@@ -9077,8 +10173,11 @@
       <c r="L129" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M129" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>16</v>
       </c>
@@ -9091,8 +10190,8 @@
       <c r="D130" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H130" s="1" t="s">
-        <v>237</v>
+      <c r="F130" s="1" t="s">
+        <v>1665</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>237</v>
@@ -9106,8 +10205,11 @@
       <c r="L130" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M130" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>56</v>
       </c>
@@ -9123,8 +10225,8 @@
       <c r="E131" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>237</v>
+      <c r="F131" s="1" t="s">
+        <v>1666</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>237</v>
@@ -9138,8 +10240,11 @@
       <c r="L131" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M131" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>101</v>
       </c>
@@ -9155,8 +10260,8 @@
       <c r="E132" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>237</v>
+      <c r="F132" s="1" t="s">
+        <v>1667</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>237</v>
@@ -9170,8 +10275,11 @@
       <c r="L132" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M132" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>17</v>
       </c>
@@ -9187,8 +10295,8 @@
       <c r="E133" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>237</v>
+      <c r="F133" s="1" t="s">
+        <v>1668</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>237</v>
@@ -9202,8 +10310,11 @@
       <c r="L133" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M133" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>103</v>
       </c>
@@ -9216,8 +10327,8 @@
       <c r="D134" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>237</v>
+      <c r="F134" s="1" t="s">
+        <v>1669</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>237</v>
@@ -9231,8 +10342,11 @@
       <c r="L134" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M134" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9245,8 +10359,8 @@
       <c r="D135" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>237</v>
+      <c r="F135" s="1" t="s">
+        <v>1670</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>237</v>
@@ -9260,8 +10374,11 @@
       <c r="L135" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M135" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>59</v>
       </c>
@@ -9277,8 +10394,8 @@
       <c r="E136" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="H136" s="1" t="s">
-        <v>237</v>
+      <c r="F136" s="1" t="s">
+        <v>1671</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>237</v>
@@ -9292,8 +10409,11 @@
       <c r="L136" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M136" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>58</v>
       </c>
@@ -9309,8 +10429,8 @@
       <c r="E137" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="H137" s="1" t="s">
-        <v>237</v>
+      <c r="F137" s="1" t="s">
+        <v>1672</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>237</v>
@@ -9324,8 +10444,11 @@
       <c r="L137" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M137" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>54</v>
       </c>
@@ -9338,8 +10461,8 @@
       <c r="D138" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H138" s="1" t="s">
-        <v>237</v>
+      <c r="F138" s="1" t="s">
+        <v>1673</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>237</v>
@@ -9353,8 +10476,11 @@
       <c r="L138" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M138" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>52</v>
       </c>
@@ -9370,8 +10496,8 @@
       <c r="E139" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="H139" s="1" t="s">
-        <v>237</v>
+      <c r="F139" s="1" t="s">
+        <v>1674</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>237</v>
@@ -9385,8 +10511,11 @@
       <c r="L139" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M139" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>57</v>
       </c>
@@ -9402,8 +10531,8 @@
       <c r="E140" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="H140" s="1" t="s">
-        <v>237</v>
+      <c r="F140" s="1" t="s">
+        <v>1675</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>237</v>
@@ -9417,8 +10546,11 @@
       <c r="L140" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M140" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>51</v>
       </c>
@@ -9434,8 +10566,8 @@
       <c r="E141" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="H141" s="1" t="s">
-        <v>237</v>
+      <c r="F141" s="1" t="s">
+        <v>1676</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>237</v>
@@ -9449,8 +10581,11 @@
       <c r="L141" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M141" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>194</v>
       </c>
@@ -9463,8 +10598,8 @@
       <c r="D142" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H142" s="1" t="s">
-        <v>237</v>
+      <c r="F142" s="1" t="s">
+        <v>1677</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>237</v>
@@ -9478,8 +10613,11 @@
       <c r="L142" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M142" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>195</v>
       </c>
@@ -9495,8 +10633,8 @@
       <c r="E143" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="H143" s="1" t="s">
-        <v>237</v>
+      <c r="F143" s="1" t="s">
+        <v>1678</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>237</v>
@@ -9510,8 +10648,11 @@
       <c r="L143" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M143" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>196</v>
       </c>
@@ -9527,8 +10668,8 @@
       <c r="E144" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="H144" s="1" t="s">
-        <v>237</v>
+      <c r="F144" s="1" t="s">
+        <v>1679</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>237</v>
@@ -9542,8 +10683,11 @@
       <c r="L144" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M144" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>145</v>
       </c>
@@ -9559,8 +10703,8 @@
       <c r="E145" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="H145" s="1" t="s">
-        <v>237</v>
+      <c r="F145" s="1" t="s">
+        <v>1680</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>237</v>
@@ -9574,8 +10718,11 @@
       <c r="L145" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M145" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>197</v>
       </c>
@@ -9588,8 +10735,8 @@
       <c r="D146" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H146" s="1" t="s">
-        <v>237</v>
+      <c r="F146" s="1" t="s">
+        <v>1681</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>237</v>
@@ -9603,8 +10750,11 @@
       <c r="L146" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M146" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>73</v>
       </c>
@@ -9620,8 +10770,8 @@
       <c r="E147" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H147" s="1" t="s">
-        <v>237</v>
+      <c r="F147" s="1" t="s">
+        <v>1682</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>237</v>
@@ -9635,8 +10785,11 @@
       <c r="L147" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M147" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>154</v>
       </c>
@@ -9649,8 +10802,8 @@
       <c r="D148" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H148" s="1" t="s">
-        <v>237</v>
+      <c r="F148" s="1" t="s">
+        <v>1683</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>237</v>
@@ -9664,8 +10817,11 @@
       <c r="L148" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M148" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>46</v>
       </c>
@@ -9678,8 +10834,8 @@
       <c r="D149" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H149" s="1" t="s">
-        <v>237</v>
+      <c r="F149" s="1" t="s">
+        <v>1684</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>237</v>
@@ -9693,8 +10849,11 @@
       <c r="L149" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M149" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>232</v>
       </c>
@@ -9707,8 +10866,8 @@
       <c r="D150" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H150" s="1" t="s">
-        <v>237</v>
+      <c r="F150" s="1" t="s">
+        <v>1685</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>237</v>
@@ -9722,8 +10881,11 @@
       <c r="L150" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M150" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>169</v>
       </c>
@@ -9736,8 +10898,8 @@
       <c r="D151" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H151" s="1" t="s">
-        <v>237</v>
+      <c r="F151" s="1" t="s">
+        <v>1686</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>237</v>
@@ -9751,8 +10913,11 @@
       <c r="L151" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M151" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>219</v>
       </c>
@@ -9765,8 +10930,8 @@
       <c r="D152" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H152" s="1" t="s">
-        <v>237</v>
+      <c r="F152" s="1" t="s">
+        <v>1687</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>237</v>
@@ -9780,8 +10945,11 @@
       <c r="L152" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M152" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>31</v>
       </c>
@@ -9797,8 +10965,8 @@
       <c r="E153" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H153" s="1" t="s">
-        <v>237</v>
+      <c r="F153" s="1" t="s">
+        <v>1688</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>237</v>
@@ -9812,8 +10980,11 @@
       <c r="L153" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M153" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>143</v>
       </c>
@@ -9829,8 +11000,8 @@
       <c r="E154" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="H154" s="1" t="s">
-        <v>237</v>
+      <c r="F154" s="1" t="s">
+        <v>1689</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>237</v>
@@ -9844,8 +11015,11 @@
       <c r="L154" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M154" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>74</v>
       </c>
@@ -9861,8 +11035,8 @@
       <c r="E155" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="H155" s="1" t="s">
-        <v>237</v>
+      <c r="F155" s="1" t="s">
+        <v>1690</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>237</v>
@@ -9876,8 +11050,11 @@
       <c r="L155" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M155" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>221</v>
       </c>
@@ -9893,8 +11070,8 @@
       <c r="E156" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="H156" s="1" t="s">
-        <v>237</v>
+      <c r="F156" s="1" t="s">
+        <v>1691</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>237</v>
@@ -9908,8 +11085,11 @@
       <c r="L156" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M156" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>222</v>
       </c>
@@ -9925,8 +11105,8 @@
       <c r="E157" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="H157" s="1" t="s">
-        <v>237</v>
+      <c r="F157" s="1" t="s">
+        <v>1692</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>237</v>
@@ -9940,8 +11120,11 @@
       <c r="L157" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M157" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>220</v>
       </c>
@@ -9957,8 +11140,8 @@
       <c r="E158" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="H158" s="1" t="s">
-        <v>237</v>
+      <c r="F158" s="1" t="s">
+        <v>1693</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>237</v>
@@ -9972,8 +11155,11 @@
       <c r="L158" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M158" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>156</v>
       </c>
@@ -9986,8 +11172,8 @@
       <c r="D159" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H159" s="1" t="s">
-        <v>237</v>
+      <c r="F159" s="1" t="s">
+        <v>1694</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>237</v>
@@ -10001,8 +11187,11 @@
       <c r="L159" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M159" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>223</v>
       </c>
@@ -10018,8 +11207,8 @@
       <c r="E160" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="H160" s="1" t="s">
-        <v>237</v>
+      <c r="F160" s="1" t="s">
+        <v>1695</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>237</v>
@@ -10033,8 +11222,11 @@
       <c r="L160" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M160" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>147</v>
       </c>
@@ -10050,8 +11242,8 @@
       <c r="E161" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="H161" s="1" t="s">
-        <v>237</v>
+      <c r="F161" s="1" t="s">
+        <v>1696</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>237</v>
@@ -10065,8 +11257,11 @@
       <c r="L161" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M161" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>224</v>
       </c>
@@ -10079,8 +11274,8 @@
       <c r="D162" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H162" s="1" t="s">
-        <v>237</v>
+      <c r="F162" s="1" t="s">
+        <v>1697</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>237</v>
@@ -10094,8 +11289,11 @@
       <c r="L162" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M162" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>215</v>
       </c>
@@ -10108,8 +11306,8 @@
       <c r="D163" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H163" s="1" t="s">
-        <v>237</v>
+      <c r="F163" s="1" t="s">
+        <v>1698</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>237</v>
@@ -10123,8 +11321,11 @@
       <c r="L163" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M163" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>144</v>
       </c>
@@ -10137,8 +11338,8 @@
       <c r="D164" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H164" s="1" t="s">
-        <v>237</v>
+      <c r="F164" s="1" t="s">
+        <v>1699</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>237</v>
@@ -10152,8 +11353,11 @@
       <c r="L164" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M164" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>43</v>
       </c>
@@ -10169,8 +11373,8 @@
       <c r="E165" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="H165" s="1" t="s">
-        <v>237</v>
+      <c r="F165" s="1" t="s">
+        <v>1700</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>237</v>
@@ -10184,8 +11388,11 @@
       <c r="L165" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M165" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>39</v>
       </c>
@@ -10201,8 +11408,8 @@
       <c r="E166" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="H166" s="1" t="s">
-        <v>237</v>
+      <c r="F166" s="1" t="s">
+        <v>1701</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>237</v>
@@ -10216,8 +11423,11 @@
       <c r="L166" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M166" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>170</v>
       </c>
@@ -10230,8 +11440,8 @@
       <c r="D167" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H167" s="1" t="s">
-        <v>237</v>
+      <c r="F167" s="1" t="s">
+        <v>1702</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>237</v>
@@ -10245,8 +11455,11 @@
       <c r="L167" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M167" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>216</v>
       </c>
@@ -10262,8 +11475,8 @@
       <c r="E168" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="H168" s="1" t="s">
-        <v>237</v>
+      <c r="F168" s="1" t="s">
+        <v>1703</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>237</v>
@@ -10277,8 +11490,11 @@
       <c r="L168" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M168" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>40</v>
       </c>
@@ -10294,8 +11510,8 @@
       <c r="E169" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="H169" s="1" t="s">
-        <v>237</v>
+      <c r="F169" s="1" t="s">
+        <v>1704</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>237</v>
@@ -10309,8 +11525,11 @@
       <c r="L169" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M169" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>227</v>
       </c>
@@ -10326,8 +11545,8 @@
       <c r="E170" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="H170" s="1" t="s">
-        <v>237</v>
+      <c r="F170" s="1" t="s">
+        <v>1705</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>237</v>
@@ -10341,8 +11560,11 @@
       <c r="L170" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M170" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>217</v>
       </c>
@@ -10358,8 +11580,8 @@
       <c r="E171" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="H171" s="1" t="s">
-        <v>237</v>
+      <c r="F171" s="1" t="s">
+        <v>1706</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>237</v>
@@ -10373,8 +11595,11 @@
       <c r="L171" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M171" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>148</v>
       </c>
@@ -10390,8 +11615,8 @@
       <c r="E172" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="H172" s="1" t="s">
-        <v>237</v>
+      <c r="F172" s="1" t="s">
+        <v>1707</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>237</v>
@@ -10405,8 +11630,11 @@
       <c r="L172" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M172" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>183</v>
       </c>
@@ -10422,8 +11650,8 @@
       <c r="E173" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H173" s="1" t="s">
-        <v>237</v>
+      <c r="F173" s="1" t="s">
+        <v>1708</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>237</v>
@@ -10437,8 +11665,11 @@
       <c r="L173" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M173" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>172</v>
       </c>
@@ -10454,8 +11685,8 @@
       <c r="E174" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="H174" s="1" t="s">
-        <v>237</v>
+      <c r="F174" s="1" t="s">
+        <v>1709</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>237</v>
@@ -10469,8 +11700,11 @@
       <c r="L174" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M174" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>185</v>
       </c>
@@ -10486,8 +11720,8 @@
       <c r="E175" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H175" s="1" t="s">
-        <v>237</v>
+      <c r="F175" s="1" t="s">
+        <v>1710</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>237</v>
@@ -10501,8 +11735,11 @@
       <c r="L175" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M175" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>133</v>
       </c>
@@ -10518,8 +11755,8 @@
       <c r="E176" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="H176" s="1" t="s">
-        <v>237</v>
+      <c r="F176" s="1" t="s">
+        <v>1711</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>237</v>
@@ -10533,8 +11770,11 @@
       <c r="L176" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M176" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>186</v>
       </c>
@@ -10550,8 +11790,8 @@
       <c r="E177" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="H177" s="1" t="s">
-        <v>237</v>
+      <c r="F177" s="1" t="s">
+        <v>1712</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>237</v>
@@ -10565,8 +11805,11 @@
       <c r="L177" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M177" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>187</v>
       </c>
@@ -10582,8 +11825,8 @@
       <c r="E178" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H178" s="1" t="s">
-        <v>237</v>
+      <c r="F178" s="1" t="s">
+        <v>1713</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>237</v>
@@ -10597,8 +11840,11 @@
       <c r="L178" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M178" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>188</v>
       </c>
@@ -10614,8 +11860,8 @@
       <c r="E179" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="H179" s="1" t="s">
-        <v>237</v>
+      <c r="F179" s="1" t="s">
+        <v>1714</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>237</v>
@@ -10629,8 +11875,11 @@
       <c r="L179" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M179" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>189</v>
       </c>
@@ -10646,8 +11895,8 @@
       <c r="E180" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="H180" s="1" t="s">
-        <v>237</v>
+      <c r="F180" s="1" t="s">
+        <v>1715</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>237</v>
@@ -10661,8 +11910,11 @@
       <c r="L180" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M180" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>45</v>
       </c>
@@ -10678,8 +11930,8 @@
       <c r="E181" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H181" s="1" t="s">
-        <v>237</v>
+      <c r="F181" s="1" t="s">
+        <v>1716</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>237</v>
@@ -10693,8 +11945,11 @@
       <c r="L181" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M181" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>83</v>
       </c>
@@ -10710,8 +11965,8 @@
       <c r="E182" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="H182" s="1" t="s">
-        <v>237</v>
+      <c r="F182" s="1" t="s">
+        <v>1717</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>237</v>
@@ -10725,8 +11980,11 @@
       <c r="L182" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M182" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>525</v>
       </c>
@@ -10742,8 +12000,8 @@
       <c r="E183" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H183" s="1" t="s">
-        <v>237</v>
+      <c r="F183" s="1" t="s">
+        <v>1718</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>237</v>
@@ -10757,8 +12015,11 @@
       <c r="L183" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M183" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>528</v>
       </c>
@@ -10774,8 +12035,8 @@
       <c r="E184" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="H184" s="1" t="s">
-        <v>237</v>
+      <c r="F184" s="1" t="s">
+        <v>1719</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>237</v>
@@ -10789,8 +12050,11 @@
       <c r="L184" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M184" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>68</v>
       </c>
@@ -10806,8 +12070,8 @@
       <c r="E185" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H185" s="1" t="s">
-        <v>237</v>
+      <c r="F185" s="1" t="s">
+        <v>1720</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>237</v>
@@ -10821,8 +12085,11 @@
       <c r="L185" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M185" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>35</v>
       </c>
@@ -10838,8 +12105,8 @@
       <c r="E186" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H186" s="1" t="s">
-        <v>237</v>
+      <c r="F186" s="1" t="s">
+        <v>1721</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>237</v>
@@ -10853,8 +12120,11 @@
       <c r="L186" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M186" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>36</v>
       </c>
@@ -10870,8 +12140,8 @@
       <c r="E187" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="H187" s="1" t="s">
-        <v>237</v>
+      <c r="F187" s="1" t="s">
+        <v>1722</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>237</v>
@@ -10885,8 +12155,11 @@
       <c r="L187" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M187" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>69</v>
       </c>
@@ -10902,8 +12175,8 @@
       <c r="E188" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H188" s="1" t="s">
-        <v>237</v>
+      <c r="F188" s="1" t="s">
+        <v>1723</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>237</v>
@@ -10917,8 +12190,11 @@
       <c r="L188" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M188" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>539</v>
       </c>
@@ -10934,8 +12210,8 @@
       <c r="E189" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="H189" s="1" t="s">
-        <v>237</v>
+      <c r="F189" s="1" t="s">
+        <v>1724</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>237</v>
@@ -10949,8 +12225,11 @@
       <c r="L189" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M189" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>542</v>
       </c>
@@ -10966,8 +12245,8 @@
       <c r="E190" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="H190" s="1" t="s">
-        <v>237</v>
+      <c r="F190" s="1" t="s">
+        <v>1725</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>237</v>
@@ -10981,8 +12260,11 @@
       <c r="L190" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M190" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>24</v>
       </c>
@@ -10998,8 +12280,8 @@
       <c r="E191" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="H191" s="1" t="s">
-        <v>237</v>
+      <c r="F191" s="1" t="s">
+        <v>1726</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>237</v>
@@ -11013,8 +12295,11 @@
       <c r="L191" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M191" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>12</v>
       </c>
@@ -11030,8 +12315,8 @@
       <c r="E192" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="H192" s="1" t="s">
-        <v>237</v>
+      <c r="F192" s="1" t="s">
+        <v>1727</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>237</v>
@@ -11045,8 +12330,11 @@
       <c r="L192" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M192" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>131</v>
       </c>
@@ -11062,8 +12350,8 @@
       <c r="E193" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="H193" s="1" t="s">
-        <v>237</v>
+      <c r="F193" s="1" t="s">
+        <v>1728</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>237</v>
@@ -11077,8 +12365,11 @@
       <c r="L193" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M193" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>551</v>
       </c>
@@ -11094,8 +12385,8 @@
       <c r="E194" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="H194" s="1" t="s">
-        <v>237</v>
+      <c r="F194" s="1" t="s">
+        <v>1729</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>237</v>
@@ -11109,8 +12400,11 @@
       <c r="L194" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M194" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>554</v>
       </c>
@@ -11126,8 +12420,8 @@
       <c r="E195" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="H195" s="1" t="s">
-        <v>237</v>
+      <c r="F195" s="1" t="s">
+        <v>1730</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>237</v>
@@ -11141,8 +12435,11 @@
       <c r="L195" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M195" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>557</v>
       </c>
@@ -11158,8 +12455,8 @@
       <c r="E196" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="H196" s="1" t="s">
-        <v>237</v>
+      <c r="F196" s="1" t="s">
+        <v>1731</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>237</v>
@@ -11173,8 +12470,11 @@
       <c r="L196" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M196" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>560</v>
       </c>
@@ -11190,8 +12490,8 @@
       <c r="E197" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="H197" s="1" t="s">
-        <v>237</v>
+      <c r="F197" s="1" t="s">
+        <v>1732</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>237</v>
@@ -11205,8 +12505,11 @@
       <c r="L197" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M197" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>159</v>
       </c>
@@ -11222,8 +12525,8 @@
       <c r="E198" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="H198" s="1" t="s">
-        <v>237</v>
+      <c r="F198" s="1" t="s">
+        <v>1733</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>237</v>
@@ -11237,8 +12540,11 @@
       <c r="L198" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M198" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>565</v>
       </c>
@@ -11254,8 +12560,8 @@
       <c r="E199" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="H199" s="1" t="s">
-        <v>237</v>
+      <c r="F199" s="1" t="s">
+        <v>1734</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>237</v>
@@ -11269,8 +12575,11 @@
       <c r="L199" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M199" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>568</v>
       </c>
@@ -11286,8 +12595,8 @@
       <c r="E200" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="H200" s="1" t="s">
-        <v>237</v>
+      <c r="F200" s="1" t="s">
+        <v>1735</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>237</v>
@@ -11301,8 +12610,11 @@
       <c r="L200" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M200" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>571</v>
       </c>
@@ -11318,8 +12630,8 @@
       <c r="E201" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="H201" s="1" t="s">
-        <v>237</v>
+      <c r="F201" s="1" t="s">
+        <v>1736</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>237</v>
@@ -11333,8 +12645,11 @@
       <c r="L201" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M201" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>574</v>
       </c>
@@ -11350,8 +12665,8 @@
       <c r="E202" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="H202" s="1" t="s">
-        <v>237</v>
+      <c r="F202" s="1" t="s">
+        <v>1737</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>237</v>
@@ -11365,8 +12680,11 @@
       <c r="L202" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M202" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>157</v>
       </c>
@@ -11382,8 +12700,8 @@
       <c r="E203" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="H203" s="1" t="s">
-        <v>237</v>
+      <c r="F203" s="1" t="s">
+        <v>1738</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>237</v>
@@ -11397,8 +12715,11 @@
       <c r="L203" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M203" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>579</v>
       </c>
@@ -11414,8 +12735,8 @@
       <c r="E204" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="H204" s="1" t="s">
-        <v>237</v>
+      <c r="F204" s="1" t="s">
+        <v>1739</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>237</v>
@@ -11429,8 +12750,11 @@
       <c r="L204" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M204" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>582</v>
       </c>
@@ -11446,8 +12770,8 @@
       <c r="E205" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H205" s="1" t="s">
-        <v>237</v>
+      <c r="F205" s="1" t="s">
+        <v>1740</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>237</v>
@@ -11459,10 +12783,13 @@
         <v>237</v>
       </c>
       <c r="L205" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M205" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>204</v>
       </c>
@@ -11478,8 +12805,8 @@
       <c r="E206" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="H206" s="1" t="s">
-        <v>237</v>
+      <c r="F206" s="1" t="s">
+        <v>1741</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>237</v>
@@ -11493,8 +12820,11 @@
       <c r="L206" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M206" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>205</v>
       </c>
@@ -11510,8 +12840,8 @@
       <c r="E207" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="H207" s="1" t="s">
-        <v>237</v>
+      <c r="F207" s="1" t="s">
+        <v>1742</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>237</v>
@@ -11525,8 +12855,11 @@
       <c r="L207" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M207" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>158</v>
       </c>
@@ -11542,8 +12875,8 @@
       <c r="E208" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="H208" s="1" t="s">
-        <v>237</v>
+      <c r="F208" s="1" t="s">
+        <v>1743</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>237</v>
@@ -11557,8 +12890,11 @@
       <c r="L208" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M208" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>206</v>
       </c>
@@ -11571,8 +12907,8 @@
       <c r="D209" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H209" s="1" t="s">
-        <v>237</v>
+      <c r="F209" s="1" t="s">
+        <v>1744</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>237</v>
@@ -11586,8 +12922,11 @@
       <c r="L209" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M209" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>207</v>
       </c>
@@ -11603,8 +12942,8 @@
       <c r="E210" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="H210" s="1" t="s">
-        <v>237</v>
+      <c r="F210" s="1" t="s">
+        <v>1745</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>237</v>
@@ -11618,8 +12957,11 @@
       <c r="L210" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M210" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>208</v>
       </c>
@@ -11635,8 +12977,8 @@
       <c r="E211" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="H211" s="1" t="s">
-        <v>237</v>
+      <c r="F211" s="1" t="s">
+        <v>1746</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>237</v>
@@ -11650,8 +12992,11 @@
       <c r="L211" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M211" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>209</v>
       </c>
@@ -11667,8 +13012,8 @@
       <c r="E212" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="H212" s="1" t="s">
-        <v>237</v>
+      <c r="F212" s="1" t="s">
+        <v>1747</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>237</v>
@@ -11682,8 +13027,11 @@
       <c r="L212" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M212" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>171</v>
       </c>
@@ -11699,8 +13047,8 @@
       <c r="E213" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="H213" s="1" t="s">
-        <v>237</v>
+      <c r="F213" s="1" t="s">
+        <v>1748</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>237</v>
@@ -11714,8 +13062,11 @@
       <c r="L213" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M213" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>60</v>
       </c>
@@ -11731,8 +13082,8 @@
       <c r="E214" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="H214" s="1" t="s">
-        <v>237</v>
+      <c r="F214" s="1" t="s">
+        <v>1749</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>237</v>
@@ -11746,8 +13097,11 @@
       <c r="L214" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M214" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>62</v>
       </c>
@@ -11763,8 +13117,8 @@
       <c r="E215" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="H215" s="1" t="s">
-        <v>237</v>
+      <c r="F215" s="1" t="s">
+        <v>1750</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>237</v>
@@ -11778,8 +13132,11 @@
       <c r="L215" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M215" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>105</v>
       </c>
@@ -11795,8 +13152,8 @@
       <c r="E216" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="H216" s="1" t="s">
-        <v>237</v>
+      <c r="F216" s="1" t="s">
+        <v>1751</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>237</v>
@@ -11810,8 +13167,11 @@
       <c r="L216" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M216" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>104</v>
       </c>
@@ -11827,8 +13187,8 @@
       <c r="E217" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="H217" s="1" t="s">
-        <v>237</v>
+      <c r="F217" s="1" t="s">
+        <v>1752</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>237</v>
@@ -11842,8 +13202,11 @@
       <c r="L217" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M217" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>61</v>
       </c>
@@ -11859,8 +13222,8 @@
       <c r="E218" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="H218" s="1" t="s">
-        <v>237</v>
+      <c r="F218" s="1" t="s">
+        <v>1753</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>237</v>
@@ -11874,8 +13237,11 @@
       <c r="L218" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M218" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>95</v>
       </c>
@@ -11891,8 +13257,8 @@
       <c r="E219" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="H219" s="1" t="s">
-        <v>237</v>
+      <c r="F219" s="1" t="s">
+        <v>1754</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>237</v>
@@ -11906,8 +13272,11 @@
       <c r="L219" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M219" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>78</v>
       </c>
@@ -11920,8 +13289,8 @@
       <c r="D220" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H220" s="1" t="s">
-        <v>237</v>
+      <c r="F220" s="1" t="s">
+        <v>1755</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>237</v>
@@ -11935,8 +13304,11 @@
       <c r="L220" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M220" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>75</v>
       </c>
@@ -11949,8 +13321,8 @@
       <c r="D221" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H221" s="1" t="s">
-        <v>237</v>
+      <c r="F221" s="1" t="s">
+        <v>1756</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>237</v>
@@ -11964,8 +13336,11 @@
       <c r="L221" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M221" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>92</v>
       </c>
@@ -11981,8 +13356,8 @@
       <c r="E222" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="H222" s="1" t="s">
-        <v>237</v>
+      <c r="F222" s="1" t="s">
+        <v>1757</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>237</v>
@@ -11996,8 +13371,11 @@
       <c r="L222" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M222" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>93</v>
       </c>
@@ -12013,8 +13391,8 @@
       <c r="E223" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="H223" s="1" t="s">
-        <v>237</v>
+      <c r="F223" s="1" t="s">
+        <v>1758</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>237</v>
@@ -12028,8 +13406,11 @@
       <c r="L223" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M223" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>81</v>
       </c>
@@ -12045,8 +13426,8 @@
       <c r="E224" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="H224" s="1" t="s">
-        <v>237</v>
+      <c r="F224" s="1" t="s">
+        <v>1759</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>237</v>
@@ -12060,8 +13441,11 @@
       <c r="L224" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M224" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>84</v>
       </c>
@@ -12077,8 +13461,8 @@
       <c r="E225" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="H225" s="1" t="s">
-        <v>237</v>
+      <c r="F225" s="1" t="s">
+        <v>1760</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>237</v>
@@ -12092,8 +13476,11 @@
       <c r="L225" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M225" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>100</v>
       </c>
@@ -12109,8 +13496,8 @@
       <c r="E226" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="H226" s="1" t="s">
-        <v>237</v>
+      <c r="F226" s="1" t="s">
+        <v>1761</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>237</v>
@@ -12124,8 +13511,11 @@
       <c r="L226" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M226" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>85</v>
       </c>
@@ -12141,8 +13531,8 @@
       <c r="E227" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="H227" s="1" t="s">
-        <v>237</v>
+      <c r="F227" s="1" t="s">
+        <v>1762</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>237</v>
@@ -12156,8 +13546,11 @@
       <c r="L227" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M227" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>86</v>
       </c>
@@ -12173,8 +13566,8 @@
       <c r="E228" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="H228" s="1" t="s">
-        <v>237</v>
+      <c r="F228" s="1" t="s">
+        <v>1763</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>237</v>
@@ -12188,8 +13581,11 @@
       <c r="L228" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M228" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>96</v>
       </c>
@@ -12205,8 +13601,8 @@
       <c r="E229" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="H229" s="1" t="s">
-        <v>237</v>
+      <c r="F229" s="1" t="s">
+        <v>1764</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>237</v>
@@ -12220,8 +13616,11 @@
       <c r="L229" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M229" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>91</v>
       </c>
@@ -12237,8 +13636,8 @@
       <c r="E230" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="H230" s="1" t="s">
-        <v>237</v>
+      <c r="F230" s="1" t="s">
+        <v>1765</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>237</v>
@@ -12252,8 +13651,11 @@
       <c r="L230" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M230" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>97</v>
       </c>
@@ -12269,8 +13671,8 @@
       <c r="E231" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="H231" s="1" t="s">
-        <v>237</v>
+      <c r="F231" s="1" t="s">
+        <v>1766</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>237</v>
@@ -12284,8 +13686,11 @@
       <c r="L231" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M231" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>89</v>
       </c>
@@ -12301,8 +13706,8 @@
       <c r="E232" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="H232" s="1" t="s">
-        <v>237</v>
+      <c r="F232" s="1" t="s">
+        <v>1767</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>237</v>
@@ -12316,8 +13721,11 @@
       <c r="L232" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M232" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>98</v>
       </c>
@@ -12333,8 +13741,8 @@
       <c r="E233" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="H233" s="1" t="s">
-        <v>237</v>
+      <c r="F233" s="1" t="s">
+        <v>1768</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>237</v>
@@ -12348,8 +13756,11 @@
       <c r="L233" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M233" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>76</v>
       </c>
@@ -12365,8 +13776,8 @@
       <c r="E234" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="H234" s="1" t="s">
-        <v>237</v>
+      <c r="F234" s="1" t="s">
+        <v>1769</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>237</v>
@@ -12380,8 +13791,11 @@
       <c r="L234" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M234" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>79</v>
       </c>
@@ -12394,8 +13808,8 @@
       <c r="D235" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H235" s="1" t="s">
-        <v>237</v>
+      <c r="F235" s="1" t="s">
+        <v>1770</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>237</v>
@@ -12409,8 +13823,11 @@
       <c r="L235" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M235" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>80</v>
       </c>
@@ -12423,8 +13840,8 @@
       <c r="D236" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H236" s="1" t="s">
-        <v>237</v>
+      <c r="F236" s="1" t="s">
+        <v>1771</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>237</v>
@@ -12438,8 +13855,11 @@
       <c r="L236" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M236" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>99</v>
       </c>
@@ -12452,8 +13872,8 @@
       <c r="D237" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H237" s="1" t="s">
-        <v>237</v>
+      <c r="F237" s="1" t="s">
+        <v>1772</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>237</v>
@@ -12467,8 +13887,11 @@
       <c r="L237" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M237" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>88</v>
       </c>
@@ -12481,8 +13904,8 @@
       <c r="D238" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H238" s="1" t="s">
-        <v>237</v>
+      <c r="F238" s="1" t="s">
+        <v>1773</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>237</v>
@@ -12496,8 +13919,11 @@
       <c r="L238" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M238" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>94</v>
       </c>
@@ -12510,8 +13936,8 @@
       <c r="D239" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H239" s="1" t="s">
-        <v>237</v>
+      <c r="F239" s="1" t="s">
+        <v>1774</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>237</v>
@@ -12525,8 +13951,11 @@
       <c r="L239" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M239" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>210</v>
       </c>
@@ -12539,8 +13968,8 @@
       <c r="D240" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H240" s="1" t="s">
-        <v>237</v>
+      <c r="F240" s="1" t="s">
+        <v>1775</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>237</v>
@@ -12554,8 +13983,11 @@
       <c r="L240" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M240" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>90</v>
       </c>
@@ -12568,8 +14000,8 @@
       <c r="D241" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H241" s="1" t="s">
-        <v>237</v>
+      <c r="F241" s="1" t="s">
+        <v>1776</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>237</v>
@@ -12583,8 +14015,11 @@
       <c r="L241" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M241" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>82</v>
       </c>
@@ -12600,8 +14035,8 @@
       <c r="E242" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="H242" s="1" t="s">
-        <v>237</v>
+      <c r="F242" s="1" t="s">
+        <v>1777</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>237</v>
@@ -12615,8 +14050,11 @@
       <c r="L242" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M242" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>77</v>
       </c>
@@ -12632,8 +14070,8 @@
       <c r="E243" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="H243" s="1" t="s">
-        <v>237</v>
+      <c r="F243" s="1" t="s">
+        <v>1778</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>237</v>
@@ -12645,6 +14083,9 @@
         <v>237</v>
       </c>
       <c r="L243" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M243" s="1" t="s">
         <v>237</v>
       </c>
     </row>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77AD699-3415-4657-8589-5428B35F9EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3CD438-5A5A-4F56-B425-67F974A3A679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6570" uniqueCount="2296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6570" uniqueCount="2295">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6964,10 +6964,6 @@
   </si>
   <si>
     <t>weapon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>$item?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -7512,7 +7508,7 @@
         <v>2266</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7544,7 +7540,7 @@
         <v>2271</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -13241,10 +13237,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>2290</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>2291</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>1521</v>
@@ -13293,34 +13289,34 @@
         <v>2272</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2274</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2276</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>2277</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>2278</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>2279</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>2295</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>2280</v>
-      </c>
       <c r="L1" s="2" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -13331,34 +13327,34 @@
         <v>2273</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>2275</v>
+        <v>2288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -13404,7 +13400,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -13412,17 +13408,26 @@
       <c r="D4" s="2">
         <v>0</v>
       </c>
+      <c r="E4" s="2">
+        <v>60</v>
+      </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
+      <c r="G4" s="2">
+        <v>2</v>
+      </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
+      <c r="I4" s="2">
+        <v>16</v>
+      </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
   </sheetData>
@@ -24908,10 +24913,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>657</v>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -5,20 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65801FBF-F0D5-4381-B150-D84FFCA82D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7154F340-9D20-41A6-B4A2-11577A461E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
-    <sheet name="preset" sheetId="7" r:id="rId2"/>
-    <sheet name="sell" sheetId="3" r:id="rId3"/>
-    <sheet name="buy" sheetId="4" r:id="rId4"/>
-    <sheet name="npc_spawn" sheetId="5" r:id="rId5"/>
-    <sheet name="soliloquy" sheetId="6" r:id="rId6"/>
+    <sheet name="sell" sheetId="3" r:id="rId2"/>
+    <sheet name="buy" sheetId="4" r:id="rId3"/>
+    <sheet name="npc_spawn" sheetId="5" r:id="rId4"/>
+    <sheet name="soliloquy" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6609" uniqueCount="2310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6565" uniqueCount="2288">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6955,74 +6954,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weapon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weapon_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>armor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>armor_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>disguise</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint16?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NORMAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>261</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -7036,26 +6967,6 @@
   </si>
   <si>
     <t>10, 10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shield_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint8?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WOMAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GHOST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RIDING</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -7197,7 +7108,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7213,7 +7124,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -7563,7 +7474,7 @@
         <v>2266</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>2290</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7595,7 +7506,7 @@
         <v>2271</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>2291</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -13292,10 +13203,10 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>2289</v>
+        <v>2272</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>2301</v>
+        <v>2279</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>1521</v>
@@ -13318,10 +13229,10 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>2298</v>
+        <v>2276</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>2302</v>
+        <v>2280</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>1521</v>
@@ -13344,10 +13255,10 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>2299</v>
+        <v>2277</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>2303</v>
+        <v>2281</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>1521</v>
@@ -13370,10 +13281,10 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>2300</v>
+        <v>2278</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>2304</v>
+        <v>2282</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>1521</v>
@@ -13405,258 +13316,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72547E2E-7C01-450E-BFAA-AA26DEFD419B}">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2272</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2285</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2287</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2274</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2275</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2276</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>2277</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>2278</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>2293</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>2279</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>2281</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2288</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>2280</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2294</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2280</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>2294</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2294</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>2294</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>2280</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2283</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>2284</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2295</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>60</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>16</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>2284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2283</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>60</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>16</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>2296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>2295</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>60</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>16</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>2297</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467D91EC-BF40-4F9B-8B8D-6019747193CB}">
   <dimension ref="A1:E756"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -19231,7 +18890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22443152-8BD8-489A-B59C-AD30C7EE0DA5}">
   <dimension ref="A1:D790"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -25063,7 +24722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A8B4EC-A9F0-4F37-A700-83BC81A3F915}">
   <dimension ref="A1:D1474"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
@@ -25133,10 +24792,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>2289</v>
+        <v>2272</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2292</v>
+        <v>2275</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>657</v>
@@ -25144,35 +24803,35 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>2298</v>
+        <v>2276</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2305</v>
+        <v>2283</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2307</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>2299</v>
+        <v>2277</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2306</v>
+        <v>2284</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2308</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>2300</v>
+        <v>2278</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1274</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2309</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -38141,7 +37800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B925D1-5541-4FEF-A6C8-C42626081064}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44090542-2495-48C9-AA48-A33D13FBA94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EDC6C7-D805-49B4-9515-EC964468CA41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8831" uniqueCount="2264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7063" uniqueCount="2271">
   <si>
     <t>map</t>
   </si>
@@ -6790,42 +6790,78 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>scripts/npc/원주민장로.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/찬찬.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/폭염도미용사.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/폭염왕장식품.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/화사화사.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/화화.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/환상의섬무당.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/환상의섬갑옷상.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/돌순이.lua</t>
-  </si>
-  <si>
-    <t>scripts/npc/돌돌이.lua</t>
-  </si>
-  <si>
     <t>도주영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>scripts/npc/도주영.lua</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길림미로보초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길림동굴보초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/npc/길림미로보초.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/npc/길림동굴보초.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC_265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC_266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>267</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서쪽태극문보초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>268</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동쪽태극문보초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/npc/서쪽태극문보초.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/npc/동쪽태극문보초.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC_267</t>
+  </si>
+  <si>
+    <t>NPC_268</t>
   </si>
 </sst>
 </file>
@@ -7232,7 +7268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J256"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -9709,7 +9745,7 @@
         <v>1292</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>2262</v>
+        <v>2252</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>1293</v>
@@ -9718,7 +9754,7 @@
         <v>10</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>2263</v>
+        <v>2253</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>1294</v>
@@ -13257,6 +13293,98 @@
       </c>
       <c r="J256" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>2259</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66B700D-D86F-4031-BE3D-FB9C8E7AE991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7D9ACF-D0E2-414B-8EFF-081CAFE0C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="npc" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9256" uniqueCount="3347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9256" uniqueCount="3349">
   <si>
     <t>map</t>
   </si>
@@ -10068,6 +10068,28 @@
   </si>
   <si>
     <t>scripts/npc/흑령굴도우미.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2
+3
+4
+5
+6
+7
+8
+9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11
+12
+13
+14
+15
+16
+17
+18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11015,7 +11037,7 @@
         <v>1183</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1173</v>
+        <v>3347</v>
       </c>
       <c r="H19" s="3">
         <v>10</v>
@@ -11045,7 +11067,7 @@
         <v>1183</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1173</v>
+        <v>3347</v>
       </c>
       <c r="H20" s="3">
         <v>10</v>
@@ -11075,7 +11097,7 @@
         <v>1187</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>30</v>
+        <v>3348</v>
       </c>
       <c r="H21" s="3">
         <v>19</v>
@@ -11105,7 +11127,7 @@
         <v>1189</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>30</v>
+        <v>3348</v>
       </c>
       <c r="H22" s="3">
         <v>19</v>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H556"/>
+  <dimension ref="A1:H557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -15357,6 +15357,27 @@
         </is>
       </c>
       <c r="H556" s="4" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="0" t="n">
+        <v>625</v>
+      </c>
+      <c r="B557" s="0" t="inlineStr">
+        <is>
+          <t>문파성선생</t>
+        </is>
+      </c>
+      <c r="C557" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="D557" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G557" s="0" t="inlineStr">
+        <is>
+          <t>REVIVE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40299,7 +40320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2280"/>
+  <dimension ref="A1:D2288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -72739,6 +72760,86 @@
         </is>
       </c>
       <c r="D2280" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="n">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="B2282" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>14, 19</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="B2284" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>14, 19</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="n">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="B2286" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>14, 19</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="B2288" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>14, 19</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -70139,15 +70139,15 @@
     </row>
     <row r="2044">
       <c r="A2044" s="9" t="n"/>
-      <c r="B2044" t="n">
+      <c r="B2044" s="0" t="n">
         <v>545</v>
       </c>
-      <c r="C2044" t="inlineStr">
+      <c r="C2044" s="0" t="inlineStr">
         <is>
           <t>10, 6</t>
         </is>
       </c>
-      <c r="D2044" t="inlineStr">
+      <c r="D2044" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70192,15 +70192,15 @@
     </row>
     <row r="2048">
       <c r="A2048" s="9" t="n"/>
-      <c r="B2048" t="n">
+      <c r="B2048" s="0" t="n">
         <v>444</v>
       </c>
-      <c r="C2048" t="inlineStr">
+      <c r="C2048" s="0" t="inlineStr">
         <is>
           <t>4, 38</t>
         </is>
       </c>
-      <c r="D2048" t="inlineStr">
+      <c r="D2048" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70455,15 +70455,15 @@
     </row>
     <row r="2072">
       <c r="A2072" s="9" t="n"/>
-      <c r="B2072" t="n">
+      <c r="B2072" s="0" t="n">
         <v>609</v>
       </c>
-      <c r="C2072" t="inlineStr">
+      <c r="C2072" s="0" t="inlineStr">
         <is>
           <t>14, 14</t>
         </is>
       </c>
-      <c r="D2072" t="inlineStr">
+      <c r="D2072" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70479,15 +70479,15 @@
     </row>
     <row r="2074">
       <c r="A2074" s="9" t="n"/>
-      <c r="B2074" t="n">
+      <c r="B2074" s="0" t="n">
         <v>610</v>
       </c>
-      <c r="C2074" t="inlineStr">
+      <c r="C2074" s="0" t="inlineStr">
         <is>
           <t>6, 7</t>
         </is>
       </c>
-      <c r="D2074" t="inlineStr">
+      <c r="D2074" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70503,15 +70503,15 @@
     </row>
     <row r="2076">
       <c r="A2076" s="9" t="n"/>
-      <c r="B2076" t="n">
+      <c r="B2076" s="0" t="n">
         <v>612</v>
       </c>
-      <c r="C2076" t="inlineStr">
+      <c r="C2076" s="0" t="inlineStr">
         <is>
           <t>5, 7</t>
         </is>
       </c>
-      <c r="D2076" t="inlineStr">
+      <c r="D2076" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70527,15 +70527,15 @@
     </row>
     <row r="2078">
       <c r="A2078" s="9" t="n"/>
-      <c r="B2078" t="n">
+      <c r="B2078" s="0" t="n">
         <v>613</v>
       </c>
-      <c r="C2078" t="inlineStr">
+      <c r="C2078" s="0" t="inlineStr">
         <is>
           <t>6, 5</t>
         </is>
       </c>
-      <c r="D2078" t="inlineStr">
+      <c r="D2078" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70551,15 +70551,15 @@
     </row>
     <row r="2080">
       <c r="A2080" s="9" t="n"/>
-      <c r="B2080" t="n">
+      <c r="B2080" s="0" t="n">
         <v>614</v>
       </c>
-      <c r="C2080" t="inlineStr">
+      <c r="C2080" s="0" t="inlineStr">
         <is>
           <t>10, 2</t>
         </is>
       </c>
-      <c r="D2080" t="inlineStr">
+      <c r="D2080" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70575,15 +70575,15 @@
     </row>
     <row r="2082">
       <c r="A2082" s="9" t="n"/>
-      <c r="B2082" t="n">
+      <c r="B2082" s="0" t="n">
         <v>615</v>
       </c>
-      <c r="C2082" t="inlineStr">
+      <c r="C2082" s="0" t="inlineStr">
         <is>
           <t>5, 5</t>
         </is>
       </c>
-      <c r="D2082" t="inlineStr">
+      <c r="D2082" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70599,15 +70599,15 @@
     </row>
     <row r="2084">
       <c r="A2084" s="9" t="n"/>
-      <c r="B2084" t="n">
+      <c r="B2084" s="0" t="n">
         <v>616</v>
       </c>
-      <c r="C2084" t="inlineStr">
+      <c r="C2084" s="0" t="inlineStr">
         <is>
           <t>6, 5</t>
         </is>
       </c>
-      <c r="D2084" t="inlineStr">
+      <c r="D2084" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70623,15 +70623,15 @@
     </row>
     <row r="2086">
       <c r="A2086" s="9" t="n"/>
-      <c r="B2086" t="n">
+      <c r="B2086" s="0" t="n">
         <v>617</v>
       </c>
-      <c r="C2086" t="inlineStr">
+      <c r="C2086" s="0" t="inlineStr">
         <is>
           <t>6, 6</t>
         </is>
       </c>
-      <c r="D2086" t="inlineStr">
+      <c r="D2086" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70647,15 +70647,15 @@
     </row>
     <row r="2088">
       <c r="A2088" s="9" t="n"/>
-      <c r="B2088" t="n">
+      <c r="B2088" s="0" t="n">
         <v>618</v>
       </c>
-      <c r="C2088" t="inlineStr">
+      <c r="C2088" s="0" t="inlineStr">
         <is>
           <t>10, 10</t>
         </is>
       </c>
-      <c r="D2088" t="inlineStr">
+      <c r="D2088" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70671,15 +70671,15 @@
     </row>
     <row r="2090">
       <c r="A2090" s="9" t="n"/>
-      <c r="B2090" t="n">
+      <c r="B2090" s="0" t="n">
         <v>619</v>
       </c>
-      <c r="C2090" t="inlineStr">
+      <c r="C2090" s="0" t="inlineStr">
         <is>
           <t>7, 7</t>
         </is>
       </c>
-      <c r="D2090" t="inlineStr">
+      <c r="D2090" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70695,15 +70695,15 @@
     </row>
     <row r="2092">
       <c r="A2092" s="9" t="n"/>
-      <c r="B2092" t="n">
+      <c r="B2092" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="C2092" t="inlineStr">
+      <c r="C2092" s="0" t="inlineStr">
         <is>
           <t>6, 8</t>
         </is>
       </c>
-      <c r="D2092" t="inlineStr">
+      <c r="D2092" s="0" t="inlineStr">
         <is>
           <t>RIGHT</t>
         </is>
@@ -70719,15 +70719,15 @@
     </row>
     <row r="2094">
       <c r="A2094" s="9" t="n"/>
-      <c r="B2094" t="n">
+      <c r="B2094" s="0" t="n">
         <v>620</v>
       </c>
-      <c r="C2094" t="inlineStr">
+      <c r="C2094" s="0" t="inlineStr">
         <is>
           <t>6, 4</t>
         </is>
       </c>
-      <c r="D2094" t="inlineStr">
+      <c r="D2094" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70743,15 +70743,15 @@
     </row>
     <row r="2096">
       <c r="A2096" s="9" t="n"/>
-      <c r="B2096" t="n">
+      <c r="B2096" s="0" t="n">
         <v>621</v>
       </c>
-      <c r="C2096" t="inlineStr">
+      <c r="C2096" s="0" t="inlineStr">
         <is>
           <t>6, 4</t>
         </is>
       </c>
-      <c r="D2096" t="inlineStr">
+      <c r="D2096" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70767,15 +70767,15 @@
     </row>
     <row r="2098">
       <c r="A2098" s="9" t="n"/>
-      <c r="B2098" t="n">
+      <c r="B2098" s="0" t="n">
         <v>623</v>
       </c>
-      <c r="C2098" t="inlineStr">
+      <c r="C2098" s="0" t="inlineStr">
         <is>
           <t>6, 4</t>
         </is>
       </c>
-      <c r="D2098" t="inlineStr">
+      <c r="D2098" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70791,15 +70791,15 @@
     </row>
     <row r="2100">
       <c r="A2100" s="9" t="n"/>
-      <c r="B2100" t="n">
+      <c r="B2100" s="0" t="n">
         <v>622</v>
       </c>
-      <c r="C2100" t="inlineStr">
+      <c r="C2100" s="0" t="inlineStr">
         <is>
           <t>62, 14</t>
         </is>
       </c>
-      <c r="D2100" t="inlineStr">
+      <c r="D2100" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70815,15 +70815,15 @@
     </row>
     <row r="2102">
       <c r="A2102" s="9" t="n"/>
-      <c r="B2102" t="n">
+      <c r="B2102" s="0" t="n">
         <v>624</v>
       </c>
-      <c r="C2102" t="inlineStr">
+      <c r="C2102" s="0" t="inlineStr">
         <is>
           <t>4, 4</t>
         </is>
       </c>
-      <c r="D2102" t="inlineStr">
+      <c r="D2102" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70839,15 +70839,15 @@
     </row>
     <row r="2104">
       <c r="A2104" s="9" t="n"/>
-      <c r="B2104" t="n">
+      <c r="B2104" s="0" t="n">
         <v>444</v>
       </c>
-      <c r="C2104" t="inlineStr">
+      <c r="C2104" s="0" t="inlineStr">
         <is>
           <t>3, 5</t>
         </is>
       </c>
-      <c r="D2104" t="inlineStr">
+      <c r="D2104" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70887,15 +70887,15 @@
     </row>
     <row r="2108">
       <c r="A2108" s="9" t="n"/>
-      <c r="B2108" t="n">
+      <c r="B2108" s="0" t="n">
         <v>227</v>
       </c>
-      <c r="C2108" t="inlineStr">
+      <c r="C2108" s="0" t="inlineStr">
         <is>
           <t>20, 0</t>
         </is>
       </c>
-      <c r="D2108" t="inlineStr">
+      <c r="D2108" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70911,15 +70911,15 @@
     </row>
     <row r="2110">
       <c r="A2110" s="9" t="n"/>
-      <c r="B2110" t="n">
+      <c r="B2110" s="0" t="n">
         <v>227</v>
       </c>
-      <c r="C2110" t="inlineStr">
+      <c r="C2110" s="0" t="inlineStr">
         <is>
           <t>20, 0</t>
         </is>
       </c>
-      <c r="D2110" t="inlineStr">
+      <c r="D2110" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70935,15 +70935,15 @@
     </row>
     <row r="2112">
       <c r="A2112" s="9" t="n"/>
-      <c r="B2112" t="n">
+      <c r="B2112" s="0" t="n">
         <v>227</v>
       </c>
-      <c r="C2112" t="inlineStr">
+      <c r="C2112" s="0" t="inlineStr">
         <is>
           <t>20, 0</t>
         </is>
       </c>
-      <c r="D2112" t="inlineStr">
+      <c r="D2112" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70959,15 +70959,15 @@
     </row>
     <row r="2114">
       <c r="A2114" s="9" t="n"/>
-      <c r="B2114" t="n">
+      <c r="B2114" s="0" t="n">
         <v>600</v>
       </c>
-      <c r="C2114" t="inlineStr">
+      <c r="C2114" s="0" t="inlineStr">
         <is>
           <t>7, 4</t>
         </is>
       </c>
-      <c r="D2114" t="inlineStr">
+      <c r="D2114" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70983,15 +70983,15 @@
     </row>
     <row r="2116">
       <c r="A2116" s="9" t="n"/>
-      <c r="B2116" t="n">
+      <c r="B2116" s="0" t="n">
         <v>458</v>
       </c>
-      <c r="C2116" t="inlineStr">
+      <c r="C2116" s="0" t="inlineStr">
         <is>
           <t>14, 9</t>
         </is>
       </c>
-      <c r="D2116" t="inlineStr">
+      <c r="D2116" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71007,15 +71007,15 @@
     </row>
     <row r="2118">
       <c r="A2118" s="9" t="n"/>
-      <c r="B2118" t="n">
+      <c r="B2118" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="C2118" t="inlineStr">
+      <c r="C2118" s="0" t="inlineStr">
         <is>
           <t>13, 10</t>
         </is>
       </c>
-      <c r="D2118" t="inlineStr">
+      <c r="D2118" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71031,15 +71031,15 @@
     </row>
     <row r="2120">
       <c r="A2120" s="9" t="n"/>
-      <c r="B2120" t="n">
+      <c r="B2120" s="0" t="n">
         <v>501</v>
       </c>
-      <c r="C2120" t="inlineStr">
+      <c r="C2120" s="0" t="inlineStr">
         <is>
           <t>13, 89</t>
         </is>
       </c>
-      <c r="D2120" t="inlineStr">
+      <c r="D2120" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71197,15 +71197,15 @@
     </row>
     <row r="2135">
       <c r="A2135" s="9" t="n"/>
-      <c r="B2135" t="n">
+      <c r="B2135" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="C2135" t="inlineStr">
+      <c r="C2135" s="0" t="inlineStr">
         <is>
           <t>37, 47</t>
         </is>
       </c>
-      <c r="D2135" t="inlineStr">
+      <c r="D2135" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71595,15 +71595,15 @@
     </row>
     <row r="2169">
       <c r="A2169" s="9" t="n"/>
-      <c r="B2169" t="n">
+      <c r="B2169" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2169" t="inlineStr">
+      <c r="C2169" s="0" t="inlineStr">
         <is>
           <t>25, 25</t>
         </is>
       </c>
-      <c r="D2169" t="inlineStr">
+      <c r="D2169" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71627,15 +71627,15 @@
     </row>
     <row r="2171">
       <c r="A2171" s="9" t="n"/>
-      <c r="B2171" t="n">
+      <c r="B2171" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2171" t="inlineStr">
+      <c r="C2171" s="0" t="inlineStr">
         <is>
           <t>25, 125</t>
         </is>
       </c>
-      <c r="D2171" t="inlineStr">
+      <c r="D2171" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71659,15 +71659,15 @@
     </row>
     <row r="2173">
       <c r="A2173" s="9" t="n"/>
-      <c r="B2173" t="n">
+      <c r="B2173" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2173" t="inlineStr">
+      <c r="C2173" s="0" t="inlineStr">
         <is>
           <t>75, 25</t>
         </is>
       </c>
-      <c r="D2173" t="inlineStr">
+      <c r="D2173" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71691,15 +71691,15 @@
     </row>
     <row r="2175">
       <c r="A2175" s="9" t="n"/>
-      <c r="B2175" t="n">
+      <c r="B2175" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2175" t="inlineStr">
+      <c r="C2175" s="0" t="inlineStr">
         <is>
           <t>75, 125</t>
         </is>
       </c>
-      <c r="D2175" t="inlineStr">
+      <c r="D2175" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71723,15 +71723,15 @@
     </row>
     <row r="2177">
       <c r="A2177" s="9" t="n"/>
-      <c r="B2177" t="n">
+      <c r="B2177" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2177" t="inlineStr">
+      <c r="C2177" s="0" t="inlineStr">
         <is>
           <t>125, 25</t>
         </is>
       </c>
-      <c r="D2177" t="inlineStr">
+      <c r="D2177" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71755,15 +71755,15 @@
     </row>
     <row r="2179">
       <c r="A2179" s="9" t="n"/>
-      <c r="B2179" t="n">
+      <c r="B2179" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2179" t="inlineStr">
+      <c r="C2179" s="0" t="inlineStr">
         <is>
           <t>125, 125</t>
         </is>
       </c>
-      <c r="D2179" t="inlineStr">
+      <c r="D2179" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71787,15 +71787,15 @@
     </row>
     <row r="2181">
       <c r="A2181" s="9" t="n"/>
-      <c r="B2181" t="n">
+      <c r="B2181" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2181" t="inlineStr">
+      <c r="C2181" s="0" t="inlineStr">
         <is>
           <t>175, 25</t>
         </is>
       </c>
-      <c r="D2181" t="inlineStr">
+      <c r="D2181" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71819,15 +71819,15 @@
     </row>
     <row r="2183">
       <c r="A2183" s="9" t="n"/>
-      <c r="B2183" t="n">
+      <c r="B2183" s="0" t="n">
         <v>338</v>
       </c>
-      <c r="C2183" t="inlineStr">
+      <c r="C2183" s="0" t="inlineStr">
         <is>
           <t>175, 125</t>
         </is>
       </c>
-      <c r="D2183" t="inlineStr">
+      <c r="D2183" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71888,15 +71888,15 @@
     </row>
     <row r="2188">
       <c r="A2188" s="9" t="n"/>
-      <c r="B2188" t="n">
+      <c r="B2188" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="C2188" t="inlineStr">
+      <c r="C2188" s="0" t="inlineStr">
         <is>
           <t>1, 4</t>
         </is>
       </c>
-      <c r="D2188" t="inlineStr">
+      <c r="D2188" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71920,15 +71920,15 @@
     </row>
     <row r="2190">
       <c r="A2190" s="9" t="n"/>
-      <c r="B2190" t="n">
+      <c r="B2190" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="C2190" t="inlineStr">
+      <c r="C2190" s="0" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
       </c>
-      <c r="D2190" t="inlineStr">
+      <c r="D2190" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72015,15 +72015,15 @@
     </row>
     <row r="2198">
       <c r="A2198" s="9" t="n"/>
-      <c r="B2198" t="n">
+      <c r="B2198" s="0" t="n">
         <v>481</v>
       </c>
-      <c r="C2198" t="inlineStr">
+      <c r="C2198" s="0" t="inlineStr">
         <is>
           <t>9, 6</t>
         </is>
       </c>
-      <c r="D2198" t="inlineStr">
+      <c r="D2198" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72039,15 +72039,15 @@
     </row>
     <row r="2200">
       <c r="A2200" s="9" t="n"/>
-      <c r="B2200" t="n">
+      <c r="B2200" s="0" t="n">
         <v>284</v>
       </c>
-      <c r="C2200" t="inlineStr">
+      <c r="C2200" s="0" t="inlineStr">
         <is>
           <t>2, 4</t>
         </is>
       </c>
-      <c r="D2200" t="inlineStr">
+      <c r="D2200" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72063,15 +72063,15 @@
     </row>
     <row r="2202">
       <c r="A2202" s="9" t="n"/>
-      <c r="B2202" t="n">
+      <c r="B2202" s="0" t="n">
         <v>281</v>
       </c>
-      <c r="C2202" t="inlineStr">
+      <c r="C2202" s="0" t="inlineStr">
         <is>
           <t>2, 4</t>
         </is>
       </c>
-      <c r="D2202" t="inlineStr">
+      <c r="D2202" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72156,15 +72156,15 @@
     </row>
     <row r="2210">
       <c r="A2210" s="9" t="n"/>
-      <c r="B2210" t="n">
+      <c r="B2210" s="0" t="n">
         <v>286</v>
       </c>
-      <c r="C2210" t="inlineStr">
+      <c r="C2210" s="0" t="inlineStr">
         <is>
           <t>14, 11</t>
         </is>
       </c>
-      <c r="D2210" t="inlineStr">
+      <c r="D2210" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72204,15 +72204,15 @@
     </row>
     <row r="2214">
       <c r="A2214" s="9" t="n"/>
-      <c r="B2214" t="n">
+      <c r="B2214" s="0" t="n">
         <v>64</v>
       </c>
-      <c r="C2214" t="inlineStr">
+      <c r="C2214" s="0" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="D2214" t="inlineStr">
+      <c r="D2214" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72331,15 +72331,15 @@
     </row>
     <row r="2225">
       <c r="A2225" s="9" t="n"/>
-      <c r="B2225" t="n">
+      <c r="B2225" s="0" t="n">
         <v>271</v>
       </c>
-      <c r="C2225" t="inlineStr">
+      <c r="C2225" s="0" t="inlineStr">
         <is>
           <t>6, 8</t>
         </is>
       </c>
-      <c r="D2225" t="inlineStr">
+      <c r="D2225" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72355,15 +72355,15 @@
     </row>
     <row r="2227">
       <c r="A2227" s="9" t="n"/>
-      <c r="B2227" t="n">
+      <c r="B2227" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="C2227" t="inlineStr">
+      <c r="C2227" s="0" t="inlineStr">
         <is>
           <t>5, 10</t>
         </is>
       </c>
-      <c r="D2227" t="inlineStr">
+      <c r="D2227" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72379,15 +72379,15 @@
     </row>
     <row r="2229">
       <c r="A2229" s="9" t="n"/>
-      <c r="B2229" t="n">
+      <c r="B2229" s="0" t="n">
         <v>368</v>
       </c>
-      <c r="C2229" t="inlineStr">
+      <c r="C2229" s="0" t="inlineStr">
         <is>
           <t>10, 8</t>
         </is>
       </c>
-      <c r="D2229" t="inlineStr">
+      <c r="D2229" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72403,15 +72403,15 @@
     </row>
     <row r="2231">
       <c r="A2231" s="9" t="n"/>
-      <c r="B2231" t="n">
+      <c r="B2231" s="0" t="n">
         <v>369</v>
       </c>
-      <c r="C2231" t="inlineStr">
+      <c r="C2231" s="0" t="inlineStr">
         <is>
           <t>45, 2</t>
         </is>
       </c>
-      <c r="D2231" t="inlineStr">
+      <c r="D2231" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72427,15 +72427,15 @@
     </row>
     <row r="2233">
       <c r="A2233" s="9" t="n"/>
-      <c r="B2233" t="n">
+      <c r="B2233" s="0" t="n">
         <v>371</v>
       </c>
-      <c r="C2233" t="inlineStr">
+      <c r="C2233" s="0" t="inlineStr">
         <is>
           <t>6, 3</t>
         </is>
       </c>
-      <c r="D2233" t="inlineStr">
+      <c r="D2233" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72480,15 +72480,15 @@
     </row>
     <row r="2237">
       <c r="A2237" s="9" t="n"/>
-      <c r="B2237" t="n">
+      <c r="B2237" s="0" t="n">
         <v>395</v>
       </c>
-      <c r="C2237" t="inlineStr">
+      <c r="C2237" s="0" t="inlineStr">
         <is>
           <t>83, 12</t>
         </is>
       </c>
-      <c r="D2237" t="inlineStr">
+      <c r="D2237" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72512,15 +72512,15 @@
     </row>
     <row r="2239">
       <c r="A2239" s="9" t="n"/>
-      <c r="B2239" t="n">
+      <c r="B2239" s="0" t="n">
         <v>397</v>
       </c>
-      <c r="C2239" t="inlineStr">
+      <c r="C2239" s="0" t="inlineStr">
         <is>
           <t>42, 15</t>
         </is>
       </c>
-      <c r="D2239" t="inlineStr">
+      <c r="D2239" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72536,15 +72536,15 @@
     </row>
     <row r="2241">
       <c r="A2241" s="9" t="n"/>
-      <c r="B2241" t="n">
+      <c r="B2241" s="0" t="n">
         <v>398</v>
       </c>
-      <c r="C2241" t="inlineStr">
+      <c r="C2241" s="0" t="inlineStr">
         <is>
           <t>24, 52</t>
         </is>
       </c>
-      <c r="D2241" t="inlineStr">
+      <c r="D2241" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72568,15 +72568,15 @@
     </row>
     <row r="2243">
       <c r="A2243" s="9" t="n"/>
-      <c r="B2243" t="n">
+      <c r="B2243" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="C2243" t="inlineStr">
+      <c r="C2243" s="0" t="inlineStr">
         <is>
           <t>9, 61</t>
         </is>
       </c>
-      <c r="D2243" t="inlineStr">
+      <c r="D2243" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72608,15 +72608,15 @@
     </row>
     <row r="2246">
       <c r="A2246" s="9" t="n"/>
-      <c r="B2246" t="n">
+      <c r="B2246" s="0" t="n">
         <v>405</v>
       </c>
-      <c r="C2246" t="inlineStr">
+      <c r="C2246" s="0" t="inlineStr">
         <is>
           <t>35, 5</t>
         </is>
       </c>
-      <c r="D2246" t="inlineStr">
+      <c r="D2246" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72861,365 +72861,365 @@
       </c>
     </row>
     <row r="2269">
-      <c r="A2269" t="n">
+      <c r="A2269" s="0" t="n">
         <v>1912</v>
       </c>
     </row>
     <row r="2270">
-      <c r="B2270" t="n">
+      <c r="B2270" s="0" t="n">
         <v>147</v>
       </c>
-      <c r="C2270" t="inlineStr">
+      <c r="C2270" s="0" t="inlineStr">
         <is>
           <t>9, 7</t>
         </is>
       </c>
-      <c r="D2270" t="inlineStr">
+      <c r="D2270" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2271">
-      <c r="A2271" t="n">
+      <c r="A2271" s="0" t="n">
         <v>1696</v>
       </c>
     </row>
     <row r="2272">
-      <c r="B2272" t="n">
+      <c r="B2272" s="0" t="n">
         <v>112</v>
       </c>
-      <c r="C2272" t="inlineStr">
+      <c r="C2272" s="0" t="inlineStr">
         <is>
           <t>10, 9</t>
         </is>
       </c>
-      <c r="D2272" t="inlineStr">
+      <c r="D2272" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2273">
-      <c r="A2273" t="n">
+      <c r="A2273" s="0" t="n">
         <v>1652</v>
       </c>
     </row>
     <row r="2274">
-      <c r="B2274" t="n">
+      <c r="B2274" s="0" t="n">
         <v>129</v>
       </c>
-      <c r="C2274" t="inlineStr">
+      <c r="C2274" s="0" t="inlineStr">
         <is>
           <t>10, 7</t>
         </is>
       </c>
-      <c r="D2274" t="inlineStr">
+      <c r="D2274" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2275">
-      <c r="B2275" t="n">
+      <c r="B2275" s="0" t="n">
         <v>132</v>
       </c>
-      <c r="C2275" t="inlineStr">
+      <c r="C2275" s="0" t="inlineStr">
         <is>
           <t>8, 7</t>
         </is>
       </c>
-      <c r="D2275" t="inlineStr">
+      <c r="D2275" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2276">
-      <c r="A2276" t="n">
+      <c r="A2276" s="0" t="n">
         <v>1653</v>
       </c>
     </row>
     <row r="2277">
-      <c r="B2277" t="n">
+      <c r="B2277" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="C2277" t="inlineStr">
+      <c r="C2277" s="0" t="inlineStr">
         <is>
           <t>7, 7</t>
         </is>
       </c>
-      <c r="D2277" t="inlineStr">
+      <c r="D2277" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2278">
-      <c r="A2278" t="n">
+      <c r="A2278" s="0" t="n">
         <v>1685</v>
       </c>
     </row>
     <row r="2279">
-      <c r="B2279" t="n">
+      <c r="B2279" s="0" t="n">
         <v>272</v>
       </c>
-      <c r="C2279" t="inlineStr">
+      <c r="C2279" s="0" t="inlineStr">
         <is>
           <t>8, 6</t>
         </is>
       </c>
-      <c r="D2279" t="inlineStr">
+      <c r="D2279" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2280">
-      <c r="A2280" t="n">
+      <c r="A2280" s="0" t="n">
         <v>1674</v>
       </c>
     </row>
     <row r="2281">
-      <c r="B2281" t="n">
+      <c r="B2281" s="0" t="n">
         <v>131</v>
       </c>
-      <c r="C2281" t="inlineStr">
+      <c r="C2281" s="0" t="inlineStr">
         <is>
           <t>10, 7</t>
         </is>
       </c>
-      <c r="D2281" t="inlineStr">
+      <c r="D2281" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2282">
-      <c r="A2282" t="n">
+      <c r="A2282" s="0" t="n">
         <v>1702</v>
       </c>
     </row>
     <row r="2283">
-      <c r="B2283" t="n">
+      <c r="B2283" s="0" t="n">
         <v>129</v>
       </c>
-      <c r="C2283" t="inlineStr">
+      <c r="C2283" s="0" t="inlineStr">
         <is>
           <t>10, 7</t>
         </is>
       </c>
-      <c r="D2283" t="inlineStr">
+      <c r="D2283" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2284">
-      <c r="B2284" t="n">
+      <c r="B2284" s="0" t="n">
         <v>132</v>
       </c>
-      <c r="C2284" t="inlineStr">
+      <c r="C2284" s="0" t="inlineStr">
         <is>
           <t>8, 7</t>
         </is>
       </c>
-      <c r="D2284" t="inlineStr">
+      <c r="D2284" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2285">
-      <c r="A2285" t="n">
+      <c r="A2285" s="0" t="n">
         <v>1703</v>
       </c>
     </row>
     <row r="2286">
-      <c r="B2286" t="n">
+      <c r="B2286" s="0" t="n">
         <v>130</v>
       </c>
-      <c r="C2286" t="inlineStr">
+      <c r="C2286" s="0" t="inlineStr">
         <is>
           <t>7, 7</t>
         </is>
       </c>
-      <c r="D2286" t="inlineStr">
+      <c r="D2286" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2287">
-      <c r="A2287" t="n">
+      <c r="A2287" s="0" t="n">
         <v>1725</v>
       </c>
     </row>
     <row r="2288">
-      <c r="B2288" t="n">
+      <c r="B2288" s="0" t="n">
         <v>272</v>
       </c>
-      <c r="C2288" t="inlineStr">
+      <c r="C2288" s="0" t="inlineStr">
         <is>
           <t>8, 6</t>
         </is>
       </c>
-      <c r="D2288" t="inlineStr">
+      <c r="D2288" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2289">
-      <c r="A2289" t="n">
+      <c r="A2289" s="0" t="n">
         <v>1724</v>
       </c>
     </row>
     <row r="2290">
-      <c r="B2290" t="n">
+      <c r="B2290" s="0" t="n">
         <v>131</v>
       </c>
-      <c r="C2290" t="inlineStr">
+      <c r="C2290" s="0" t="inlineStr">
         <is>
           <t>10, 7</t>
         </is>
       </c>
-      <c r="D2290" t="inlineStr">
+      <c r="D2290" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2291">
-      <c r="A2291" t="n">
+      <c r="A2291" s="0" t="n">
         <v>1998</v>
       </c>
     </row>
     <row r="2292">
-      <c r="B2292" t="n">
+      <c r="B2292" s="0" t="n">
         <v>625</v>
       </c>
-      <c r="C2292" t="inlineStr">
+      <c r="C2292" s="0" t="inlineStr">
         <is>
           <t>14, 19</t>
         </is>
       </c>
-      <c r="D2292" t="inlineStr">
+      <c r="D2292" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2293">
-      <c r="A2293" t="n">
+      <c r="A2293" s="0" t="n">
         <v>2001</v>
       </c>
     </row>
     <row r="2294">
-      <c r="B2294" t="n">
+      <c r="B2294" s="0" t="n">
         <v>625</v>
       </c>
-      <c r="C2294" t="inlineStr">
+      <c r="C2294" s="0" t="inlineStr">
         <is>
           <t>14, 19</t>
         </is>
       </c>
-      <c r="D2294" t="inlineStr">
+      <c r="D2294" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2295">
-      <c r="A2295" t="n">
+      <c r="A2295" s="0" t="n">
         <v>2042</v>
       </c>
     </row>
     <row r="2296">
-      <c r="B2296" t="n">
+      <c r="B2296" s="0" t="n">
         <v>625</v>
       </c>
-      <c r="C2296" t="inlineStr">
+      <c r="C2296" s="0" t="inlineStr">
         <is>
           <t>14, 19</t>
         </is>
       </c>
-      <c r="D2296" t="inlineStr">
+      <c r="D2296" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2297">
-      <c r="A2297" t="n">
+      <c r="A2297" s="0" t="n">
         <v>2004</v>
       </c>
     </row>
     <row r="2298">
-      <c r="B2298" t="n">
+      <c r="B2298" s="0" t="n">
         <v>625</v>
       </c>
-      <c r="C2298" t="inlineStr">
+      <c r="C2298" s="0" t="inlineStr">
         <is>
           <t>14, 19</t>
         </is>
       </c>
-      <c r="D2298" t="inlineStr">
+      <c r="D2298" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2299">
-      <c r="A2299" t="n">
+      <c r="A2299" s="0" t="n">
         <v>46011</v>
       </c>
     </row>
     <row r="2300">
-      <c r="B2300" t="n">
+      <c r="B2300" s="0" t="n">
         <v>608</v>
       </c>
-      <c r="C2300" t="inlineStr">
+      <c r="C2300" s="0" t="inlineStr">
         <is>
           <t>15, 8</t>
         </is>
       </c>
-      <c r="D2300" t="inlineStr">
+      <c r="D2300" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2301">
-      <c r="B2301" t="n">
+      <c r="B2301" s="0" t="n">
         <v>609</v>
       </c>
-      <c r="C2301" t="inlineStr">
+      <c r="C2301" s="0" t="inlineStr">
         <is>
           <t>14, 14</t>
         </is>
       </c>
-      <c r="D2301" t="inlineStr">
+      <c r="D2301" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2302">
-      <c r="A2302" t="n">
+      <c r="A2302" s="0" t="n">
         <v>6517</v>
       </c>
     </row>
     <row r="2303">
-      <c r="B2303" t="n">
+      <c r="B2303" s="0" t="n">
         <v>64</v>
       </c>
-      <c r="C2303" t="inlineStr">
+      <c r="C2303" s="0" t="inlineStr">
         <is>
           <t>3, 4</t>
         </is>
       </c>
-      <c r="D2303" t="inlineStr">
+      <c r="D2303" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -73237,7 +73237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="5"/>
@@ -73281,24 +73281,455 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="A4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>혼잣말1</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>여기는 초보자사냥터입니다.초보자에게 적합한 던전으로,1 레벨부터 10 레벨까지 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>혼잣말2</t>
+      <c r="A6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>여기는 쥐굴입니다. 초보자에게 적합한 던전으로,5 레벨부터 10 레벨까지 사냥하기에 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>여기는 사슴굴입니다. 10 레벨부터 25 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>여기는 돼지굴입니다. 30 레벨부터 45 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>여기는 곰굴입니다. 20 레벨부터 40 레벨까지 사냥하기에 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>여기는 여우굴입니다. 30 레벨부터 45 레벨까지 사냥하기에 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>여기는 인형굴입니다. 60 레벨부터 80 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>여기는 해골굴입니다. 60 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>여기는 유령굴입니다. 60 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>여기는 흑해골굴입니다. 65 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>여기는 흑령굴입니다. 65 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>여기는 사마귀굴입니다. 55 레벨부터 70 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>여기는 전갈굴입니다. 55 레벨부터 70 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>여기는 백륜동입니다. 80 레벨부터 99 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>여기는 물망동입니다. 80 레벨부터 99 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>여기는 흉가입니다. 95 레벨부터 99 레벨 이상 고레벨이 사냥하기에 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>여기는 자호굴입니다. 40 레벨부터 60 레벨까지 사냥하기에좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>여기는 비밀세작의 집입니다.85 레벨부터 99 레벨 이상 고레벨이 사냥하기에 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>땅에 떨어져서 흙이 묻은 얼음을 씻어드립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>깨끗한 얼음이 있어야 화채를 만드실 수 있답니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>말하는 방법을 모르신다구요? 그러면 저를 클릭해 보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>단계를 모두 완료하시면 경험치를 드리고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>홈페이지가 어딘지 궁금하다면...? F2키를...</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>저는 수련방법을 알려드리는 사냥도우미라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>저 넓은 세계 어딘가에는 많은 사람들이 있다고 하던데...</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>제가 드린 퀘스트를 완료하시면 약간의 경험치를 드립니다...</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>바람의나라에 대해 잘 모르신다구요? 그럼 저 똘똘이 도우미가 알려드리겠습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>열심히 공부한 학생에게는 약간의 상이 있을지도 없을지도?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>언제나 탐구하는 자세를 가지고 정진하시길 바랍니다...</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>안녕하세요? 저를 클릭 해 보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>안녕하세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>세상에는 너무나 많은 아이템이 존재합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>적절한 아이템을 쓰는 것이 곧 고수가 되는 길...</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>말하기는 [ENTER]키를 누르시면 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>직업 선생님들은 도토리와 토끼고기를 좋아하시는 것 같던데...</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>님이 하고싶은 직업은 남들도 하고싶어요. 그러니 도사를 하는게 어떠세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>도사가 없는게 아니고,님이 도사를 안한거에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>상대방의 체력이 너무 높다고...? 그러면 방어력을 낮추면 되지...</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>방어력을 낮추는 마법은 저주와 혼마술이 있지...</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>방어력무시라는 특수한 각인이 있는데,이건 비밀이니 조용히 해야돼요...</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>부여성에 오신걸 환영합니다~</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>반갑습니다. 제 이름은 률이라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>F2를 눌러 메일주소를 등록해 주시기 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>저 넓은 세계에는 무엇이 있을까요...</t>
         </is>
       </c>
     </row>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -40320,7 +40320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2303"/>
+  <dimension ref="A1:D2301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="2"/>
@@ -66243,7 +66243,7 @@
     </row>
     <row r="1729">
       <c r="A1729" s="4" t="n">
-        <v>10946</v>
+        <v>10954</v>
       </c>
       <c r="B1729" s="4" t="n"/>
       <c r="C1729" s="4" t="n"/>
@@ -66252,11 +66252,11 @@
     <row r="1730">
       <c r="A1730" s="4" t="n"/>
       <c r="B1730" s="4" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C1730" s="4" t="inlineStr">
         <is>
-          <t>1, 1</t>
+          <t>12, 6</t>
         </is>
       </c>
       <c r="D1730" s="4" t="inlineStr">
@@ -66267,7 +66267,7 @@
     </row>
     <row r="1731">
       <c r="A1731" s="4" t="n">
-        <v>10954</v>
+        <v>10957</v>
       </c>
       <c r="B1731" s="4" t="n"/>
       <c r="C1731" s="4" t="n"/>
@@ -66276,11 +66276,11 @@
     <row r="1732">
       <c r="A1732" s="4" t="n"/>
       <c r="B1732" s="4" t="n">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="C1732" s="4" t="inlineStr">
         <is>
-          <t>12, 6</t>
+          <t>50, 0</t>
         </is>
       </c>
       <c r="D1732" s="4" t="inlineStr">
@@ -66291,7 +66291,7 @@
     </row>
     <row r="1733">
       <c r="A1733" s="4" t="n">
-        <v>10957</v>
+        <v>10960</v>
       </c>
       <c r="B1733" s="4" t="n"/>
       <c r="C1733" s="4" t="n"/>
@@ -66300,11 +66300,11 @@
     <row r="1734">
       <c r="A1734" s="4" t="n"/>
       <c r="B1734" s="4" t="n">
-        <v>227</v>
+        <v>558</v>
       </c>
       <c r="C1734" s="4" t="inlineStr">
         <is>
-          <t>50, 0</t>
+          <t>10, 3</t>
         </is>
       </c>
       <c r="D1734" s="4" t="inlineStr">
@@ -66314,37 +66314,37 @@
       </c>
     </row>
     <row r="1735">
-      <c r="A1735" s="4" t="n">
-        <v>10960</v>
-      </c>
-      <c r="B1735" s="4" t="n"/>
-      <c r="C1735" s="4" t="n"/>
-      <c r="D1735" s="4" t="n"/>
+      <c r="A1735" s="4" t="n"/>
+      <c r="B1735" s="4" t="n">
+        <v>559</v>
+      </c>
+      <c r="C1735" s="4" t="inlineStr">
+        <is>
+          <t>9, 3</t>
+        </is>
+      </c>
+      <c r="D1735" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1736">
-      <c r="A1736" s="4" t="n"/>
-      <c r="B1736" s="4" t="n">
-        <v>558</v>
-      </c>
-      <c r="C1736" s="4" t="inlineStr">
-        <is>
-          <t>10, 3</t>
-        </is>
-      </c>
-      <c r="D1736" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1736" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="B1736" s="4" t="n"/>
+      <c r="C1736" s="4" t="n"/>
+      <c r="D1736" s="4" t="n"/>
     </row>
     <row r="1737">
       <c r="A1737" s="4" t="n"/>
       <c r="B1737" s="4" t="n">
-        <v>559</v>
+        <v>460</v>
       </c>
       <c r="C1737" s="4" t="inlineStr">
         <is>
-          <t>9, 3</t>
+          <t>13, 13</t>
         </is>
       </c>
       <c r="D1737" s="4" t="inlineStr">
@@ -66355,7 +66355,7 @@
     </row>
     <row r="1738">
       <c r="A1738" s="4" t="n">
-        <v>11000</v>
+        <v>11001</v>
       </c>
       <c r="B1738" s="4" t="n"/>
       <c r="C1738" s="4" t="n"/>
@@ -66364,11 +66364,11 @@
     <row r="1739">
       <c r="A1739" s="4" t="n"/>
       <c r="B1739" s="4" t="n">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C1739" s="4" t="inlineStr">
         <is>
-          <t>13, 13</t>
+          <t>19, 11</t>
         </is>
       </c>
       <c r="D1739" s="4" t="inlineStr">
@@ -66379,7 +66379,7 @@
     </row>
     <row r="1740">
       <c r="A1740" s="4" t="n">
-        <v>11001</v>
+        <v>11002</v>
       </c>
       <c r="B1740" s="4" t="n"/>
       <c r="C1740" s="4" t="n"/>
@@ -66388,11 +66388,11 @@
     <row r="1741">
       <c r="A1741" s="4" t="n"/>
       <c r="B1741" s="4" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C1741" s="4" t="inlineStr">
         <is>
-          <t>19, 11</t>
+          <t>19, 13</t>
         </is>
       </c>
       <c r="D1741" s="4" t="inlineStr">
@@ -66403,7 +66403,7 @@
     </row>
     <row r="1742">
       <c r="A1742" s="4" t="n">
-        <v>11002</v>
+        <v>11003</v>
       </c>
       <c r="B1742" s="4" t="n"/>
       <c r="C1742" s="4" t="n"/>
@@ -66412,11 +66412,11 @@
     <row r="1743">
       <c r="A1743" s="4" t="n"/>
       <c r="B1743" s="4" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C1743" s="4" t="inlineStr">
         <is>
-          <t>19, 13</t>
+          <t>14, 4</t>
         </is>
       </c>
       <c r="D1743" s="4" t="inlineStr">
@@ -66427,7 +66427,7 @@
     </row>
     <row r="1744">
       <c r="A1744" s="4" t="n">
-        <v>11003</v>
+        <v>11004</v>
       </c>
       <c r="B1744" s="4" t="n"/>
       <c r="C1744" s="4" t="n"/>
@@ -66436,11 +66436,11 @@
     <row r="1745">
       <c r="A1745" s="4" t="n"/>
       <c r="B1745" s="4" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C1745" s="4" t="inlineStr">
         <is>
-          <t>14, 4</t>
+          <t>20, 13</t>
         </is>
       </c>
       <c r="D1745" s="4" t="inlineStr">
@@ -66451,7 +66451,7 @@
     </row>
     <row r="1746">
       <c r="A1746" s="4" t="n">
-        <v>11004</v>
+        <v>11005</v>
       </c>
       <c r="B1746" s="4" t="n"/>
       <c r="C1746" s="4" t="n"/>
@@ -66464,7 +66464,7 @@
       </c>
       <c r="C1747" s="4" t="inlineStr">
         <is>
-          <t>20, 13</t>
+          <t>14, 16</t>
         </is>
       </c>
       <c r="D1747" s="4" t="inlineStr">
@@ -66475,7 +66475,7 @@
     </row>
     <row r="1748">
       <c r="A1748" s="4" t="n">
-        <v>11005</v>
+        <v>11006</v>
       </c>
       <c r="B1748" s="4" t="n"/>
       <c r="C1748" s="4" t="n"/>
@@ -66499,7 +66499,7 @@
     </row>
     <row r="1750">
       <c r="A1750" s="4" t="n">
-        <v>11006</v>
+        <v>11007</v>
       </c>
       <c r="B1750" s="4" t="n"/>
       <c r="C1750" s="4" t="n"/>
@@ -66523,7 +66523,7 @@
     </row>
     <row r="1752">
       <c r="A1752" s="4" t="n">
-        <v>11007</v>
+        <v>11008</v>
       </c>
       <c r="B1752" s="4" t="n"/>
       <c r="C1752" s="4" t="n"/>
@@ -66547,7 +66547,7 @@
     </row>
     <row r="1754">
       <c r="A1754" s="4" t="n">
-        <v>11008</v>
+        <v>11010</v>
       </c>
       <c r="B1754" s="4" t="n"/>
       <c r="C1754" s="4" t="n"/>
@@ -66556,11 +66556,11 @@
     <row r="1755">
       <c r="A1755" s="4" t="n"/>
       <c r="B1755" s="4" t="n">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C1755" s="4" t="inlineStr">
         <is>
-          <t>14, 16</t>
+          <t>15, 6</t>
         </is>
       </c>
       <c r="D1755" s="4" t="inlineStr">
@@ -66570,37 +66570,37 @@
       </c>
     </row>
     <row r="1756">
-      <c r="A1756" s="4" t="n">
-        <v>11010</v>
-      </c>
-      <c r="B1756" s="4" t="n"/>
-      <c r="C1756" s="4" t="n"/>
-      <c r="D1756" s="4" t="n"/>
+      <c r="A1756" s="4" t="n"/>
+      <c r="B1756" s="4" t="n">
+        <v>447</v>
+      </c>
+      <c r="C1756" s="4" t="inlineStr">
+        <is>
+          <t>16, 9</t>
+        </is>
+      </c>
+      <c r="D1756" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1757">
-      <c r="A1757" s="4" t="n"/>
-      <c r="B1757" s="4" t="n">
-        <v>459</v>
-      </c>
-      <c r="C1757" s="4" t="inlineStr">
-        <is>
-          <t>15, 6</t>
-        </is>
-      </c>
-      <c r="D1757" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1757" s="4" t="n">
+        <v>11012</v>
+      </c>
+      <c r="B1757" s="4" t="n"/>
+      <c r="C1757" s="4" t="n"/>
+      <c r="D1757" s="4" t="n"/>
     </row>
     <row r="1758">
       <c r="A1758" s="4" t="n"/>
       <c r="B1758" s="4" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C1758" s="4" t="inlineStr">
         <is>
-          <t>16, 9</t>
+          <t>8, 8</t>
         </is>
       </c>
       <c r="D1758" s="4" t="inlineStr">
@@ -66610,21 +66610,29 @@
       </c>
     </row>
     <row r="1759">
-      <c r="A1759" s="4" t="n">
-        <v>11012</v>
-      </c>
-      <c r="B1759" s="4" t="n"/>
-      <c r="C1759" s="4" t="n"/>
-      <c r="D1759" s="4" t="n"/>
+      <c r="A1759" s="4" t="n"/>
+      <c r="B1759" s="4" t="n">
+        <v>453</v>
+      </c>
+      <c r="C1759" s="4" t="inlineStr">
+        <is>
+          <t>8, 24</t>
+        </is>
+      </c>
+      <c r="D1759" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1760">
       <c r="A1760" s="4" t="n"/>
       <c r="B1760" s="4" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C1760" s="4" t="inlineStr">
         <is>
-          <t>8, 8</t>
+          <t>24, 8</t>
         </is>
       </c>
       <c r="D1760" s="4" t="inlineStr">
@@ -66636,11 +66644,11 @@
     <row r="1761">
       <c r="A1761" s="4" t="n"/>
       <c r="B1761" s="4" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C1761" s="4" t="inlineStr">
         <is>
-          <t>8, 24</t>
+          <t>24, 24</t>
         </is>
       </c>
       <c r="D1761" s="4" t="inlineStr">
@@ -66650,29 +66658,21 @@
       </c>
     </row>
     <row r="1762">
-      <c r="A1762" s="4" t="n"/>
-      <c r="B1762" s="4" t="n">
-        <v>454</v>
-      </c>
-      <c r="C1762" s="4" t="inlineStr">
-        <is>
-          <t>24, 8</t>
-        </is>
-      </c>
-      <c r="D1762" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1762" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="B1762" s="4" t="n"/>
+      <c r="C1762" s="4" t="n"/>
+      <c r="D1762" s="4" t="n"/>
     </row>
     <row r="1763">
       <c r="A1763" s="4" t="n"/>
       <c r="B1763" s="4" t="n">
-        <v>455</v>
+        <v>290</v>
       </c>
       <c r="C1763" s="4" t="inlineStr">
         <is>
-          <t>24, 24</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D1763" s="4" t="inlineStr">
@@ -66682,37 +66682,37 @@
       </c>
     </row>
     <row r="1764">
-      <c r="A1764" s="4" t="n">
-        <v>11500</v>
-      </c>
-      <c r="B1764" s="4" t="n"/>
-      <c r="C1764" s="4" t="n"/>
-      <c r="D1764" s="4" t="n"/>
+      <c r="A1764" s="4" t="n"/>
+      <c r="B1764" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="C1764" s="4" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
+      </c>
+      <c r="D1764" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1765">
-      <c r="A1765" s="4" t="n"/>
-      <c r="B1765" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="C1765" s="4" t="inlineStr">
-        <is>
-          <t>3, 4</t>
-        </is>
-      </c>
-      <c r="D1765" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1765" s="4" t="n">
+        <v>11503</v>
+      </c>
+      <c r="B1765" s="4" t="n"/>
+      <c r="C1765" s="4" t="n"/>
+      <c r="D1765" s="4" t="n"/>
     </row>
     <row r="1766">
       <c r="A1766" s="4" t="n"/>
       <c r="B1766" s="4" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C1766" s="4" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D1766" s="4" t="inlineStr">
@@ -66723,7 +66723,7 @@
     </row>
     <row r="1767">
       <c r="A1767" s="4" t="n">
-        <v>11503</v>
+        <v>11504</v>
       </c>
       <c r="B1767" s="4" t="n"/>
       <c r="C1767" s="4" t="n"/>
@@ -66732,11 +66732,11 @@
     <row r="1768">
       <c r="A1768" s="4" t="n"/>
       <c r="B1768" s="4" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C1768" s="4" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>2, 4</t>
         </is>
       </c>
       <c r="D1768" s="4" t="inlineStr">
@@ -66747,7 +66747,7 @@
     </row>
     <row r="1769">
       <c r="A1769" s="4" t="n">
-        <v>11504</v>
+        <v>11508</v>
       </c>
       <c r="B1769" s="4" t="n"/>
       <c r="C1769" s="4" t="n"/>
@@ -66756,11 +66756,11 @@
     <row r="1770">
       <c r="A1770" s="4" t="n"/>
       <c r="B1770" s="4" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C1770" s="4" t="inlineStr">
         <is>
-          <t>2, 4</t>
+          <t>14, 11</t>
         </is>
       </c>
       <c r="D1770" s="4" t="inlineStr">
@@ -66771,7 +66771,7 @@
     </row>
     <row r="1771">
       <c r="A1771" s="4" t="n">
-        <v>11508</v>
+        <v>11509</v>
       </c>
       <c r="B1771" s="4" t="n"/>
       <c r="C1771" s="4" t="n"/>
@@ -66780,7 +66780,7 @@
     <row r="1772">
       <c r="A1772" s="4" t="n"/>
       <c r="B1772" s="4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C1772" s="4" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
     </row>
     <row r="1773">
       <c r="A1773" s="4" t="n">
-        <v>11509</v>
+        <v>11510</v>
       </c>
       <c r="B1773" s="4" t="n"/>
       <c r="C1773" s="4" t="n"/>
@@ -66804,7 +66804,7 @@
     <row r="1774">
       <c r="A1774" s="4" t="n"/>
       <c r="B1774" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1774" s="4" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
     </row>
     <row r="1775">
       <c r="A1775" s="4" t="n">
-        <v>11510</v>
+        <v>11511</v>
       </c>
       <c r="B1775" s="4" t="n"/>
       <c r="C1775" s="4" t="n"/>
@@ -66828,7 +66828,7 @@
     <row r="1776">
       <c r="A1776" s="4" t="n"/>
       <c r="B1776" s="4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C1776" s="4" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
     </row>
     <row r="1777">
       <c r="A1777" s="4" t="n">
-        <v>11511</v>
+        <v>11512</v>
       </c>
       <c r="B1777" s="4" t="n"/>
       <c r="C1777" s="4" t="n"/>
@@ -66852,7 +66852,7 @@
     <row r="1778">
       <c r="A1778" s="4" t="n"/>
       <c r="B1778" s="4" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C1778" s="4" t="inlineStr">
         <is>
@@ -66867,7 +66867,7 @@
     </row>
     <row r="1779">
       <c r="A1779" s="4" t="n">
-        <v>11512</v>
+        <v>11519</v>
       </c>
       <c r="B1779" s="4" t="n"/>
       <c r="C1779" s="4" t="n"/>
@@ -66876,11 +66876,11 @@
     <row r="1780">
       <c r="A1780" s="4" t="n"/>
       <c r="B1780" s="4" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C1780" s="4" t="inlineStr">
         <is>
-          <t>14, 11</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D1780" s="4" t="inlineStr">
@@ -66891,7 +66891,7 @@
     </row>
     <row r="1781">
       <c r="A1781" s="4" t="n">
-        <v>11519</v>
+        <v>11520</v>
       </c>
       <c r="B1781" s="4" t="n"/>
       <c r="C1781" s="4" t="n"/>
@@ -66900,7 +66900,7 @@
     <row r="1782">
       <c r="A1782" s="4" t="n"/>
       <c r="B1782" s="4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1782" s="4" t="inlineStr">
         <is>
@@ -66915,7 +66915,7 @@
     </row>
     <row r="1783">
       <c r="A1783" s="4" t="n">
-        <v>11520</v>
+        <v>11521</v>
       </c>
       <c r="B1783" s="4" t="n"/>
       <c r="C1783" s="4" t="n"/>
@@ -66924,11 +66924,11 @@
     <row r="1784">
       <c r="A1784" s="4" t="n"/>
       <c r="B1784" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C1784" s="4" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>10, 3</t>
         </is>
       </c>
       <c r="D1784" s="4" t="inlineStr">
@@ -66939,7 +66939,7 @@
     </row>
     <row r="1785">
       <c r="A1785" s="4" t="n">
-        <v>11521</v>
+        <v>11522</v>
       </c>
       <c r="B1785" s="4" t="n"/>
       <c r="C1785" s="4" t="n"/>
@@ -66948,11 +66948,11 @@
     <row r="1786">
       <c r="A1786" s="4" t="n"/>
       <c r="B1786" s="4" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C1786" s="4" t="inlineStr">
         <is>
-          <t>10, 3</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D1786" s="4" t="inlineStr">
@@ -66963,7 +66963,7 @@
     </row>
     <row r="1787">
       <c r="A1787" s="4" t="n">
-        <v>11522</v>
+        <v>11523</v>
       </c>
       <c r="B1787" s="4" t="n"/>
       <c r="C1787" s="4" t="n"/>
@@ -66972,7 +66972,7 @@
     <row r="1788">
       <c r="A1788" s="4" t="n"/>
       <c r="B1788" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C1788" s="4" t="inlineStr">
         <is>
@@ -66987,7 +66987,7 @@
     </row>
     <row r="1789">
       <c r="A1789" s="4" t="n">
-        <v>11523</v>
+        <v>11524</v>
       </c>
       <c r="B1789" s="4" t="n"/>
       <c r="C1789" s="4" t="n"/>
@@ -66996,11 +66996,11 @@
     <row r="1790">
       <c r="A1790" s="4" t="n"/>
       <c r="B1790" s="4" t="n">
-        <v>301</v>
+        <v>577</v>
       </c>
       <c r="C1790" s="4" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="D1790" s="4" t="inlineStr">
@@ -67011,7 +67011,7 @@
     </row>
     <row r="1791">
       <c r="A1791" s="4" t="n">
-        <v>11524</v>
+        <v>11525</v>
       </c>
       <c r="B1791" s="4" t="n"/>
       <c r="C1791" s="4" t="n"/>
@@ -67035,7 +67035,7 @@
     </row>
     <row r="1793">
       <c r="A1793" s="4" t="n">
-        <v>11525</v>
+        <v>11526</v>
       </c>
       <c r="B1793" s="4" t="n"/>
       <c r="C1793" s="4" t="n"/>
@@ -67059,7 +67059,7 @@
     </row>
     <row r="1795">
       <c r="A1795" s="4" t="n">
-        <v>11526</v>
+        <v>11531</v>
       </c>
       <c r="B1795" s="4" t="n"/>
       <c r="C1795" s="4" t="n"/>
@@ -67068,11 +67068,11 @@
     <row r="1796">
       <c r="A1796" s="4" t="n"/>
       <c r="B1796" s="4" t="n">
-        <v>577</v>
+        <v>296</v>
       </c>
       <c r="C1796" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>14, 11</t>
         </is>
       </c>
       <c r="D1796" s="4" t="inlineStr">
@@ -67083,7 +67083,7 @@
     </row>
     <row r="1797">
       <c r="A1797" s="4" t="n">
-        <v>11531</v>
+        <v>11700</v>
       </c>
       <c r="B1797" s="4" t="n"/>
       <c r="C1797" s="4" t="n"/>
@@ -67092,11 +67092,11 @@
     <row r="1798">
       <c r="A1798" s="4" t="n"/>
       <c r="B1798" s="4" t="n">
-        <v>296</v>
+        <v>444</v>
       </c>
       <c r="C1798" s="4" t="inlineStr">
         <is>
-          <t>14, 11</t>
+          <t>13, 13</t>
         </is>
       </c>
       <c r="D1798" s="4" t="inlineStr">
@@ -67107,7 +67107,7 @@
     </row>
     <row r="1799">
       <c r="A1799" s="4" t="n">
-        <v>11700</v>
+        <v>11720</v>
       </c>
       <c r="B1799" s="4" t="n"/>
       <c r="C1799" s="4" t="n"/>
@@ -67120,7 +67120,7 @@
       </c>
       <c r="C1800" s="4" t="inlineStr">
         <is>
-          <t>13, 13</t>
+          <t>14, 8</t>
         </is>
       </c>
       <c r="D1800" s="4" t="inlineStr">
@@ -67131,7 +67131,7 @@
     </row>
     <row r="1801">
       <c r="A1801" s="4" t="n">
-        <v>11720</v>
+        <v>11740</v>
       </c>
       <c r="B1801" s="4" t="n"/>
       <c r="C1801" s="4" t="n"/>
@@ -67144,7 +67144,7 @@
       </c>
       <c r="C1802" s="4" t="inlineStr">
         <is>
-          <t>14, 8</t>
+          <t>13, 17</t>
         </is>
       </c>
       <c r="D1802" s="4" t="inlineStr">
@@ -67155,7 +67155,7 @@
     </row>
     <row r="1803">
       <c r="A1803" s="4" t="n">
-        <v>11740</v>
+        <v>12000</v>
       </c>
       <c r="B1803" s="4" t="n"/>
       <c r="C1803" s="4" t="n"/>
@@ -67164,11 +67164,11 @@
     <row r="1804">
       <c r="A1804" s="4" t="n"/>
       <c r="B1804" s="4" t="n">
-        <v>444</v>
+        <v>569</v>
       </c>
       <c r="C1804" s="4" t="inlineStr">
         <is>
-          <t>13, 17</t>
+          <t>17, 10</t>
         </is>
       </c>
       <c r="D1804" s="4" t="inlineStr">
@@ -67179,7 +67179,7 @@
     </row>
     <row r="1805">
       <c r="A1805" s="4" t="n">
-        <v>12000</v>
+        <v>12010</v>
       </c>
       <c r="B1805" s="4" t="n"/>
       <c r="C1805" s="4" t="n"/>
@@ -67188,11 +67188,11 @@
     <row r="1806">
       <c r="A1806" s="4" t="n"/>
       <c r="B1806" s="4" t="n">
-        <v>569</v>
+        <v>491</v>
       </c>
       <c r="C1806" s="4" t="inlineStr">
         <is>
-          <t>17, 10</t>
+          <t>5, 4</t>
         </is>
       </c>
       <c r="D1806" s="4" t="inlineStr">
@@ -67202,21 +67202,29 @@
       </c>
     </row>
     <row r="1807">
-      <c r="A1807" s="4" t="n">
-        <v>12010</v>
-      </c>
-      <c r="B1807" s="4" t="n"/>
-      <c r="C1807" s="4" t="n"/>
-      <c r="D1807" s="4" t="n"/>
+      <c r="A1807" s="4" t="n"/>
+      <c r="B1807" s="4" t="n">
+        <v>492</v>
+      </c>
+      <c r="C1807" s="4" t="inlineStr">
+        <is>
+          <t>95, 4</t>
+        </is>
+      </c>
+      <c r="D1807" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1808">
       <c r="A1808" s="4" t="n"/>
       <c r="B1808" s="4" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C1808" s="4" t="inlineStr">
         <is>
-          <t>5, 4</t>
+          <t>95, 94</t>
         </is>
       </c>
       <c r="D1808" s="4" t="inlineStr">
@@ -67228,11 +67236,11 @@
     <row r="1809">
       <c r="A1809" s="4" t="n"/>
       <c r="B1809" s="4" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C1809" s="4" t="inlineStr">
         <is>
-          <t>95, 4</t>
+          <t>5, 94</t>
         </is>
       </c>
       <c r="D1809" s="4" t="inlineStr">
@@ -67244,11 +67252,11 @@
     <row r="1810">
       <c r="A1810" s="4" t="n"/>
       <c r="B1810" s="4" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C1810" s="4" t="inlineStr">
         <is>
-          <t>95, 94</t>
+          <t>50, 49</t>
         </is>
       </c>
       <c r="D1810" s="4" t="inlineStr">
@@ -67258,20 +67266,12 @@
       </c>
     </row>
     <row r="1811">
-      <c r="A1811" s="4" t="n"/>
-      <c r="B1811" s="4" t="n">
-        <v>494</v>
-      </c>
-      <c r="C1811" s="4" t="inlineStr">
-        <is>
-          <t>5, 94</t>
-        </is>
-      </c>
-      <c r="D1811" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1811" s="4" t="n">
+        <v>12016</v>
+      </c>
+      <c r="B1811" s="4" t="n"/>
+      <c r="C1811" s="4" t="n"/>
+      <c r="D1811" s="4" t="n"/>
     </row>
     <row r="1812">
       <c r="A1812" s="4" t="n"/>
@@ -67280,18 +67280,18 @@
       </c>
       <c r="C1812" s="4" t="inlineStr">
         <is>
-          <t>50, 49</t>
+          <t>243, 77</t>
         </is>
       </c>
       <c r="D1812" s="4" t="inlineStr">
         <is>
-          <t>BOTTOM</t>
+          <t>LEFT</t>
         </is>
       </c>
     </row>
     <row r="1813">
       <c r="A1813" s="4" t="n">
-        <v>12016</v>
+        <v>12017</v>
       </c>
       <c r="B1813" s="4" t="n"/>
       <c r="C1813" s="4" t="n"/>
@@ -67304,18 +67304,18 @@
       </c>
       <c r="C1814" s="4" t="inlineStr">
         <is>
-          <t>243, 77</t>
+          <t>7, 8</t>
         </is>
       </c>
       <c r="D1814" s="4" t="inlineStr">
         <is>
-          <t>LEFT</t>
+          <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="1815">
       <c r="A1815" s="4" t="n">
-        <v>12017</v>
+        <v>12188</v>
       </c>
       <c r="B1815" s="4" t="n"/>
       <c r="C1815" s="4" t="n"/>
@@ -67324,11 +67324,11 @@
     <row r="1816">
       <c r="A1816" s="4" t="n"/>
       <c r="B1816" s="4" t="n">
-        <v>495</v>
+        <v>176</v>
       </c>
       <c r="C1816" s="4" t="inlineStr">
         <is>
-          <t>7, 8</t>
+          <t>14, 10</t>
         </is>
       </c>
       <c r="D1816" s="4" t="inlineStr">
@@ -67339,7 +67339,7 @@
     </row>
     <row r="1817">
       <c r="A1817" s="4" t="n">
-        <v>12188</v>
+        <v>12248</v>
       </c>
       <c r="B1817" s="4" t="n"/>
       <c r="C1817" s="4" t="n"/>
@@ -67348,11 +67348,11 @@
     <row r="1818">
       <c r="A1818" s="4" t="n"/>
       <c r="B1818" s="4" t="n">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="C1818" s="4" t="inlineStr">
         <is>
-          <t>14, 10</t>
+          <t>9, 6</t>
         </is>
       </c>
       <c r="D1818" s="4" t="inlineStr">
@@ -67363,7 +67363,7 @@
     </row>
     <row r="1819">
       <c r="A1819" s="4" t="n">
-        <v>12248</v>
+        <v>12249</v>
       </c>
       <c r="B1819" s="4" t="n"/>
       <c r="C1819" s="4" t="n"/>
@@ -67372,11 +67372,11 @@
     <row r="1820">
       <c r="A1820" s="4" t="n"/>
       <c r="B1820" s="4" t="n">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C1820" s="4" t="inlineStr">
         <is>
-          <t>9, 6</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D1820" s="4" t="inlineStr">
@@ -67387,7 +67387,7 @@
     </row>
     <row r="1821">
       <c r="A1821" s="4" t="n">
-        <v>12249</v>
+        <v>12263</v>
       </c>
       <c r="B1821" s="4" t="n"/>
       <c r="C1821" s="4" t="n"/>
@@ -67396,11 +67396,11 @@
     <row r="1822">
       <c r="A1822" s="4" t="n"/>
       <c r="B1822" s="4" t="n">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C1822" s="4" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>9, 6</t>
         </is>
       </c>
       <c r="D1822" s="4" t="inlineStr">
@@ -67411,7 +67411,7 @@
     </row>
     <row r="1823">
       <c r="A1823" s="4" t="n">
-        <v>12263</v>
+        <v>12264</v>
       </c>
       <c r="B1823" s="4" t="n"/>
       <c r="C1823" s="4" t="n"/>
@@ -67420,11 +67420,11 @@
     <row r="1824">
       <c r="A1824" s="4" t="n"/>
       <c r="B1824" s="4" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C1824" s="4" t="inlineStr">
         <is>
-          <t>9, 6</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D1824" s="4" t="inlineStr">
@@ -67435,7 +67435,7 @@
     </row>
     <row r="1825">
       <c r="A1825" s="4" t="n">
-        <v>12264</v>
+        <v>12275</v>
       </c>
       <c r="B1825" s="4" t="n"/>
       <c r="C1825" s="4" t="n"/>
@@ -67444,11 +67444,11 @@
     <row r="1826">
       <c r="A1826" s="4" t="n"/>
       <c r="B1826" s="4" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C1826" s="4" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>9, 6</t>
         </is>
       </c>
       <c r="D1826" s="4" t="inlineStr">
@@ -67459,7 +67459,7 @@
     </row>
     <row r="1827">
       <c r="A1827" s="4" t="n">
-        <v>12275</v>
+        <v>12276</v>
       </c>
       <c r="B1827" s="4" t="n"/>
       <c r="C1827" s="4" t="n"/>
@@ -67468,11 +67468,11 @@
     <row r="1828">
       <c r="A1828" s="4" t="n"/>
       <c r="B1828" s="4" t="n">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C1828" s="4" t="inlineStr">
         <is>
-          <t>9, 6</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D1828" s="4" t="inlineStr">
@@ -67483,7 +67483,7 @@
     </row>
     <row r="1829">
       <c r="A1829" s="4" t="n">
-        <v>12276</v>
+        <v>12287</v>
       </c>
       <c r="B1829" s="4" t="n"/>
       <c r="C1829" s="4" t="n"/>
@@ -67492,11 +67492,11 @@
     <row r="1830">
       <c r="A1830" s="4" t="n"/>
       <c r="B1830" s="4" t="n">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C1830" s="4" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>9, 6</t>
         </is>
       </c>
       <c r="D1830" s="4" t="inlineStr">
@@ -67507,7 +67507,7 @@
     </row>
     <row r="1831">
       <c r="A1831" s="4" t="n">
-        <v>12287</v>
+        <v>12288</v>
       </c>
       <c r="B1831" s="4" t="n"/>
       <c r="C1831" s="4" t="n"/>
@@ -67516,11 +67516,11 @@
     <row r="1832">
       <c r="A1832" s="4" t="n"/>
       <c r="B1832" s="4" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C1832" s="4" t="inlineStr">
         <is>
-          <t>9, 6</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D1832" s="4" t="inlineStr">
@@ -67531,7 +67531,7 @@
     </row>
     <row r="1833">
       <c r="A1833" s="4" t="n">
-        <v>12288</v>
+        <v>126</v>
       </c>
       <c r="B1833" s="4" t="n"/>
       <c r="C1833" s="4" t="n"/>
@@ -67540,11 +67540,11 @@
     <row r="1834">
       <c r="A1834" s="4" t="n"/>
       <c r="B1834" s="4" t="n">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="C1834" s="4" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>12, 2</t>
         </is>
       </c>
       <c r="D1834" s="4" t="inlineStr">
@@ -67554,37 +67554,37 @@
       </c>
     </row>
     <row r="1835">
-      <c r="A1835" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="B1835" s="4" t="n"/>
-      <c r="C1835" s="4" t="n"/>
-      <c r="D1835" s="4" t="n"/>
+      <c r="A1835" s="4" t="n"/>
+      <c r="B1835" s="4" t="n">
+        <v>444</v>
+      </c>
+      <c r="C1835" s="4" t="inlineStr">
+        <is>
+          <t>198, 5</t>
+        </is>
+      </c>
+      <c r="D1835" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1836">
-      <c r="A1836" s="4" t="n"/>
-      <c r="B1836" s="4" t="n">
-        <v>499</v>
-      </c>
-      <c r="C1836" s="4" t="inlineStr">
-        <is>
-          <t>12, 2</t>
-        </is>
-      </c>
-      <c r="D1836" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1836" s="4" t="n">
+        <v>2544</v>
+      </c>
+      <c r="B1836" s="4" t="n"/>
+      <c r="C1836" s="4" t="n"/>
+      <c r="D1836" s="4" t="n"/>
     </row>
     <row r="1837">
       <c r="A1837" s="4" t="n"/>
       <c r="B1837" s="4" t="n">
-        <v>444</v>
+        <v>367</v>
       </c>
       <c r="C1837" s="4" t="inlineStr">
         <is>
-          <t>198, 5</t>
+          <t>5, 7</t>
         </is>
       </c>
       <c r="D1837" s="4" t="inlineStr">
@@ -67595,7 +67595,7 @@
     </row>
     <row r="1838">
       <c r="A1838" s="4" t="n">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="B1838" s="4" t="n"/>
       <c r="C1838" s="4" t="n"/>
@@ -67604,11 +67604,11 @@
     <row r="1839">
       <c r="A1839" s="4" t="n"/>
       <c r="B1839" s="4" t="n">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C1839" s="4" t="inlineStr">
         <is>
-          <t>5, 7</t>
+          <t>2, 4</t>
         </is>
       </c>
       <c r="D1839" s="4" t="inlineStr">
@@ -67618,21 +67618,29 @@
       </c>
     </row>
     <row r="1840">
-      <c r="A1840" s="4" t="n">
-        <v>2545</v>
-      </c>
-      <c r="B1840" s="4" t="n"/>
-      <c r="C1840" s="4" t="n"/>
-      <c r="D1840" s="4" t="n"/>
+      <c r="A1840" s="4" t="n"/>
+      <c r="B1840" s="4" t="n">
+        <v>393</v>
+      </c>
+      <c r="C1840" s="4" t="inlineStr">
+        <is>
+          <t>29, 4</t>
+        </is>
+      </c>
+      <c r="D1840" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1841">
       <c r="A1841" s="4" t="n"/>
       <c r="B1841" s="4" t="n">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="C1841" s="4" t="inlineStr">
         <is>
-          <t>2, 4</t>
+          <t>24, 16</t>
         </is>
       </c>
       <c r="D1841" s="4" t="inlineStr">
@@ -67642,29 +67650,21 @@
       </c>
     </row>
     <row r="1842">
-      <c r="A1842" s="4" t="n"/>
-      <c r="B1842" s="4" t="n">
-        <v>393</v>
-      </c>
-      <c r="C1842" s="4" t="inlineStr">
-        <is>
-          <t>29, 4</t>
-        </is>
-      </c>
-      <c r="D1842" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A1842" s="4" t="n">
+        <v>2720</v>
+      </c>
+      <c r="B1842" s="4" t="n"/>
+      <c r="C1842" s="4" t="n"/>
+      <c r="D1842" s="4" t="n"/>
     </row>
     <row r="1843">
       <c r="A1843" s="4" t="n"/>
       <c r="B1843" s="4" t="n">
-        <v>408</v>
+        <v>569</v>
       </c>
       <c r="C1843" s="4" t="inlineStr">
         <is>
-          <t>24, 16</t>
+          <t>10, 25</t>
         </is>
       </c>
       <c r="D1843" s="4" t="inlineStr">
@@ -67675,7 +67675,7 @@
     </row>
     <row r="1844">
       <c r="A1844" s="4" t="n">
-        <v>2720</v>
+        <v>2770</v>
       </c>
       <c r="B1844" s="4" t="n"/>
       <c r="C1844" s="4" t="n"/>
@@ -67684,7 +67684,7 @@
     <row r="1845">
       <c r="A1845" s="4" t="n"/>
       <c r="B1845" s="4" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C1845" s="4" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
     </row>
     <row r="1846">
       <c r="A1846" s="4" t="n">
-        <v>2770</v>
+        <v>2813</v>
       </c>
       <c r="B1846" s="4" t="n"/>
       <c r="C1846" s="4" t="n"/>
@@ -67708,22 +67708,22 @@
     <row r="1847">
       <c r="A1847" s="4" t="n"/>
       <c r="B1847" s="4" t="n">
-        <v>570</v>
+        <v>8</v>
       </c>
       <c r="C1847" s="4" t="inlineStr">
         <is>
-          <t>10, 25</t>
+          <t>6, 8</t>
         </is>
       </c>
       <c r="D1847" s="4" t="inlineStr">
         <is>
-          <t>BOTTOM</t>
+          <t>RIGHT</t>
         </is>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" s="4" t="n">
-        <v>2813</v>
+        <v>2814</v>
       </c>
       <c r="B1848" s="4" t="n"/>
       <c r="C1848" s="4" t="n"/>
@@ -67747,7 +67747,7 @@
     </row>
     <row r="1850">
       <c r="A1850" s="4" t="n">
-        <v>2814</v>
+        <v>2815</v>
       </c>
       <c r="B1850" s="4" t="n"/>
       <c r="C1850" s="4" t="n"/>
@@ -67771,7 +67771,7 @@
     </row>
     <row r="1852">
       <c r="A1852" s="4" t="n">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="B1852" s="4" t="n"/>
       <c r="C1852" s="4" t="n"/>
@@ -67795,7 +67795,7 @@
     </row>
     <row r="1854">
       <c r="A1854" s="4" t="n">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="B1854" s="4" t="n"/>
       <c r="C1854" s="4" t="n"/>
@@ -67819,7 +67819,7 @@
     </row>
     <row r="1856">
       <c r="A1856" s="4" t="n">
-        <v>2817</v>
+        <v>2818</v>
       </c>
       <c r="B1856" s="4" t="n"/>
       <c r="C1856" s="4" t="n"/>
@@ -67843,7 +67843,7 @@
     </row>
     <row r="1858">
       <c r="A1858" s="4" t="n">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="B1858" s="4" t="n"/>
       <c r="C1858" s="4" t="n"/>
@@ -67867,7 +67867,7 @@
     </row>
     <row r="1860">
       <c r="A1860" s="4" t="n">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="B1860" s="4" t="n"/>
       <c r="C1860" s="4" t="n"/>
@@ -67891,7 +67891,7 @@
     </row>
     <row r="1862">
       <c r="A1862" s="4" t="n">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="B1862" s="4" t="n"/>
       <c r="C1862" s="4" t="n"/>
@@ -67915,7 +67915,7 @@
     </row>
     <row r="1864">
       <c r="A1864" s="4" t="n">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="B1864" s="4" t="n"/>
       <c r="C1864" s="4" t="n"/>
@@ -67939,7 +67939,7 @@
     </row>
     <row r="1866">
       <c r="A1866" s="4" t="n">
-        <v>2822</v>
+        <v>2823</v>
       </c>
       <c r="B1866" s="4" t="n"/>
       <c r="C1866" s="4" t="n"/>
@@ -67963,7 +67963,7 @@
     </row>
     <row r="1868">
       <c r="A1868" s="4" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="B1868" s="4" t="n"/>
       <c r="C1868" s="4" t="n"/>
@@ -67987,7 +67987,7 @@
     </row>
     <row r="1870">
       <c r="A1870" s="4" t="n">
-        <v>2824</v>
+        <v>2825</v>
       </c>
       <c r="B1870" s="4" t="n"/>
       <c r="C1870" s="4" t="n"/>
@@ -68011,7 +68011,7 @@
     </row>
     <row r="1872">
       <c r="A1872" s="4" t="n">
-        <v>2825</v>
+        <v>2826</v>
       </c>
       <c r="B1872" s="4" t="n"/>
       <c r="C1872" s="4" t="n"/>
@@ -68035,7 +68035,7 @@
     </row>
     <row r="1874">
       <c r="A1874" s="4" t="n">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="B1874" s="4" t="n"/>
       <c r="C1874" s="4" t="n"/>
@@ -68059,7 +68059,7 @@
     </row>
     <row r="1876">
       <c r="A1876" s="4" t="n">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="B1876" s="4" t="n"/>
       <c r="C1876" s="4" t="n"/>
@@ -68083,7 +68083,7 @@
     </row>
     <row r="1878">
       <c r="A1878" s="4" t="n">
-        <v>2828</v>
+        <v>2829</v>
       </c>
       <c r="B1878" s="4" t="n"/>
       <c r="C1878" s="4" t="n"/>
@@ -68107,7 +68107,7 @@
     </row>
     <row r="1880">
       <c r="A1880" s="4" t="n">
-        <v>2829</v>
+        <v>2830</v>
       </c>
       <c r="B1880" s="4" t="n"/>
       <c r="C1880" s="4" t="n"/>
@@ -68131,7 +68131,7 @@
     </row>
     <row r="1882">
       <c r="A1882" s="4" t="n">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="B1882" s="4" t="n"/>
       <c r="C1882" s="4" t="n"/>
@@ -68155,7 +68155,7 @@
     </row>
     <row r="1884">
       <c r="A1884" s="4" t="n">
-        <v>2831</v>
+        <v>2832</v>
       </c>
       <c r="B1884" s="4" t="n"/>
       <c r="C1884" s="4" t="n"/>
@@ -68179,7 +68179,7 @@
     </row>
     <row r="1886">
       <c r="A1886" s="4" t="n">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="B1886" s="4" t="n"/>
       <c r="C1886" s="4" t="n"/>
@@ -68203,7 +68203,7 @@
     </row>
     <row r="1888">
       <c r="A1888" s="4" t="n">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="B1888" s="4" t="n"/>
       <c r="C1888" s="4" t="n"/>
@@ -68227,7 +68227,7 @@
     </row>
     <row r="1890">
       <c r="A1890" s="4" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="B1890" s="4" t="n"/>
       <c r="C1890" s="4" t="n"/>
@@ -68251,7 +68251,7 @@
     </row>
     <row r="1892">
       <c r="A1892" s="4" t="n">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="B1892" s="4" t="n"/>
       <c r="C1892" s="4" t="n"/>
@@ -68275,7 +68275,7 @@
     </row>
     <row r="1894">
       <c r="A1894" s="4" t="n">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="B1894" s="4" t="n"/>
       <c r="C1894" s="4" t="n"/>
@@ -68299,7 +68299,7 @@
     </row>
     <row r="1896">
       <c r="A1896" s="4" t="n">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="B1896" s="4" t="n"/>
       <c r="C1896" s="4" t="n"/>
@@ -68323,7 +68323,7 @@
     </row>
     <row r="1898">
       <c r="A1898" s="4" t="n">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="B1898" s="4" t="n"/>
       <c r="C1898" s="4" t="n"/>
@@ -68347,7 +68347,7 @@
     </row>
     <row r="1900">
       <c r="A1900" s="4" t="n">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="B1900" s="4" t="n"/>
       <c r="C1900" s="4" t="n"/>
@@ -68371,7 +68371,7 @@
     </row>
     <row r="1902">
       <c r="A1902" s="4" t="n">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="B1902" s="4" t="n"/>
       <c r="C1902" s="4" t="n"/>
@@ -68395,7 +68395,7 @@
     </row>
     <row r="1904">
       <c r="A1904" s="4" t="n">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="B1904" s="4" t="n"/>
       <c r="C1904" s="4" t="n"/>
@@ -68419,7 +68419,7 @@
     </row>
     <row r="1906">
       <c r="A1906" s="4" t="n">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="B1906" s="4" t="n"/>
       <c r="C1906" s="4" t="n"/>
@@ -68443,7 +68443,7 @@
     </row>
     <row r="1908">
       <c r="A1908" s="4" t="n">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="B1908" s="4" t="n"/>
       <c r="C1908" s="4" t="n"/>
@@ -68467,7 +68467,7 @@
     </row>
     <row r="1910">
       <c r="A1910" s="4" t="n">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="B1910" s="4" t="n"/>
       <c r="C1910" s="4" t="n"/>
@@ -68491,7 +68491,7 @@
     </row>
     <row r="1912">
       <c r="A1912" s="4" t="n">
-        <v>2845</v>
+        <v>30003</v>
       </c>
       <c r="B1912" s="4" t="n"/>
       <c r="C1912" s="4" t="n"/>
@@ -68500,22 +68500,22 @@
     <row r="1913">
       <c r="A1913" s="4" t="n"/>
       <c r="B1913" s="4" t="n">
-        <v>8</v>
+        <v>496</v>
       </c>
       <c r="C1913" s="4" t="inlineStr">
         <is>
-          <t>6, 8</t>
+          <t>72, 48</t>
         </is>
       </c>
       <c r="D1913" s="4" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="1914">
       <c r="A1914" s="4" t="n">
-        <v>30003</v>
+        <v>30009</v>
       </c>
       <c r="B1914" s="4" t="n"/>
       <c r="C1914" s="4" t="n"/>
@@ -68528,7 +68528,7 @@
       </c>
       <c r="C1915" s="4" t="inlineStr">
         <is>
-          <t>72, 48</t>
+          <t>160, 117</t>
         </is>
       </c>
       <c r="D1915" s="4" t="inlineStr">
@@ -68539,7 +68539,7 @@
     </row>
     <row r="1916">
       <c r="A1916" s="4" t="n">
-        <v>30009</v>
+        <v>30010</v>
       </c>
       <c r="B1916" s="4" t="n"/>
       <c r="C1916" s="4" t="n"/>
@@ -68548,42 +68548,42 @@
     <row r="1917">
       <c r="A1917" s="4" t="n"/>
       <c r="B1917" s="4" t="n">
-        <v>496</v>
+        <v>8</v>
       </c>
       <c r="C1917" s="4" t="inlineStr">
         <is>
-          <t>160, 117</t>
+          <t>10, 7</t>
         </is>
       </c>
       <c r="D1917" s="4" t="inlineStr">
         <is>
-          <t>BOTTOM</t>
+          <t>RIGHT</t>
         </is>
       </c>
     </row>
     <row r="1918">
-      <c r="A1918" s="4" t="n">
-        <v>30010</v>
-      </c>
-      <c r="B1918" s="4" t="n"/>
-      <c r="C1918" s="4" t="n"/>
-      <c r="D1918" s="4" t="n"/>
+      <c r="A1918" s="4" t="n"/>
+      <c r="B1918" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1918" s="4" t="inlineStr">
+        <is>
+          <t>14, 8</t>
+        </is>
+      </c>
+      <c r="D1918" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1919">
-      <c r="A1919" s="4" t="n"/>
-      <c r="B1919" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1919" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1919" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1919" s="4" t="n">
+        <v>30011</v>
+      </c>
+      <c r="B1919" s="4" t="n"/>
+      <c r="C1919" s="4" t="n"/>
+      <c r="D1919" s="4" t="n"/>
     </row>
     <row r="1920">
       <c r="A1920" s="4" t="n"/>
@@ -68592,38 +68592,38 @@
       </c>
       <c r="C1920" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1920" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="4" t="n"/>
+      <c r="B1921" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1921" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1920" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1921">
-      <c r="A1921" s="4" t="n">
-        <v>30011</v>
-      </c>
-      <c r="B1921" s="4" t="n"/>
-      <c r="C1921" s="4" t="n"/>
-      <c r="D1921" s="4" t="n"/>
+      <c r="D1921" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1922">
-      <c r="A1922" s="4" t="n"/>
-      <c r="B1922" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1922" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1922" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1922" s="4" t="n">
+        <v>30012</v>
+      </c>
+      <c r="B1922" s="4" t="n"/>
+      <c r="C1922" s="4" t="n"/>
+      <c r="D1922" s="4" t="n"/>
     </row>
     <row r="1923">
       <c r="A1923" s="4" t="n"/>
@@ -68632,38 +68632,38 @@
       </c>
       <c r="C1923" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1923" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="4" t="n"/>
+      <c r="B1924" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1924" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1923" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1924">
-      <c r="A1924" s="4" t="n">
-        <v>30012</v>
-      </c>
-      <c r="B1924" s="4" t="n"/>
-      <c r="C1924" s="4" t="n"/>
-      <c r="D1924" s="4" t="n"/>
+      <c r="D1924" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1925">
-      <c r="A1925" s="4" t="n"/>
-      <c r="B1925" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1925" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1925" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1925" s="4" t="n">
+        <v>30013</v>
+      </c>
+      <c r="B1925" s="4" t="n"/>
+      <c r="C1925" s="4" t="n"/>
+      <c r="D1925" s="4" t="n"/>
     </row>
     <row r="1926">
       <c r="A1926" s="4" t="n"/>
@@ -68672,38 +68672,38 @@
       </c>
       <c r="C1926" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1926" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="4" t="n"/>
+      <c r="B1927" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1927" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1926" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1927">
-      <c r="A1927" s="4" t="n">
-        <v>30013</v>
-      </c>
-      <c r="B1927" s="4" t="n"/>
-      <c r="C1927" s="4" t="n"/>
-      <c r="D1927" s="4" t="n"/>
+      <c r="D1927" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1928">
-      <c r="A1928" s="4" t="n"/>
-      <c r="B1928" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1928" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1928" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1928" s="4" t="n">
+        <v>30014</v>
+      </c>
+      <c r="B1928" s="4" t="n"/>
+      <c r="C1928" s="4" t="n"/>
+      <c r="D1928" s="4" t="n"/>
     </row>
     <row r="1929">
       <c r="A1929" s="4" t="n"/>
@@ -68712,38 +68712,38 @@
       </c>
       <c r="C1929" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1929" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="4" t="n"/>
+      <c r="B1930" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1930" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1929" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1930">
-      <c r="A1930" s="4" t="n">
-        <v>30014</v>
-      </c>
-      <c r="B1930" s="4" t="n"/>
-      <c r="C1930" s="4" t="n"/>
-      <c r="D1930" s="4" t="n"/>
+      <c r="D1930" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1931">
-      <c r="A1931" s="4" t="n"/>
-      <c r="B1931" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1931" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1931" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1931" s="4" t="n">
+        <v>30015</v>
+      </c>
+      <c r="B1931" s="4" t="n"/>
+      <c r="C1931" s="4" t="n"/>
+      <c r="D1931" s="4" t="n"/>
     </row>
     <row r="1932">
       <c r="A1932" s="4" t="n"/>
@@ -68752,38 +68752,38 @@
       </c>
       <c r="C1932" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1932" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="4" t="n"/>
+      <c r="B1933" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1933" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1932" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1933">
-      <c r="A1933" s="4" t="n">
-        <v>30015</v>
-      </c>
-      <c r="B1933" s="4" t="n"/>
-      <c r="C1933" s="4" t="n"/>
-      <c r="D1933" s="4" t="n"/>
+      <c r="D1933" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1934">
-      <c r="A1934" s="4" t="n"/>
-      <c r="B1934" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1934" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1934" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1934" s="4" t="n">
+        <v>30100</v>
+      </c>
+      <c r="B1934" s="4" t="n"/>
+      <c r="C1934" s="4" t="n"/>
+      <c r="D1934" s="4" t="n"/>
     </row>
     <row r="1935">
       <c r="A1935" s="4" t="n"/>
@@ -68792,38 +68792,38 @@
       </c>
       <c r="C1935" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1935" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="4" t="n"/>
+      <c r="B1936" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1936" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1935" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1936">
-      <c r="A1936" s="4" t="n">
-        <v>30100</v>
-      </c>
-      <c r="B1936" s="4" t="n"/>
-      <c r="C1936" s="4" t="n"/>
-      <c r="D1936" s="4" t="n"/>
+      <c r="D1936" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1937">
-      <c r="A1937" s="4" t="n"/>
-      <c r="B1937" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1937" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1937" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1937" s="4" t="n">
+        <v>30101</v>
+      </c>
+      <c r="B1937" s="4" t="n"/>
+      <c r="C1937" s="4" t="n"/>
+      <c r="D1937" s="4" t="n"/>
     </row>
     <row r="1938">
       <c r="A1938" s="4" t="n"/>
@@ -68832,38 +68832,38 @@
       </c>
       <c r="C1938" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1938" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="4" t="n"/>
+      <c r="B1939" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1939" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1938" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1939">
-      <c r="A1939" s="4" t="n">
-        <v>30101</v>
-      </c>
-      <c r="B1939" s="4" t="n"/>
-      <c r="C1939" s="4" t="n"/>
-      <c r="D1939" s="4" t="n"/>
+      <c r="D1939" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1940">
-      <c r="A1940" s="4" t="n"/>
-      <c r="B1940" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1940" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1940" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1940" s="4" t="n">
+        <v>30102</v>
+      </c>
+      <c r="B1940" s="4" t="n"/>
+      <c r="C1940" s="4" t="n"/>
+      <c r="D1940" s="4" t="n"/>
     </row>
     <row r="1941">
       <c r="A1941" s="4" t="n"/>
@@ -68872,38 +68872,38 @@
       </c>
       <c r="C1941" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1941" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="4" t="n"/>
+      <c r="B1942" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1942" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1941" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1942">
-      <c r="A1942" s="4" t="n">
-        <v>30102</v>
-      </c>
-      <c r="B1942" s="4" t="n"/>
-      <c r="C1942" s="4" t="n"/>
-      <c r="D1942" s="4" t="n"/>
+      <c r="D1942" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1943">
-      <c r="A1943" s="4" t="n"/>
-      <c r="B1943" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1943" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1943" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1943" s="4" t="n">
+        <v>30103</v>
+      </c>
+      <c r="B1943" s="4" t="n"/>
+      <c r="C1943" s="4" t="n"/>
+      <c r="D1943" s="4" t="n"/>
     </row>
     <row r="1944">
       <c r="A1944" s="4" t="n"/>
@@ -68912,38 +68912,38 @@
       </c>
       <c r="C1944" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1944" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="4" t="n"/>
+      <c r="B1945" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1945" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1944" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1945">
-      <c r="A1945" s="4" t="n">
-        <v>30103</v>
-      </c>
-      <c r="B1945" s="4" t="n"/>
-      <c r="C1945" s="4" t="n"/>
-      <c r="D1945" s="4" t="n"/>
+      <c r="D1945" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1946">
-      <c r="A1946" s="4" t="n"/>
-      <c r="B1946" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1946" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1946" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1946" s="4" t="n">
+        <v>30104</v>
+      </c>
+      <c r="B1946" s="4" t="n"/>
+      <c r="C1946" s="4" t="n"/>
+      <c r="D1946" s="4" t="n"/>
     </row>
     <row r="1947">
       <c r="A1947" s="4" t="n"/>
@@ -68952,38 +68952,38 @@
       </c>
       <c r="C1947" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1947" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="4" t="n"/>
+      <c r="B1948" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1948" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1947" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1948">
-      <c r="A1948" s="4" t="n">
-        <v>30104</v>
-      </c>
-      <c r="B1948" s="4" t="n"/>
-      <c r="C1948" s="4" t="n"/>
-      <c r="D1948" s="4" t="n"/>
+      <c r="D1948" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1949">
-      <c r="A1949" s="4" t="n"/>
-      <c r="B1949" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1949" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1949" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1949" s="4" t="n">
+        <v>30105</v>
+      </c>
+      <c r="B1949" s="4" t="n"/>
+      <c r="C1949" s="4" t="n"/>
+      <c r="D1949" s="4" t="n"/>
     </row>
     <row r="1950">
       <c r="A1950" s="4" t="n"/>
@@ -68992,38 +68992,38 @@
       </c>
       <c r="C1950" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1950" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="4" t="n"/>
+      <c r="B1951" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1951" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1950" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1951">
-      <c r="A1951" s="4" t="n">
-        <v>30105</v>
-      </c>
-      <c r="B1951" s="4" t="n"/>
-      <c r="C1951" s="4" t="n"/>
-      <c r="D1951" s="4" t="n"/>
+      <c r="D1951" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1952">
-      <c r="A1952" s="4" t="n"/>
-      <c r="B1952" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1952" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1952" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1952" s="4" t="n">
+        <v>30106</v>
+      </c>
+      <c r="B1952" s="4" t="n"/>
+      <c r="C1952" s="4" t="n"/>
+      <c r="D1952" s="4" t="n"/>
     </row>
     <row r="1953">
       <c r="A1953" s="4" t="n"/>
@@ -69032,38 +69032,38 @@
       </c>
       <c r="C1953" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1953" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="4" t="n"/>
+      <c r="B1954" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1954" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1953" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1954">
-      <c r="A1954" s="4" t="n">
-        <v>30106</v>
-      </c>
-      <c r="B1954" s="4" t="n"/>
-      <c r="C1954" s="4" t="n"/>
-      <c r="D1954" s="4" t="n"/>
+      <c r="D1954" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1955">
-      <c r="A1955" s="4" t="n"/>
-      <c r="B1955" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1955" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1955" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1955" s="4" t="n">
+        <v>30107</v>
+      </c>
+      <c r="B1955" s="4" t="n"/>
+      <c r="C1955" s="4" t="n"/>
+      <c r="D1955" s="4" t="n"/>
     </row>
     <row r="1956">
       <c r="A1956" s="4" t="n"/>
@@ -69072,47 +69072,47 @@
       </c>
       <c r="C1956" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1956" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="4" t="n"/>
+      <c r="B1957" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1957" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1956" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1957">
-      <c r="A1957" s="4" t="n">
-        <v>30107</v>
-      </c>
-      <c r="B1957" s="4" t="n"/>
-      <c r="C1957" s="4" t="n"/>
-      <c r="D1957" s="4" t="n"/>
+      <c r="D1957" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1958">
-      <c r="A1958" s="4" t="n"/>
-      <c r="B1958" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1958" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1958" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1958" s="4" t="n">
+        <v>30222</v>
+      </c>
+      <c r="B1958" s="4" t="n"/>
+      <c r="C1958" s="4" t="n"/>
+      <c r="D1958" s="4" t="n"/>
     </row>
     <row r="1959">
       <c r="A1959" s="4" t="n"/>
       <c r="B1959" s="4" t="n">
-        <v>8</v>
+        <v>450</v>
       </c>
       <c r="C1959" s="4" t="inlineStr">
         <is>
-          <t>14, 8</t>
+          <t>5, 32</t>
         </is>
       </c>
       <c r="D1959" s="4" t="inlineStr">
@@ -69123,7 +69123,7 @@
     </row>
     <row r="1960">
       <c r="A1960" s="4" t="n">
-        <v>30222</v>
+        <v>33003</v>
       </c>
       <c r="B1960" s="4" t="n"/>
       <c r="C1960" s="4" t="n"/>
@@ -69132,11 +69132,11 @@
     <row r="1961">
       <c r="A1961" s="4" t="n"/>
       <c r="B1961" s="4" t="n">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="C1961" s="4" t="inlineStr">
         <is>
-          <t>5, 32</t>
+          <t>6, 87</t>
         </is>
       </c>
       <c r="D1961" s="4" t="inlineStr">
@@ -69147,7 +69147,7 @@
     </row>
     <row r="1962">
       <c r="A1962" s="4" t="n">
-        <v>33003</v>
+        <v>33009</v>
       </c>
       <c r="B1962" s="4" t="n"/>
       <c r="C1962" s="4" t="n"/>
@@ -69160,7 +69160,7 @@
       </c>
       <c r="C1963" s="4" t="inlineStr">
         <is>
-          <t>6, 87</t>
+          <t>149, 55</t>
         </is>
       </c>
       <c r="D1963" s="4" t="inlineStr">
@@ -69171,7 +69171,7 @@
     </row>
     <row r="1964">
       <c r="A1964" s="4" t="n">
-        <v>33009</v>
+        <v>33010</v>
       </c>
       <c r="B1964" s="4" t="n"/>
       <c r="C1964" s="4" t="n"/>
@@ -69180,42 +69180,42 @@
     <row r="1965">
       <c r="A1965" s="4" t="n"/>
       <c r="B1965" s="4" t="n">
-        <v>496</v>
+        <v>8</v>
       </c>
       <c r="C1965" s="4" t="inlineStr">
         <is>
-          <t>149, 55</t>
+          <t>10, 7</t>
         </is>
       </c>
       <c r="D1965" s="4" t="inlineStr">
         <is>
-          <t>BOTTOM</t>
+          <t>RIGHT</t>
         </is>
       </c>
     </row>
     <row r="1966">
-      <c r="A1966" s="4" t="n">
-        <v>33010</v>
-      </c>
-      <c r="B1966" s="4" t="n"/>
-      <c r="C1966" s="4" t="n"/>
-      <c r="D1966" s="4" t="n"/>
+      <c r="A1966" s="4" t="n"/>
+      <c r="B1966" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1966" s="4" t="inlineStr">
+        <is>
+          <t>14, 8</t>
+        </is>
+      </c>
+      <c r="D1966" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1967">
-      <c r="A1967" s="4" t="n"/>
-      <c r="B1967" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1967" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1967" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1967" s="4" t="n">
+        <v>33011</v>
+      </c>
+      <c r="B1967" s="4" t="n"/>
+      <c r="C1967" s="4" t="n"/>
+      <c r="D1967" s="4" t="n"/>
     </row>
     <row r="1968">
       <c r="A1968" s="4" t="n"/>
@@ -69224,38 +69224,38 @@
       </c>
       <c r="C1968" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1968" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="4" t="n"/>
+      <c r="B1969" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1969" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1968" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1969">
-      <c r="A1969" s="4" t="n">
-        <v>33011</v>
-      </c>
-      <c r="B1969" s="4" t="n"/>
-      <c r="C1969" s="4" t="n"/>
-      <c r="D1969" s="4" t="n"/>
+      <c r="D1969" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1970">
-      <c r="A1970" s="4" t="n"/>
-      <c r="B1970" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1970" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1970" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1970" s="4" t="n">
+        <v>33012</v>
+      </c>
+      <c r="B1970" s="4" t="n"/>
+      <c r="C1970" s="4" t="n"/>
+      <c r="D1970" s="4" t="n"/>
     </row>
     <row r="1971">
       <c r="A1971" s="4" t="n"/>
@@ -69264,38 +69264,38 @@
       </c>
       <c r="C1971" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1971" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="4" t="n"/>
+      <c r="B1972" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1972" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1971" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1972">
-      <c r="A1972" s="4" t="n">
-        <v>33012</v>
-      </c>
-      <c r="B1972" s="4" t="n"/>
-      <c r="C1972" s="4" t="n"/>
-      <c r="D1972" s="4" t="n"/>
+      <c r="D1972" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1973">
-      <c r="A1973" s="4" t="n"/>
-      <c r="B1973" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1973" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1973" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1973" s="4" t="n">
+        <v>33013</v>
+      </c>
+      <c r="B1973" s="4" t="n"/>
+      <c r="C1973" s="4" t="n"/>
+      <c r="D1973" s="4" t="n"/>
     </row>
     <row r="1974">
       <c r="A1974" s="4" t="n"/>
@@ -69304,38 +69304,38 @@
       </c>
       <c r="C1974" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1974" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="4" t="n"/>
+      <c r="B1975" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1975" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1974" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1975">
-      <c r="A1975" s="4" t="n">
-        <v>33013</v>
-      </c>
-      <c r="B1975" s="4" t="n"/>
-      <c r="C1975" s="4" t="n"/>
-      <c r="D1975" s="4" t="n"/>
+      <c r="D1975" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1976">
-      <c r="A1976" s="4" t="n"/>
-      <c r="B1976" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1976" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1976" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1976" s="4" t="n">
+        <v>33014</v>
+      </c>
+      <c r="B1976" s="4" t="n"/>
+      <c r="C1976" s="4" t="n"/>
+      <c r="D1976" s="4" t="n"/>
     </row>
     <row r="1977">
       <c r="A1977" s="4" t="n"/>
@@ -69344,38 +69344,38 @@
       </c>
       <c r="C1977" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1977" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="4" t="n"/>
+      <c r="B1978" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1978" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1977" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1978">
-      <c r="A1978" s="4" t="n">
-        <v>33014</v>
-      </c>
-      <c r="B1978" s="4" t="n"/>
-      <c r="C1978" s="4" t="n"/>
-      <c r="D1978" s="4" t="n"/>
+      <c r="D1978" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1979">
-      <c r="A1979" s="4" t="n"/>
-      <c r="B1979" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1979" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1979" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1979" s="4" t="n">
+        <v>33100</v>
+      </c>
+      <c r="B1979" s="4" t="n"/>
+      <c r="C1979" s="4" t="n"/>
+      <c r="D1979" s="4" t="n"/>
     </row>
     <row r="1980">
       <c r="A1980" s="4" t="n"/>
@@ -69384,38 +69384,38 @@
       </c>
       <c r="C1980" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1980" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="4" t="n"/>
+      <c r="B1981" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1981" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1980" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1981">
-      <c r="A1981" s="4" t="n">
-        <v>33100</v>
-      </c>
-      <c r="B1981" s="4" t="n"/>
-      <c r="C1981" s="4" t="n"/>
-      <c r="D1981" s="4" t="n"/>
+      <c r="D1981" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1982">
-      <c r="A1982" s="4" t="n"/>
-      <c r="B1982" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1982" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1982" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1982" s="4" t="n">
+        <v>33101</v>
+      </c>
+      <c r="B1982" s="4" t="n"/>
+      <c r="C1982" s="4" t="n"/>
+      <c r="D1982" s="4" t="n"/>
     </row>
     <row r="1983">
       <c r="A1983" s="4" t="n"/>
@@ -69424,38 +69424,38 @@
       </c>
       <c r="C1983" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1983" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="4" t="n"/>
+      <c r="B1984" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1984" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1983" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1984">
-      <c r="A1984" s="4" t="n">
-        <v>33101</v>
-      </c>
-      <c r="B1984" s="4" t="n"/>
-      <c r="C1984" s="4" t="n"/>
-      <c r="D1984" s="4" t="n"/>
+      <c r="D1984" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1985">
-      <c r="A1985" s="4" t="n"/>
-      <c r="B1985" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1985" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1985" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1985" s="4" t="n">
+        <v>33102</v>
+      </c>
+      <c r="B1985" s="4" t="n"/>
+      <c r="C1985" s="4" t="n"/>
+      <c r="D1985" s="4" t="n"/>
     </row>
     <row r="1986">
       <c r="A1986" s="4" t="n"/>
@@ -69464,38 +69464,38 @@
       </c>
       <c r="C1986" s="4" t="inlineStr">
         <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D1986" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="4" t="n"/>
+      <c r="B1987" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1987" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1986" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1987">
-      <c r="A1987" s="4" t="n">
-        <v>33102</v>
-      </c>
-      <c r="B1987" s="4" t="n"/>
-      <c r="C1987" s="4" t="n"/>
-      <c r="D1987" s="4" t="n"/>
+      <c r="D1987" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1988">
-      <c r="A1988" s="4" t="n"/>
-      <c r="B1988" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1988" s="4" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D1988" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1988" s="4" t="n">
+        <v>33103</v>
+      </c>
+      <c r="B1988" s="4" t="n"/>
+      <c r="C1988" s="4" t="n"/>
+      <c r="D1988" s="4" t="n"/>
     </row>
     <row r="1989">
       <c r="A1989" s="4" t="n"/>
@@ -69504,47 +69504,47 @@
       </c>
       <c r="C1989" s="4" t="inlineStr">
         <is>
+          <t>12, 7</t>
+        </is>
+      </c>
+      <c r="D1989" s="4" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="4" t="n"/>
+      <c r="B1990" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1990" s="4" t="inlineStr">
+        <is>
           <t>14, 8</t>
         </is>
       </c>
-      <c r="D1989" s="4" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="1990">
-      <c r="A1990" s="4" t="n">
-        <v>33103</v>
-      </c>
-      <c r="B1990" s="4" t="n"/>
-      <c r="C1990" s="4" t="n"/>
-      <c r="D1990" s="4" t="n"/>
+      <c r="D1990" s="4" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="1991">
-      <c r="A1991" s="4" t="n"/>
-      <c r="B1991" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1991" s="4" t="inlineStr">
-        <is>
-          <t>12, 7</t>
-        </is>
-      </c>
-      <c r="D1991" s="4" t="inlineStr">
-        <is>
-          <t>RIGHT</t>
-        </is>
-      </c>
+      <c r="A1991" s="4" t="n">
+        <v>3409</v>
+      </c>
+      <c r="B1991" s="4" t="n"/>
+      <c r="C1991" s="4" t="n"/>
+      <c r="D1991" s="4" t="n"/>
     </row>
     <row r="1992">
       <c r="A1992" s="4" t="n"/>
       <c r="B1992" s="4" t="n">
-        <v>8</v>
+        <v>463</v>
       </c>
       <c r="C1992" s="4" t="inlineStr">
         <is>
-          <t>14, 8</t>
+          <t>11, 6</t>
         </is>
       </c>
       <c r="D1992" s="4" t="inlineStr">
@@ -69555,7 +69555,7 @@
     </row>
     <row r="1993">
       <c r="A1993" s="4" t="n">
-        <v>3409</v>
+        <v>3419</v>
       </c>
       <c r="B1993" s="4" t="n"/>
       <c r="C1993" s="4" t="n"/>
@@ -69564,7 +69564,7 @@
     <row r="1994">
       <c r="A1994" s="4" t="n"/>
       <c r="B1994" s="4" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C1994" s="4" t="inlineStr">
         <is>
@@ -69579,7 +69579,7 @@
     </row>
     <row r="1995">
       <c r="A1995" s="4" t="n">
-        <v>3419</v>
+        <v>3429</v>
       </c>
       <c r="B1995" s="4" t="n"/>
       <c r="C1995" s="4" t="n"/>
@@ -69588,7 +69588,7 @@
     <row r="1996">
       <c r="A1996" s="4" t="n"/>
       <c r="B1996" s="4" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C1996" s="4" t="inlineStr">
         <is>
@@ -69603,7 +69603,7 @@
     </row>
     <row r="1997">
       <c r="A1997" s="4" t="n">
-        <v>3429</v>
+        <v>3439</v>
       </c>
       <c r="B1997" s="4" t="n"/>
       <c r="C1997" s="4" t="n"/>
@@ -69612,7 +69612,7 @@
     <row r="1998">
       <c r="A1998" s="4" t="n"/>
       <c r="B1998" s="4" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C1998" s="4" t="inlineStr">
         <is>
@@ -69627,7 +69627,7 @@
     </row>
     <row r="1999">
       <c r="A1999" s="4" t="n">
-        <v>3439</v>
+        <v>3449</v>
       </c>
       <c r="B1999" s="4" t="n"/>
       <c r="C1999" s="4" t="n"/>
@@ -69636,7 +69636,7 @@
     <row r="2000">
       <c r="A2000" s="4" t="n"/>
       <c r="B2000" s="4" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C2000" s="4" t="inlineStr">
         <is>
@@ -69651,7 +69651,7 @@
     </row>
     <row r="2001">
       <c r="A2001" s="4" t="n">
-        <v>3449</v>
+        <v>3459</v>
       </c>
       <c r="B2001" s="4" t="n"/>
       <c r="C2001" s="4" t="n"/>
@@ -69660,7 +69660,7 @@
     <row r="2002">
       <c r="A2002" s="4" t="n"/>
       <c r="B2002" s="4" t="n">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C2002" s="4" t="inlineStr">
         <is>
@@ -69675,7 +69675,7 @@
     </row>
     <row r="2003">
       <c r="A2003" s="4" t="n">
-        <v>3459</v>
+        <v>3469</v>
       </c>
       <c r="B2003" s="4" t="n"/>
       <c r="C2003" s="4" t="n"/>
@@ -69684,7 +69684,7 @@
     <row r="2004">
       <c r="A2004" s="4" t="n"/>
       <c r="B2004" s="4" t="n">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C2004" s="4" t="inlineStr">
         <is>
@@ -69699,7 +69699,7 @@
     </row>
     <row r="2005">
       <c r="A2005" s="4" t="n">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="B2005" s="4" t="n"/>
       <c r="C2005" s="4" t="n"/>
@@ -69708,11 +69708,11 @@
     <row r="2006">
       <c r="A2006" s="4" t="n"/>
       <c r="B2006" s="4" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C2006" s="4" t="inlineStr">
         <is>
-          <t>11, 6</t>
+          <t>15, 10</t>
         </is>
       </c>
       <c r="D2006" s="4" t="inlineStr">
@@ -69723,7 +69723,7 @@
     </row>
     <row r="2007">
       <c r="A2007" s="4" t="n">
-        <v>3470</v>
+        <v>3479</v>
       </c>
       <c r="B2007" s="4" t="n"/>
       <c r="C2007" s="4" t="n"/>
@@ -69732,11 +69732,11 @@
     <row r="2008">
       <c r="A2008" s="4" t="n"/>
       <c r="B2008" s="4" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C2008" s="4" t="inlineStr">
         <is>
-          <t>15, 10</t>
+          <t>11, 6</t>
         </is>
       </c>
       <c r="D2008" s="4" t="inlineStr">
@@ -69747,7 +69747,7 @@
     </row>
     <row r="2009">
       <c r="A2009" s="4" t="n">
-        <v>3479</v>
+        <v>3489</v>
       </c>
       <c r="B2009" s="4" t="n"/>
       <c r="C2009" s="4" t="n"/>
@@ -69756,7 +69756,7 @@
     <row r="2010">
       <c r="A2010" s="4" t="n"/>
       <c r="B2010" s="4" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C2010" s="4" t="inlineStr">
         <is>
@@ -69771,7 +69771,7 @@
     </row>
     <row r="2011">
       <c r="A2011" s="4" t="n">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="B2011" s="4" t="n"/>
       <c r="C2011" s="4" t="n"/>
@@ -69780,11 +69780,11 @@
     <row r="2012">
       <c r="A2012" s="4" t="n"/>
       <c r="B2012" s="4" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C2012" s="4" t="inlineStr">
         <is>
-          <t>11, 6</t>
+          <t>15, 10</t>
         </is>
       </c>
       <c r="D2012" s="4" t="inlineStr">
@@ -69795,7 +69795,7 @@
     </row>
     <row r="2013">
       <c r="A2013" s="4" t="n">
-        <v>3490</v>
+        <v>3499</v>
       </c>
       <c r="B2013" s="4" t="n"/>
       <c r="C2013" s="4" t="n"/>
@@ -69804,11 +69804,11 @@
     <row r="2014">
       <c r="A2014" s="4" t="n"/>
       <c r="B2014" s="4" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C2014" s="4" t="inlineStr">
         <is>
-          <t>15, 10</t>
+          <t>11, 6</t>
         </is>
       </c>
       <c r="D2014" s="4" t="inlineStr">
@@ -69819,7 +69819,7 @@
     </row>
     <row r="2015">
       <c r="A2015" s="4" t="n">
-        <v>3499</v>
+        <v>3509</v>
       </c>
       <c r="B2015" s="4" t="n"/>
       <c r="C2015" s="4" t="n"/>
@@ -69828,7 +69828,7 @@
     <row r="2016">
       <c r="A2016" s="4" t="n"/>
       <c r="B2016" s="4" t="n">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C2016" s="4" t="inlineStr">
         <is>
@@ -69843,7 +69843,7 @@
     </row>
     <row r="2017">
       <c r="A2017" s="4" t="n">
-        <v>3509</v>
+        <v>3519</v>
       </c>
       <c r="B2017" s="4" t="n"/>
       <c r="C2017" s="4" t="n"/>
@@ -69852,7 +69852,7 @@
     <row r="2018">
       <c r="A2018" s="4" t="n"/>
       <c r="B2018" s="4" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C2018" s="4" t="inlineStr">
         <is>
@@ -69867,7 +69867,7 @@
     </row>
     <row r="2019">
       <c r="A2019" s="4" t="n">
-        <v>3519</v>
+        <v>3529</v>
       </c>
       <c r="B2019" s="4" t="n"/>
       <c r="C2019" s="4" t="n"/>
@@ -69876,7 +69876,7 @@
     <row r="2020">
       <c r="A2020" s="4" t="n"/>
       <c r="B2020" s="4" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C2020" s="4" t="inlineStr">
         <is>
@@ -69891,7 +69891,7 @@
     </row>
     <row r="2021">
       <c r="A2021" s="4" t="n">
-        <v>3529</v>
+        <v>3539</v>
       </c>
       <c r="B2021" s="4" t="n"/>
       <c r="C2021" s="4" t="n"/>
@@ -69900,7 +69900,7 @@
     <row r="2022">
       <c r="A2022" s="4" t="n"/>
       <c r="B2022" s="4" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C2022" s="4" t="inlineStr">
         <is>
@@ -69915,7 +69915,7 @@
     </row>
     <row r="2023">
       <c r="A2023" s="4" t="n">
-        <v>3539</v>
+        <v>3549</v>
       </c>
       <c r="B2023" s="4" t="n"/>
       <c r="C2023" s="4" t="n"/>
@@ -69924,7 +69924,7 @@
     <row r="2024">
       <c r="A2024" s="4" t="n"/>
       <c r="B2024" s="4" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C2024" s="4" t="inlineStr">
         <is>
@@ -69938,24 +69938,21 @@
       </c>
     </row>
     <row r="2025">
-      <c r="A2025" s="4" t="n">
-        <v>3549</v>
-      </c>
-      <c r="B2025" s="4" t="n"/>
-      <c r="C2025" s="4" t="n"/>
-      <c r="D2025" s="4" t="n"/>
+      <c r="A2025" s="9" t="n">
+        <v>3559</v>
+      </c>
     </row>
     <row r="2026">
-      <c r="A2026" s="4" t="n"/>
-      <c r="B2026" s="4" t="n">
-        <v>469</v>
-      </c>
-      <c r="C2026" s="4" t="inlineStr">
+      <c r="A2026" s="9" t="n"/>
+      <c r="B2026" s="9" t="n">
+        <v>474</v>
+      </c>
+      <c r="C2026" s="9" t="inlineStr">
         <is>
           <t>11, 6</t>
         </is>
       </c>
-      <c r="D2026" s="4" t="inlineStr">
+      <c r="D2026" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -69963,13 +69960,13 @@
     </row>
     <row r="2027">
       <c r="A2027" s="9" t="n">
-        <v>3559</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="2028">
       <c r="A2028" s="9" t="n"/>
       <c r="B2028" s="9" t="n">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C2028" s="9" t="inlineStr">
         <is>
@@ -69984,17 +69981,17 @@
     </row>
     <row r="2029">
       <c r="A2029" s="9" t="n">
-        <v>3569</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="2030">
       <c r="A2030" s="9" t="n"/>
       <c r="B2030" s="9" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C2030" s="9" t="inlineStr">
         <is>
-          <t>11, 6</t>
+          <t>15, 10</t>
         </is>
       </c>
       <c r="D2030" s="9" t="inlineStr">
@@ -70005,17 +70002,17 @@
     </row>
     <row r="2031">
       <c r="A2031" s="9" t="n">
-        <v>3570</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="2032">
       <c r="A2032" s="9" t="n"/>
       <c r="B2032" s="9" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C2032" s="9" t="inlineStr">
         <is>
-          <t>15, 10</t>
+          <t>11, 6</t>
         </is>
       </c>
       <c r="D2032" s="9" t="inlineStr">
@@ -70026,13 +70023,13 @@
     </row>
     <row r="2033">
       <c r="A2033" s="9" t="n">
-        <v>3579</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="2034">
       <c r="A2034" s="9" t="n"/>
       <c r="B2034" s="9" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C2034" s="9" t="inlineStr">
         <is>
@@ -70047,17 +70044,17 @@
     </row>
     <row r="2035">
       <c r="A2035" s="9" t="n">
-        <v>3589</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="2036">
       <c r="A2036" s="9" t="n"/>
       <c r="B2036" s="9" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C2036" s="9" t="inlineStr">
         <is>
-          <t>11, 6</t>
+          <t>15, 10</t>
         </is>
       </c>
       <c r="D2036" s="9" t="inlineStr">
@@ -70068,17 +70065,17 @@
     </row>
     <row r="2037">
       <c r="A2037" s="9" t="n">
-        <v>3590</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="2038">
       <c r="A2038" s="9" t="n"/>
       <c r="B2038" s="9" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C2038" s="9" t="inlineStr">
         <is>
-          <t>15, 10</t>
+          <t>11, 6</t>
         </is>
       </c>
       <c r="D2038" s="9" t="inlineStr">
@@ -70089,17 +70086,17 @@
     </row>
     <row r="2039">
       <c r="A2039" s="9" t="n">
-        <v>3599</v>
+        <v>46012</v>
       </c>
     </row>
     <row r="2040">
       <c r="A2040" s="9" t="n"/>
       <c r="B2040" s="9" t="n">
-        <v>467</v>
+        <v>611</v>
       </c>
       <c r="C2040" s="9" t="inlineStr">
         <is>
-          <t>11, 6</t>
+          <t>14, 10</t>
         </is>
       </c>
       <c r="D2040" s="9" t="inlineStr">
@@ -70110,57 +70107,57 @@
     </row>
     <row r="2041">
       <c r="A2041" s="9" t="n">
-        <v>46012</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="B2041" s="9" t="n"/>
+      <c r="C2041" s="9" t="n"/>
+      <c r="D2041" s="9" t="n"/>
     </row>
     <row r="2042">
       <c r="A2042" s="9" t="n"/>
-      <c r="B2042" s="9" t="n">
-        <v>611</v>
-      </c>
-      <c r="C2042" s="9" t="inlineStr">
-        <is>
-          <t>14, 10</t>
-        </is>
-      </c>
-      <c r="D2042" s="9" t="inlineStr">
+      <c r="B2042" s="0" t="n">
+        <v>545</v>
+      </c>
+      <c r="C2042" s="0" t="inlineStr">
+        <is>
+          <t>10, 6</t>
+        </is>
+      </c>
+      <c r="D2042" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2043">
-      <c r="A2043" s="9" t="n">
-        <v>504</v>
-      </c>
-      <c r="B2043" s="9" t="n"/>
-      <c r="C2043" s="9" t="n"/>
-      <c r="D2043" s="9" t="n"/>
+      <c r="A2043" s="9" t="n"/>
+      <c r="B2043" s="9" t="n">
+        <v>407</v>
+      </c>
+      <c r="C2043" s="9" t="inlineStr">
+        <is>
+          <t>8, 6</t>
+        </is>
+      </c>
+      <c r="D2043" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2044">
-      <c r="A2044" s="9" t="n"/>
-      <c r="B2044" s="0" t="n">
-        <v>545</v>
-      </c>
-      <c r="C2044" s="0" t="inlineStr">
-        <is>
-          <t>10, 6</t>
-        </is>
-      </c>
-      <c r="D2044" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2044" s="9" t="n">
+        <v>2190</v>
       </c>
     </row>
     <row r="2045">
       <c r="A2045" s="9" t="n"/>
       <c r="B2045" s="9" t="n">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="C2045" s="9" t="inlineStr">
         <is>
-          <t>8, 6</t>
+          <t>9, 38</t>
         </is>
       </c>
       <c r="D2045" s="9" t="inlineStr">
@@ -70170,18 +70167,29 @@
       </c>
     </row>
     <row r="2046">
-      <c r="A2046" s="9" t="n">
-        <v>2190</v>
+      <c r="A2046" s="9" t="n"/>
+      <c r="B2046" s="0" t="n">
+        <v>444</v>
+      </c>
+      <c r="C2046" s="0" t="inlineStr">
+        <is>
+          <t>4, 38</t>
+        </is>
+      </c>
+      <c r="D2046" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2047">
       <c r="A2047" s="9" t="n"/>
       <c r="B2047" s="9" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C2047" s="9" t="inlineStr">
         <is>
-          <t>9, 38</t>
+          <t>9, 1</t>
         </is>
       </c>
       <c r="D2047" s="9" t="inlineStr">
@@ -70191,29 +70199,18 @@
       </c>
     </row>
     <row r="2048">
-      <c r="A2048" s="9" t="n"/>
-      <c r="B2048" s="0" t="n">
-        <v>444</v>
-      </c>
-      <c r="C2048" s="0" t="inlineStr">
-        <is>
-          <t>4, 38</t>
-        </is>
-      </c>
-      <c r="D2048" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2048" s="9" t="n">
+        <v>53126</v>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" s="9" t="n"/>
       <c r="B2049" s="9" t="n">
-        <v>444</v>
+        <v>542</v>
       </c>
       <c r="C2049" s="9" t="inlineStr">
         <is>
-          <t>9, 1</t>
+          <t>11, 9</t>
         </is>
       </c>
       <c r="D2049" s="9" t="inlineStr">
@@ -70224,17 +70221,17 @@
     </row>
     <row r="2050">
       <c r="A2050" s="9" t="n">
-        <v>53126</v>
+        <v>53127</v>
       </c>
     </row>
     <row r="2051">
       <c r="A2051" s="9" t="n"/>
       <c r="B2051" s="9" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C2051" s="9" t="inlineStr">
         <is>
-          <t>11, 9</t>
+          <t>11, 16</t>
         </is>
       </c>
       <c r="D2051" s="9" t="inlineStr">
@@ -70245,17 +70242,17 @@
     </row>
     <row r="2052">
       <c r="A2052" s="9" t="n">
-        <v>53127</v>
+        <v>53125</v>
       </c>
     </row>
     <row r="2053">
       <c r="A2053" s="9" t="n"/>
       <c r="B2053" s="9" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C2053" s="9" t="inlineStr">
         <is>
-          <t>11, 16</t>
+          <t>10, 8</t>
         </is>
       </c>
       <c r="D2053" s="9" t="inlineStr">
@@ -70266,17 +70263,17 @@
     </row>
     <row r="2054">
       <c r="A2054" s="9" t="n">
-        <v>53125</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="2055">
       <c r="A2055" s="9" t="n"/>
       <c r="B2055" s="9" t="n">
-        <v>545</v>
+        <v>462</v>
       </c>
       <c r="C2055" s="9" t="inlineStr">
         <is>
-          <t>10, 8</t>
+          <t>19, 9</t>
         </is>
       </c>
       <c r="D2055" s="9" t="inlineStr">
@@ -70287,17 +70284,17 @@
     </row>
     <row r="2056">
       <c r="A2056" s="9" t="n">
-        <v>1489</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="2057">
       <c r="A2057" s="9" t="n"/>
       <c r="B2057" s="9" t="n">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="C2057" s="9" t="inlineStr">
         <is>
-          <t>19, 9</t>
+          <t>8, 4</t>
         </is>
       </c>
       <c r="D2057" s="9" t="inlineStr">
@@ -70308,7 +70305,7 @@
     </row>
     <row r="2058">
       <c r="A2058" s="9" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="2059">
@@ -70329,17 +70326,17 @@
     </row>
     <row r="2060">
       <c r="A2060" s="9" t="n">
-        <v>46006</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="2061">
       <c r="A2061" s="9" t="n"/>
       <c r="B2061" s="9" t="n">
-        <v>444</v>
+        <v>604</v>
       </c>
       <c r="C2061" s="9" t="inlineStr">
         <is>
-          <t>8, 4</t>
+          <t>9, 17</t>
         </is>
       </c>
       <c r="D2061" s="9" t="inlineStr">
@@ -70350,17 +70347,17 @@
     </row>
     <row r="2062">
       <c r="A2062" s="9" t="n">
-        <v>46029</v>
+        <v>46039</v>
       </c>
     </row>
     <row r="2063">
       <c r="A2063" s="9" t="n"/>
       <c r="B2063" s="9" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C2063" s="9" t="inlineStr">
         <is>
-          <t>9, 17</t>
+          <t>7, 4</t>
         </is>
       </c>
       <c r="D2063" s="9" t="inlineStr">
@@ -70371,17 +70368,17 @@
     </row>
     <row r="2064">
       <c r="A2064" s="9" t="n">
-        <v>46039</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="2065">
       <c r="A2065" s="9" t="n"/>
       <c r="B2065" s="9" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C2065" s="9" t="inlineStr">
         <is>
-          <t>7, 4</t>
+          <t>9, 11</t>
         </is>
       </c>
       <c r="D2065" s="9" t="inlineStr">
@@ -70392,17 +70389,17 @@
     </row>
     <row r="2066">
       <c r="A2066" s="9" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="2067">
       <c r="A2067" s="9" t="n"/>
       <c r="B2067" s="9" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C2067" s="9" t="inlineStr">
         <is>
-          <t>9, 11</t>
+          <t>12, 6</t>
         </is>
       </c>
       <c r="D2067" s="9" t="inlineStr">
@@ -70413,17 +70410,17 @@
     </row>
     <row r="2068">
       <c r="A2068" s="9" t="n">
-        <v>46059</v>
+        <v>904</v>
       </c>
     </row>
     <row r="2069">
       <c r="A2069" s="9" t="n"/>
       <c r="B2069" s="9" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C2069" s="9" t="inlineStr">
         <is>
-          <t>12, 6</t>
+          <t>15, 8</t>
         </is>
       </c>
       <c r="D2069" s="9" t="inlineStr">
@@ -70433,34 +70430,37 @@
       </c>
     </row>
     <row r="2070">
-      <c r="A2070" s="9" t="n">
-        <v>904</v>
+      <c r="A2070" s="9" t="n"/>
+      <c r="B2070" s="0" t="n">
+        <v>609</v>
+      </c>
+      <c r="C2070" s="0" t="inlineStr">
+        <is>
+          <t>14, 14</t>
+        </is>
+      </c>
+      <c r="D2070" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2071">
-      <c r="A2071" s="9" t="n"/>
-      <c r="B2071" s="9" t="n">
-        <v>608</v>
-      </c>
-      <c r="C2071" s="9" t="inlineStr">
-        <is>
-          <t>15, 8</t>
-        </is>
-      </c>
-      <c r="D2071" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A2071" s="9" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B2071" s="9" t="n"/>
+      <c r="C2071" s="9" t="n"/>
+      <c r="D2071" s="9" t="n"/>
     </row>
     <row r="2072">
       <c r="A2072" s="9" t="n"/>
       <c r="B2072" s="0" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C2072" s="0" t="inlineStr">
         <is>
-          <t>14, 14</t>
+          <t>6, 7</t>
         </is>
       </c>
       <c r="D2072" s="0" t="inlineStr">
@@ -70471,7 +70471,7 @@
     </row>
     <row r="2073">
       <c r="A2073" s="9" t="n">
-        <v>46069</v>
+        <v>46079</v>
       </c>
       <c r="B2073" s="9" t="n"/>
       <c r="C2073" s="9" t="n"/>
@@ -70480,11 +70480,11 @@
     <row r="2074">
       <c r="A2074" s="9" t="n"/>
       <c r="B2074" s="0" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C2074" s="0" t="inlineStr">
         <is>
-          <t>6, 7</t>
+          <t>5, 7</t>
         </is>
       </c>
       <c r="D2074" s="0" t="inlineStr">
@@ -70495,7 +70495,7 @@
     </row>
     <row r="2075">
       <c r="A2075" s="9" t="n">
-        <v>46079</v>
+        <v>46013</v>
       </c>
       <c r="B2075" s="9" t="n"/>
       <c r="C2075" s="9" t="n"/>
@@ -70504,11 +70504,11 @@
     <row r="2076">
       <c r="A2076" s="9" t="n"/>
       <c r="B2076" s="0" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C2076" s="0" t="inlineStr">
         <is>
-          <t>5, 7</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D2076" s="0" t="inlineStr">
@@ -70519,7 +70519,7 @@
     </row>
     <row r="2077">
       <c r="A2077" s="9" t="n">
-        <v>46013</v>
+        <v>46088</v>
       </c>
       <c r="B2077" s="9" t="n"/>
       <c r="C2077" s="9" t="n"/>
@@ -70528,11 +70528,11 @@
     <row r="2078">
       <c r="A2078" s="9" t="n"/>
       <c r="B2078" s="0" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C2078" s="0" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>10, 2</t>
         </is>
       </c>
       <c r="D2078" s="0" t="inlineStr">
@@ -70543,7 +70543,7 @@
     </row>
     <row r="2079">
       <c r="A2079" s="9" t="n">
-        <v>46088</v>
+        <v>46015</v>
       </c>
       <c r="B2079" s="9" t="n"/>
       <c r="C2079" s="9" t="n"/>
@@ -70552,11 +70552,11 @@
     <row r="2080">
       <c r="A2080" s="9" t="n"/>
       <c r="B2080" s="0" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C2080" s="0" t="inlineStr">
         <is>
-          <t>10, 2</t>
+          <t>5, 5</t>
         </is>
       </c>
       <c r="D2080" s="0" t="inlineStr">
@@ -70567,7 +70567,7 @@
     </row>
     <row r="2081">
       <c r="A2081" s="9" t="n">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="B2081" s="9" t="n"/>
       <c r="C2081" s="9" t="n"/>
@@ -70576,11 +70576,11 @@
     <row r="2082">
       <c r="A2082" s="9" t="n"/>
       <c r="B2082" s="0" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C2082" s="0" t="inlineStr">
         <is>
-          <t>5, 5</t>
+          <t>6, 5</t>
         </is>
       </c>
       <c r="D2082" s="0" t="inlineStr">
@@ -70591,7 +70591,7 @@
     </row>
     <row r="2083">
       <c r="A2083" s="9" t="n">
-        <v>46014</v>
+        <v>46099</v>
       </c>
       <c r="B2083" s="9" t="n"/>
       <c r="C2083" s="9" t="n"/>
@@ -70600,11 +70600,11 @@
     <row r="2084">
       <c r="A2084" s="9" t="n"/>
       <c r="B2084" s="0" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C2084" s="0" t="inlineStr">
         <is>
-          <t>6, 5</t>
+          <t>6, 6</t>
         </is>
       </c>
       <c r="D2084" s="0" t="inlineStr">
@@ -70615,7 +70615,7 @@
     </row>
     <row r="2085">
       <c r="A2085" s="9" t="n">
-        <v>46099</v>
+        <v>46109</v>
       </c>
       <c r="B2085" s="9" t="n"/>
       <c r="C2085" s="9" t="n"/>
@@ -70624,11 +70624,11 @@
     <row r="2086">
       <c r="A2086" s="9" t="n"/>
       <c r="B2086" s="0" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C2086" s="0" t="inlineStr">
         <is>
-          <t>6, 6</t>
+          <t>10, 10</t>
         </is>
       </c>
       <c r="D2086" s="0" t="inlineStr">
@@ -70639,7 +70639,7 @@
     </row>
     <row r="2087">
       <c r="A2087" s="9" t="n">
-        <v>46109</v>
+        <v>46120</v>
       </c>
       <c r="B2087" s="9" t="n"/>
       <c r="C2087" s="9" t="n"/>
@@ -70648,11 +70648,11 @@
     <row r="2088">
       <c r="A2088" s="9" t="n"/>
       <c r="B2088" s="0" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C2088" s="0" t="inlineStr">
         <is>
-          <t>10, 10</t>
+          <t>7, 7</t>
         </is>
       </c>
       <c r="D2088" s="0" t="inlineStr">
@@ -70663,7 +70663,7 @@
     </row>
     <row r="2089">
       <c r="A2089" s="9" t="n">
-        <v>46120</v>
+        <v>46001</v>
       </c>
       <c r="B2089" s="9" t="n"/>
       <c r="C2089" s="9" t="n"/>
@@ -70672,22 +70672,22 @@
     <row r="2090">
       <c r="A2090" s="9" t="n"/>
       <c r="B2090" s="0" t="n">
-        <v>619</v>
+        <v>8</v>
       </c>
       <c r="C2090" s="0" t="inlineStr">
         <is>
-          <t>7, 7</t>
+          <t>6, 8</t>
         </is>
       </c>
       <c r="D2090" s="0" t="inlineStr">
         <is>
-          <t>BOTTOM</t>
+          <t>RIGHT</t>
         </is>
       </c>
     </row>
     <row r="2091">
       <c r="A2091" s="9" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B2091" s="9" t="n"/>
       <c r="C2091" s="9" t="n"/>
@@ -70696,22 +70696,22 @@
     <row r="2092">
       <c r="A2092" s="9" t="n"/>
       <c r="B2092" s="0" t="n">
-        <v>8</v>
+        <v>620</v>
       </c>
       <c r="C2092" s="0" t="inlineStr">
         <is>
-          <t>6, 8</t>
+          <t>6, 4</t>
         </is>
       </c>
       <c r="D2092" s="0" t="inlineStr">
         <is>
-          <t>RIGHT</t>
+          <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2093">
       <c r="A2093" s="9" t="n">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="B2093" s="9" t="n"/>
       <c r="C2093" s="9" t="n"/>
@@ -70720,7 +70720,7 @@
     <row r="2094">
       <c r="A2094" s="9" t="n"/>
       <c r="B2094" s="0" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C2094" s="0" t="inlineStr">
         <is>
@@ -70735,7 +70735,7 @@
     </row>
     <row r="2095">
       <c r="A2095" s="9" t="n">
-        <v>46004</v>
+        <v>46007</v>
       </c>
       <c r="B2095" s="9" t="n"/>
       <c r="C2095" s="9" t="n"/>
@@ -70744,7 +70744,7 @@
     <row r="2096">
       <c r="A2096" s="9" t="n"/>
       <c r="B2096" s="0" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C2096" s="0" t="inlineStr">
         <is>
@@ -70759,7 +70759,7 @@
     </row>
     <row r="2097">
       <c r="A2097" s="9" t="n">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="B2097" s="9" t="n"/>
       <c r="C2097" s="9" t="n"/>
@@ -70768,11 +70768,11 @@
     <row r="2098">
       <c r="A2098" s="9" t="n"/>
       <c r="B2098" s="0" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C2098" s="0" t="inlineStr">
         <is>
-          <t>6, 4</t>
+          <t>62, 14</t>
         </is>
       </c>
       <c r="D2098" s="0" t="inlineStr">
@@ -70783,7 +70783,7 @@
     </row>
     <row r="2099">
       <c r="A2099" s="9" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B2099" s="9" t="n"/>
       <c r="C2099" s="9" t="n"/>
@@ -70792,11 +70792,11 @@
     <row r="2100">
       <c r="A2100" s="9" t="n"/>
       <c r="B2100" s="0" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C2100" s="0" t="inlineStr">
         <is>
-          <t>62, 14</t>
+          <t>4, 4</t>
         </is>
       </c>
       <c r="D2100" s="0" t="inlineStr">
@@ -70807,7 +70807,7 @@
     </row>
     <row r="2101">
       <c r="A2101" s="9" t="n">
-        <v>46002</v>
+        <v>618</v>
       </c>
       <c r="B2101" s="9" t="n"/>
       <c r="C2101" s="9" t="n"/>
@@ -70816,11 +70816,11 @@
     <row r="2102">
       <c r="A2102" s="9" t="n"/>
       <c r="B2102" s="0" t="n">
-        <v>624</v>
+        <v>444</v>
       </c>
       <c r="C2102" s="0" t="inlineStr">
         <is>
-          <t>4, 4</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="D2102" s="0" t="inlineStr">
@@ -70831,7 +70831,7 @@
     </row>
     <row r="2103">
       <c r="A2103" s="9" t="n">
-        <v>618</v>
+        <v>2000</v>
       </c>
       <c r="B2103" s="9" t="n"/>
       <c r="C2103" s="9" t="n"/>
@@ -70839,15 +70839,15 @@
     </row>
     <row r="2104">
       <c r="A2104" s="9" t="n"/>
-      <c r="B2104" s="0" t="n">
-        <v>444</v>
-      </c>
-      <c r="C2104" s="0" t="inlineStr">
-        <is>
-          <t>3, 5</t>
-        </is>
-      </c>
-      <c r="D2104" s="0" t="inlineStr">
+      <c r="B2104" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="C2104" s="9" t="inlineStr">
+        <is>
+          <t>20, 0</t>
+        </is>
+      </c>
+      <c r="D2104" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70855,7 +70855,7 @@
     </row>
     <row r="2105">
       <c r="A2105" s="9" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B2105" s="9" t="n"/>
       <c r="C2105" s="9" t="n"/>
@@ -70863,15 +70863,15 @@
     </row>
     <row r="2106">
       <c r="A2106" s="9" t="n"/>
-      <c r="B2106" s="9" t="n">
+      <c r="B2106" s="0" t="n">
         <v>227</v>
       </c>
-      <c r="C2106" s="9" t="inlineStr">
+      <c r="C2106" s="0" t="inlineStr">
         <is>
           <t>20, 0</t>
         </is>
       </c>
-      <c r="D2106" s="9" t="inlineStr">
+      <c r="D2106" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -70879,7 +70879,7 @@
     </row>
     <row r="2107">
       <c r="A2107" s="9" t="n">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="B2107" s="9" t="n"/>
       <c r="C2107" s="9" t="n"/>
@@ -70903,7 +70903,7 @@
     </row>
     <row r="2109">
       <c r="A2109" s="9" t="n">
-        <v>2003</v>
+        <v>2041</v>
       </c>
       <c r="B2109" s="9" t="n"/>
       <c r="C2109" s="9" t="n"/>
@@ -70927,7 +70927,7 @@
     </row>
     <row r="2111">
       <c r="A2111" s="9" t="n">
-        <v>2041</v>
+        <v>2956</v>
       </c>
       <c r="B2111" s="9" t="n"/>
       <c r="C2111" s="9" t="n"/>
@@ -70936,11 +70936,11 @@
     <row r="2112">
       <c r="A2112" s="9" t="n"/>
       <c r="B2112" s="0" t="n">
-        <v>227</v>
+        <v>600</v>
       </c>
       <c r="C2112" s="0" t="inlineStr">
         <is>
-          <t>20, 0</t>
+          <t>7, 4</t>
         </is>
       </c>
       <c r="D2112" s="0" t="inlineStr">
@@ -70951,7 +70951,7 @@
     </row>
     <row r="2113">
       <c r="A2113" s="9" t="n">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="B2113" s="9" t="n"/>
       <c r="C2113" s="9" t="n"/>
@@ -70960,11 +70960,11 @@
     <row r="2114">
       <c r="A2114" s="9" t="n"/>
       <c r="B2114" s="0" t="n">
-        <v>600</v>
+        <v>458</v>
       </c>
       <c r="C2114" s="0" t="inlineStr">
         <is>
-          <t>7, 4</t>
+          <t>14, 9</t>
         </is>
       </c>
       <c r="D2114" s="0" t="inlineStr">
@@ -70975,7 +70975,7 @@
     </row>
     <row r="2115">
       <c r="A2115" s="9" t="n">
-        <v>2954</v>
+        <v>120</v>
       </c>
       <c r="B2115" s="9" t="n"/>
       <c r="C2115" s="9" t="n"/>
@@ -70984,11 +70984,11 @@
     <row r="2116">
       <c r="A2116" s="9" t="n"/>
       <c r="B2116" s="0" t="n">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="C2116" s="0" t="inlineStr">
         <is>
-          <t>14, 9</t>
+          <t>13, 10</t>
         </is>
       </c>
       <c r="D2116" s="0" t="inlineStr">
@@ -70999,7 +70999,7 @@
     </row>
     <row r="2117">
       <c r="A2117" s="9" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B2117" s="9" t="n"/>
       <c r="C2117" s="9" t="n"/>
@@ -71008,11 +71008,11 @@
     <row r="2118">
       <c r="A2118" s="9" t="n"/>
       <c r="B2118" s="0" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C2118" s="0" t="inlineStr">
         <is>
-          <t>13, 10</t>
+          <t>13, 89</t>
         </is>
       </c>
       <c r="D2118" s="0" t="inlineStr">
@@ -71023,7 +71023,7 @@
     </row>
     <row r="2119">
       <c r="A2119" s="9" t="n">
-        <v>127</v>
+        <v>2442</v>
       </c>
       <c r="B2119" s="9" t="n"/>
       <c r="C2119" s="9" t="n"/>
@@ -71031,15 +71031,15 @@
     </row>
     <row r="2120">
       <c r="A2120" s="9" t="n"/>
-      <c r="B2120" s="0" t="n">
-        <v>501</v>
-      </c>
-      <c r="C2120" s="0" t="inlineStr">
-        <is>
-          <t>13, 89</t>
-        </is>
-      </c>
-      <c r="D2120" s="0" t="inlineStr">
+      <c r="B2120" s="9" t="n">
+        <v>457</v>
+      </c>
+      <c r="C2120" s="9" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
+      <c r="D2120" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71047,11 +71047,8 @@
     </row>
     <row r="2121">
       <c r="A2121" s="9" t="n">
-        <v>2442</v>
-      </c>
-      <c r="B2121" s="9" t="n"/>
-      <c r="C2121" s="9" t="n"/>
-      <c r="D2121" s="9" t="n"/>
+        <v>2443</v>
+      </c>
     </row>
     <row r="2122">
       <c r="A2122" s="9" t="n"/>
@@ -71071,7 +71068,7 @@
     </row>
     <row r="2123">
       <c r="A2123" s="9" t="n">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="2124">
@@ -71092,7 +71089,7 @@
     </row>
     <row r="2125">
       <c r="A2125" s="9" t="n">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="2126">
@@ -71113,7 +71110,7 @@
     </row>
     <row r="2127">
       <c r="A2127" s="9" t="n">
-        <v>2445</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="2128">
@@ -71134,17 +71131,17 @@
     </row>
     <row r="2129">
       <c r="A2129" s="9" t="n">
-        <v>2446</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="2130">
       <c r="A2130" s="9" t="n"/>
       <c r="B2130" s="9" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="C2130" s="9" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>14, 14</t>
         </is>
       </c>
       <c r="D2130" s="9" t="inlineStr">
@@ -71155,17 +71152,17 @@
     </row>
     <row r="2131">
       <c r="A2131" s="9" t="n">
-        <v>1480</v>
+        <v>10265</v>
       </c>
     </row>
     <row r="2132">
       <c r="A2132" s="9" t="n"/>
       <c r="B2132" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C2132" s="9" t="inlineStr">
         <is>
-          <t>14, 14</t>
+          <t>33, 47</t>
         </is>
       </c>
       <c r="D2132" s="9" t="inlineStr">
@@ -71175,18 +71172,29 @@
       </c>
     </row>
     <row r="2133">
-      <c r="A2133" s="9" t="n">
-        <v>10265</v>
+      <c r="A2133" s="9" t="n"/>
+      <c r="B2133" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C2133" s="0" t="inlineStr">
+        <is>
+          <t>37, 47</t>
+        </is>
+      </c>
+      <c r="D2133" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2134">
       <c r="A2134" s="9" t="n"/>
       <c r="B2134" s="9" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C2134" s="9" t="inlineStr">
         <is>
-          <t>33, 47</t>
+          <t>35, 48</t>
         </is>
       </c>
       <c r="D2134" s="9" t="inlineStr">
@@ -71196,29 +71204,18 @@
       </c>
     </row>
     <row r="2135">
-      <c r="A2135" s="9" t="n"/>
-      <c r="B2135" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2135" s="0" t="inlineStr">
-        <is>
-          <t>37, 47</t>
-        </is>
-      </c>
-      <c r="D2135" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2135" s="9" t="n">
+        <v>10934</v>
       </c>
     </row>
     <row r="2136">
       <c r="A2136" s="9" t="n"/>
       <c r="B2136" s="9" t="n">
-        <v>8</v>
+        <v>353</v>
       </c>
       <c r="C2136" s="9" t="inlineStr">
         <is>
-          <t>35, 48</t>
+          <t>9, 9</t>
         </is>
       </c>
       <c r="D2136" s="9" t="inlineStr">
@@ -71229,17 +71226,17 @@
     </row>
     <row r="2137">
       <c r="A2137" s="9" t="n">
-        <v>10934</v>
+        <v>10935</v>
       </c>
     </row>
     <row r="2138">
       <c r="A2138" s="9" t="n"/>
       <c r="B2138" s="9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C2138" s="9" t="inlineStr">
         <is>
-          <t>9, 9</t>
+          <t>7, 6</t>
         </is>
       </c>
       <c r="D2138" s="9" t="inlineStr">
@@ -71250,17 +71247,20 @@
     </row>
     <row r="2139">
       <c r="A2139" s="9" t="n">
-        <v>10935</v>
-      </c>
+        <v>10936</v>
+      </c>
+      <c r="B2139" s="9" t="n"/>
+      <c r="C2139" s="9" t="n"/>
+      <c r="D2139" s="9" t="n"/>
     </row>
     <row r="2140">
       <c r="A2140" s="9" t="n"/>
       <c r="B2140" s="9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C2140" s="9" t="inlineStr">
         <is>
-          <t>7, 6</t>
+          <t>12, 5</t>
         </is>
       </c>
       <c r="D2140" s="9" t="inlineStr">
@@ -71271,7 +71271,7 @@
     </row>
     <row r="2141">
       <c r="A2141" s="9" t="n">
-        <v>10936</v>
+        <v>10937</v>
       </c>
       <c r="B2141" s="9" t="n"/>
       <c r="C2141" s="9" t="n"/>
@@ -71280,11 +71280,11 @@
     <row r="2142">
       <c r="A2142" s="9" t="n"/>
       <c r="B2142" s="9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C2142" s="9" t="inlineStr">
         <is>
-          <t>12, 5</t>
+          <t>4, 4</t>
         </is>
       </c>
       <c r="D2142" s="9" t="inlineStr">
@@ -71295,7 +71295,7 @@
     </row>
     <row r="2143">
       <c r="A2143" s="9" t="n">
-        <v>10937</v>
+        <v>10938</v>
       </c>
       <c r="B2143" s="9" t="n"/>
       <c r="C2143" s="9" t="n"/>
@@ -71304,11 +71304,11 @@
     <row r="2144">
       <c r="A2144" s="9" t="n"/>
       <c r="B2144" s="9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C2144" s="9" t="inlineStr">
         <is>
-          <t>4, 4</t>
+          <t>9, 10</t>
         </is>
       </c>
       <c r="D2144" s="9" t="inlineStr">
@@ -71319,7 +71319,7 @@
     </row>
     <row r="2145">
       <c r="A2145" s="9" t="n">
-        <v>10938</v>
+        <v>10939</v>
       </c>
       <c r="B2145" s="9" t="n"/>
       <c r="C2145" s="9" t="n"/>
@@ -71328,11 +71328,11 @@
     <row r="2146">
       <c r="A2146" s="9" t="n"/>
       <c r="B2146" s="9" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C2146" s="9" t="inlineStr">
         <is>
-          <t>9, 10</t>
+          <t>5, 5</t>
         </is>
       </c>
       <c r="D2146" s="9" t="inlineStr">
@@ -71343,7 +71343,7 @@
     </row>
     <row r="2147">
       <c r="A2147" s="9" t="n">
-        <v>10939</v>
+        <v>10940</v>
       </c>
       <c r="B2147" s="9" t="n"/>
       <c r="C2147" s="9" t="n"/>
@@ -71352,11 +71352,11 @@
     <row r="2148">
       <c r="A2148" s="9" t="n"/>
       <c r="B2148" s="9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C2148" s="9" t="inlineStr">
         <is>
-          <t>5, 5</t>
+          <t>7, 4</t>
         </is>
       </c>
       <c r="D2148" s="9" t="inlineStr">
@@ -71366,37 +71366,37 @@
       </c>
     </row>
     <row r="2149">
-      <c r="A2149" s="9" t="n">
-        <v>10940</v>
-      </c>
-      <c r="B2149" s="9" t="n"/>
-      <c r="C2149" s="9" t="n"/>
-      <c r="D2149" s="9" t="n"/>
+      <c r="A2149" s="9" t="n"/>
+      <c r="B2149" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="C2149" s="9" t="inlineStr">
+        <is>
+          <t>8, 4</t>
+        </is>
+      </c>
+      <c r="D2149" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2150">
-      <c r="A2150" s="9" t="n"/>
-      <c r="B2150" s="9" t="n">
-        <v>359</v>
-      </c>
-      <c r="C2150" s="9" t="inlineStr">
-        <is>
-          <t>7, 4</t>
-        </is>
-      </c>
-      <c r="D2150" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A2150" s="9" t="n">
+        <v>10941</v>
+      </c>
+      <c r="B2150" s="9" t="n"/>
+      <c r="C2150" s="9" t="n"/>
+      <c r="D2150" s="9" t="n"/>
     </row>
     <row r="2151">
       <c r="A2151" s="9" t="n"/>
       <c r="B2151" s="9" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C2151" s="9" t="inlineStr">
         <is>
-          <t>8, 4</t>
+          <t>9, 3</t>
         </is>
       </c>
       <c r="D2151" s="9" t="inlineStr">
@@ -71407,7 +71407,7 @@
     </row>
     <row r="2152">
       <c r="A2152" s="9" t="n">
-        <v>10941</v>
+        <v>10942</v>
       </c>
       <c r="B2152" s="9" t="n"/>
       <c r="C2152" s="9" t="n"/>
@@ -71416,11 +71416,11 @@
     <row r="2153">
       <c r="A2153" s="9" t="n"/>
       <c r="B2153" s="9" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C2153" s="9" t="inlineStr">
         <is>
-          <t>9, 3</t>
+          <t>12, 4</t>
         </is>
       </c>
       <c r="D2153" s="9" t="inlineStr">
@@ -71431,20 +71431,17 @@
     </row>
     <row r="2154">
       <c r="A2154" s="9" t="n">
-        <v>10942</v>
-      </c>
-      <c r="B2154" s="9" t="n"/>
-      <c r="C2154" s="9" t="n"/>
-      <c r="D2154" s="9" t="n"/>
+        <v>10943</v>
+      </c>
     </row>
     <row r="2155">
       <c r="A2155" s="9" t="n"/>
       <c r="B2155" s="9" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C2155" s="9" t="inlineStr">
         <is>
-          <t>12, 4</t>
+          <t>5, 5</t>
         </is>
       </c>
       <c r="D2155" s="9" t="inlineStr">
@@ -71455,17 +71452,20 @@
     </row>
     <row r="2156">
       <c r="A2156" s="9" t="n">
-        <v>10943</v>
-      </c>
+        <v>10948</v>
+      </c>
+      <c r="B2156" s="9" t="n"/>
+      <c r="C2156" s="9" t="n"/>
+      <c r="D2156" s="9" t="n"/>
     </row>
     <row r="2157">
       <c r="A2157" s="9" t="n"/>
       <c r="B2157" s="9" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2157" s="9" t="inlineStr">
         <is>
-          <t>5, 5</t>
+          <t>11, 16</t>
         </is>
       </c>
       <c r="D2157" s="9" t="inlineStr">
@@ -71476,7 +71476,7 @@
     </row>
     <row r="2158">
       <c r="A2158" s="9" t="n">
-        <v>10948</v>
+        <v>10950</v>
       </c>
       <c r="B2158" s="9" t="n"/>
       <c r="C2158" s="9" t="n"/>
@@ -71485,11 +71485,11 @@
     <row r="2159">
       <c r="A2159" s="9" t="n"/>
       <c r="B2159" s="9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C2159" s="9" t="inlineStr">
         <is>
-          <t>11, 16</t>
+          <t>12, 6</t>
         </is>
       </c>
       <c r="D2159" s="9" t="inlineStr">
@@ -71500,20 +71500,17 @@
     </row>
     <row r="2160">
       <c r="A2160" s="9" t="n">
-        <v>10950</v>
-      </c>
-      <c r="B2160" s="9" t="n"/>
-      <c r="C2160" s="9" t="n"/>
-      <c r="D2160" s="9" t="n"/>
+        <v>10953</v>
+      </c>
     </row>
     <row r="2161">
       <c r="A2161" s="9" t="n"/>
       <c r="B2161" s="9" t="n">
-        <v>365</v>
+        <v>548</v>
       </c>
       <c r="C2161" s="9" t="inlineStr">
         <is>
-          <t>12, 6</t>
+          <t>6, 34</t>
         </is>
       </c>
       <c r="D2161" s="9" t="inlineStr">
@@ -71524,17 +71521,17 @@
     </row>
     <row r="2162">
       <c r="A2162" s="9" t="n">
-        <v>10953</v>
+        <v>10947</v>
       </c>
     </row>
     <row r="2163">
       <c r="A2163" s="9" t="n"/>
       <c r="B2163" s="9" t="n">
-        <v>548</v>
+        <v>227</v>
       </c>
       <c r="C2163" s="9" t="inlineStr">
         <is>
-          <t>6, 34</t>
+          <t>0, 11</t>
         </is>
       </c>
       <c r="D2163" s="9" t="inlineStr">
@@ -71545,17 +71542,17 @@
     </row>
     <row r="2164">
       <c r="A2164" s="9" t="n">
-        <v>10947</v>
+        <v>10945</v>
       </c>
     </row>
     <row r="2165">
       <c r="A2165" s="9" t="n"/>
       <c r="B2165" s="9" t="n">
-        <v>227</v>
+        <v>497</v>
       </c>
       <c r="C2165" s="9" t="inlineStr">
         <is>
-          <t>0, 11</t>
+          <t>23, 20</t>
         </is>
       </c>
       <c r="D2165" s="9" t="inlineStr">
@@ -71566,32 +71563,43 @@
     </row>
     <row r="2166">
       <c r="A2166" s="9" t="n">
-        <v>10945</v>
-      </c>
+        <v>14401</v>
+      </c>
+      <c r="B2166" s="9" t="n"/>
+      <c r="C2166" s="9" t="n"/>
+      <c r="D2166" s="9" t="n"/>
     </row>
     <row r="2167">
       <c r="A2167" s="9" t="n"/>
-      <c r="B2167" s="9" t="n">
-        <v>497</v>
-      </c>
-      <c r="C2167" s="9" t="inlineStr">
-        <is>
-          <t>23, 20</t>
-        </is>
-      </c>
-      <c r="D2167" s="9" t="inlineStr">
+      <c r="B2167" s="0" t="n">
+        <v>338</v>
+      </c>
+      <c r="C2167" s="0" t="inlineStr">
+        <is>
+          <t>25, 25</t>
+        </is>
+      </c>
+      <c r="D2167" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2168">
-      <c r="A2168" s="9" t="n">
-        <v>14401</v>
-      </c>
-      <c r="B2168" s="9" t="n"/>
-      <c r="C2168" s="9" t="n"/>
-      <c r="D2168" s="9" t="n"/>
+      <c r="A2168" s="9" t="n"/>
+      <c r="B2168" s="9" t="n">
+        <v>338</v>
+      </c>
+      <c r="C2168" s="9" t="inlineStr">
+        <is>
+          <t>25, 75</t>
+        </is>
+      </c>
+      <c r="D2168" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2169">
       <c r="A2169" s="9" t="n"/>
@@ -71600,7 +71608,7 @@
       </c>
       <c r="C2169" s="0" t="inlineStr">
         <is>
-          <t>25, 25</t>
+          <t>25, 125</t>
         </is>
       </c>
       <c r="D2169" s="0" t="inlineStr">
@@ -71616,7 +71624,7 @@
       </c>
       <c r="C2170" s="9" t="inlineStr">
         <is>
-          <t>25, 75</t>
+          <t>25, 175</t>
         </is>
       </c>
       <c r="D2170" s="9" t="inlineStr">
@@ -71632,7 +71640,7 @@
       </c>
       <c r="C2171" s="0" t="inlineStr">
         <is>
-          <t>25, 125</t>
+          <t>75, 25</t>
         </is>
       </c>
       <c r="D2171" s="0" t="inlineStr">
@@ -71648,7 +71656,7 @@
       </c>
       <c r="C2172" s="9" t="inlineStr">
         <is>
-          <t>25, 175</t>
+          <t>75, 75</t>
         </is>
       </c>
       <c r="D2172" s="9" t="inlineStr">
@@ -71664,7 +71672,7 @@
       </c>
       <c r="C2173" s="0" t="inlineStr">
         <is>
-          <t>75, 25</t>
+          <t>75, 125</t>
         </is>
       </c>
       <c r="D2173" s="0" t="inlineStr">
@@ -71680,7 +71688,7 @@
       </c>
       <c r="C2174" s="9" t="inlineStr">
         <is>
-          <t>75, 75</t>
+          <t>75, 175</t>
         </is>
       </c>
       <c r="D2174" s="9" t="inlineStr">
@@ -71696,7 +71704,7 @@
       </c>
       <c r="C2175" s="0" t="inlineStr">
         <is>
-          <t>75, 125</t>
+          <t>125, 25</t>
         </is>
       </c>
       <c r="D2175" s="0" t="inlineStr">
@@ -71712,7 +71720,7 @@
       </c>
       <c r="C2176" s="9" t="inlineStr">
         <is>
-          <t>75, 175</t>
+          <t>125, 75</t>
         </is>
       </c>
       <c r="D2176" s="9" t="inlineStr">
@@ -71728,7 +71736,7 @@
       </c>
       <c r="C2177" s="0" t="inlineStr">
         <is>
-          <t>125, 25</t>
+          <t>125, 125</t>
         </is>
       </c>
       <c r="D2177" s="0" t="inlineStr">
@@ -71744,7 +71752,7 @@
       </c>
       <c r="C2178" s="9" t="inlineStr">
         <is>
-          <t>125, 75</t>
+          <t>125, 175</t>
         </is>
       </c>
       <c r="D2178" s="9" t="inlineStr">
@@ -71760,7 +71768,7 @@
       </c>
       <c r="C2179" s="0" t="inlineStr">
         <is>
-          <t>125, 125</t>
+          <t>175, 25</t>
         </is>
       </c>
       <c r="D2179" s="0" t="inlineStr">
@@ -71776,7 +71784,7 @@
       </c>
       <c r="C2180" s="9" t="inlineStr">
         <is>
-          <t>125, 175</t>
+          <t>175, 75</t>
         </is>
       </c>
       <c r="D2180" s="9" t="inlineStr">
@@ -71792,7 +71800,7 @@
       </c>
       <c r="C2181" s="0" t="inlineStr">
         <is>
-          <t>175, 25</t>
+          <t>175, 125</t>
         </is>
       </c>
       <c r="D2181" s="0" t="inlineStr">
@@ -71808,7 +71816,7 @@
       </c>
       <c r="C2182" s="9" t="inlineStr">
         <is>
-          <t>175, 75</t>
+          <t>175, 175</t>
         </is>
       </c>
       <c r="D2182" s="9" t="inlineStr">
@@ -71818,29 +71826,18 @@
       </c>
     </row>
     <row r="2183">
-      <c r="A2183" s="9" t="n"/>
-      <c r="B2183" s="0" t="n">
-        <v>338</v>
-      </c>
-      <c r="C2183" s="0" t="inlineStr">
-        <is>
-          <t>175, 125</t>
-        </is>
-      </c>
-      <c r="D2183" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2183" s="9" t="n">
+        <v>2386</v>
       </c>
     </row>
     <row r="2184">
       <c r="A2184" s="9" t="n"/>
       <c r="B2184" s="9" t="n">
-        <v>338</v>
+        <v>22</v>
       </c>
       <c r="C2184" s="9" t="inlineStr">
         <is>
-          <t>175, 175</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="D2184" s="9" t="inlineStr">
@@ -71850,21 +71847,32 @@
       </c>
     </row>
     <row r="2185">
-      <c r="A2185" s="9" t="n">
-        <v>2386</v>
+      <c r="A2185" s="9" t="n"/>
+      <c r="B2185" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2185" s="9" t="inlineStr">
+        <is>
+          <t>3, 2</t>
+        </is>
+      </c>
+      <c r="D2185" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2186">
       <c r="A2186" s="9" t="n"/>
-      <c r="B2186" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="C2186" s="9" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-      <c r="D2186" s="9" t="inlineStr">
+      <c r="B2186" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2186" s="0" t="inlineStr">
+        <is>
+          <t>1, 4</t>
+        </is>
+      </c>
+      <c r="D2186" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -71873,11 +71881,11 @@
     <row r="2187">
       <c r="A2187" s="9" t="n"/>
       <c r="B2187" s="9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2187" s="9" t="inlineStr">
         <is>
-          <t>3, 2</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D2187" s="9" t="inlineStr">
@@ -71889,11 +71897,11 @@
     <row r="2188">
       <c r="A2188" s="9" t="n"/>
       <c r="B2188" s="0" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C2188" s="0" t="inlineStr">
         <is>
-          <t>1, 4</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="D2188" s="0" t="inlineStr">
@@ -71905,11 +71913,11 @@
     <row r="2189">
       <c r="A2189" s="9" t="n"/>
       <c r="B2189" s="9" t="n">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="C2189" s="9" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>1, 6</t>
         </is>
       </c>
       <c r="D2189" s="9" t="inlineStr">
@@ -71919,29 +71927,18 @@
       </c>
     </row>
     <row r="2190">
-      <c r="A2190" s="9" t="n"/>
-      <c r="B2190" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="C2190" s="0" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D2190" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2190" s="9" t="n">
+        <v>10612</v>
       </c>
     </row>
     <row r="2191">
       <c r="A2191" s="9" t="n"/>
       <c r="B2191" s="9" t="n">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="C2191" s="9" t="inlineStr">
         <is>
-          <t>1, 6</t>
+          <t>16, 7</t>
         </is>
       </c>
       <c r="D2191" s="9" t="inlineStr">
@@ -71952,17 +71949,17 @@
     </row>
     <row r="2192">
       <c r="A2192" s="9" t="n">
-        <v>10612</v>
+        <v>10546</v>
       </c>
     </row>
     <row r="2193">
       <c r="A2193" s="9" t="n"/>
       <c r="B2193" s="9" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C2193" s="9" t="inlineStr">
         <is>
-          <t>16, 7</t>
+          <t>16, 14</t>
         </is>
       </c>
       <c r="D2193" s="9" t="inlineStr">
@@ -71973,17 +71970,17 @@
     </row>
     <row r="2194">
       <c r="A2194" s="9" t="n">
-        <v>10546</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="2195">
       <c r="A2195" s="9" t="n"/>
       <c r="B2195" s="9" t="n">
-        <v>308</v>
+        <v>480</v>
       </c>
       <c r="C2195" s="9" t="inlineStr">
         <is>
-          <t>16, 14</t>
+          <t>6, 6</t>
         </is>
       </c>
       <c r="D2195" s="9" t="inlineStr">
@@ -71993,34 +71990,37 @@
       </c>
     </row>
     <row r="2196">
-      <c r="A2196" s="9" t="n">
-        <v>2435</v>
+      <c r="A2196" s="9" t="n"/>
+      <c r="B2196" s="0" t="n">
+        <v>481</v>
+      </c>
+      <c r="C2196" s="0" t="inlineStr">
+        <is>
+          <t>9, 6</t>
+        </is>
+      </c>
+      <c r="D2196" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2197">
-      <c r="A2197" s="9" t="n"/>
-      <c r="B2197" s="9" t="n">
-        <v>480</v>
-      </c>
-      <c r="C2197" s="9" t="inlineStr">
-        <is>
-          <t>6, 6</t>
-        </is>
-      </c>
-      <c r="D2197" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A2197" s="9" t="n">
+        <v>2428</v>
+      </c>
+      <c r="B2197" s="9" t="n"/>
+      <c r="C2197" s="9" t="n"/>
+      <c r="D2197" s="9" t="n"/>
     </row>
     <row r="2198">
       <c r="A2198" s="9" t="n"/>
       <c r="B2198" s="0" t="n">
-        <v>481</v>
+        <v>284</v>
       </c>
       <c r="C2198" s="0" t="inlineStr">
         <is>
-          <t>9, 6</t>
+          <t>2, 4</t>
         </is>
       </c>
       <c r="D2198" s="0" t="inlineStr">
@@ -72031,7 +72031,7 @@
     </row>
     <row r="2199">
       <c r="A2199" s="9" t="n">
-        <v>2428</v>
+        <v>2433</v>
       </c>
       <c r="B2199" s="9" t="n"/>
       <c r="C2199" s="9" t="n"/>
@@ -72040,7 +72040,7 @@
     <row r="2200">
       <c r="A2200" s="9" t="n"/>
       <c r="B2200" s="0" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C2200" s="0" t="inlineStr">
         <is>
@@ -72055,7 +72055,7 @@
     </row>
     <row r="2201">
       <c r="A2201" s="9" t="n">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="B2201" s="9" t="n"/>
       <c r="C2201" s="9" t="n"/>
@@ -72063,15 +72063,15 @@
     </row>
     <row r="2202">
       <c r="A2202" s="9" t="n"/>
-      <c r="B2202" s="0" t="n">
-        <v>281</v>
-      </c>
-      <c r="C2202" s="0" t="inlineStr">
+      <c r="B2202" s="9" t="n">
+        <v>282</v>
+      </c>
+      <c r="C2202" s="9" t="inlineStr">
         <is>
           <t>2, 4</t>
         </is>
       </c>
-      <c r="D2202" s="0" t="inlineStr">
+      <c r="D2202" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72079,16 +72079,13 @@
     </row>
     <row r="2203">
       <c r="A2203" s="9" t="n">
-        <v>2436</v>
-      </c>
-      <c r="B2203" s="9" t="n"/>
-      <c r="C2203" s="9" t="n"/>
-      <c r="D2203" s="9" t="n"/>
+        <v>2439</v>
+      </c>
     </row>
     <row r="2204">
       <c r="A2204" s="9" t="n"/>
       <c r="B2204" s="9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2204" s="9" t="inlineStr">
         <is>
@@ -72103,17 +72100,20 @@
     </row>
     <row r="2205">
       <c r="A2205" s="9" t="n">
-        <v>2439</v>
-      </c>
+        <v>2429</v>
+      </c>
+      <c r="B2205" s="9" t="n"/>
+      <c r="C2205" s="9" t="n"/>
+      <c r="D2205" s="9" t="n"/>
     </row>
     <row r="2206">
       <c r="A2206" s="9" t="n"/>
       <c r="B2206" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C2206" s="9" t="inlineStr">
         <is>
-          <t>2, 4</t>
+          <t>14, 11</t>
         </is>
       </c>
       <c r="D2206" s="9" t="inlineStr">
@@ -72124,7 +72124,7 @@
     </row>
     <row r="2207">
       <c r="A2207" s="9" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="B2207" s="9" t="n"/>
       <c r="C2207" s="9" t="n"/>
@@ -72132,15 +72132,15 @@
     </row>
     <row r="2208">
       <c r="A2208" s="9" t="n"/>
-      <c r="B2208" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="C2208" s="9" t="inlineStr">
+      <c r="B2208" s="0" t="n">
+        <v>286</v>
+      </c>
+      <c r="C2208" s="0" t="inlineStr">
         <is>
           <t>14, 11</t>
         </is>
       </c>
-      <c r="D2208" s="9" t="inlineStr">
+      <c r="D2208" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72148,7 +72148,7 @@
     </row>
     <row r="2209">
       <c r="A2209" s="9" t="n">
-        <v>2430</v>
+        <v>2399</v>
       </c>
       <c r="B2209" s="9" t="n"/>
       <c r="C2209" s="9" t="n"/>
@@ -72156,15 +72156,15 @@
     </row>
     <row r="2210">
       <c r="A2210" s="9" t="n"/>
-      <c r="B2210" s="0" t="n">
-        <v>286</v>
-      </c>
-      <c r="C2210" s="0" t="inlineStr">
-        <is>
-          <t>14, 11</t>
-        </is>
-      </c>
-      <c r="D2210" s="0" t="inlineStr">
+      <c r="B2210" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="C2210" s="9" t="inlineStr">
+        <is>
+          <t>17, 17</t>
+        </is>
+      </c>
+      <c r="D2210" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72172,7 +72172,7 @@
     </row>
     <row r="2211">
       <c r="A2211" s="9" t="n">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="B2211" s="9" t="n"/>
       <c r="C2211" s="9" t="n"/>
@@ -72180,15 +72180,15 @@
     </row>
     <row r="2212">
       <c r="A2212" s="9" t="n"/>
-      <c r="B2212" s="9" t="n">
-        <v>275</v>
-      </c>
-      <c r="C2212" s="9" t="inlineStr">
-        <is>
-          <t>17, 17</t>
-        </is>
-      </c>
-      <c r="D2212" s="9" t="inlineStr">
+      <c r="B2212" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C2212" s="0" t="inlineStr">
+        <is>
+          <t>3, 4</t>
+        </is>
+      </c>
+      <c r="D2212" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72196,7 +72196,7 @@
     </row>
     <row r="2213">
       <c r="A2213" s="9" t="n">
-        <v>2397</v>
+        <v>1947</v>
       </c>
       <c r="B2213" s="9" t="n"/>
       <c r="C2213" s="9" t="n"/>
@@ -72204,52 +72204,49 @@
     </row>
     <row r="2214">
       <c r="A2214" s="9" t="n"/>
-      <c r="B2214" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="C2214" s="0" t="inlineStr">
-        <is>
-          <t>3, 4</t>
-        </is>
-      </c>
-      <c r="D2214" s="0" t="inlineStr">
+      <c r="B2214" s="9" t="n">
+        <v>221</v>
+      </c>
+      <c r="C2214" s="9" t="inlineStr">
+        <is>
+          <t>14, 6</t>
+        </is>
+      </c>
+      <c r="D2214" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2215">
-      <c r="A2215" s="9" t="n">
-        <v>1947</v>
-      </c>
-      <c r="B2215" s="9" t="n"/>
-      <c r="C2215" s="9" t="n"/>
-      <c r="D2215" s="9" t="n"/>
+      <c r="A2215" s="9" t="n"/>
+      <c r="B2215" s="9" t="n">
+        <v>222</v>
+      </c>
+      <c r="C2215" s="9" t="inlineStr">
+        <is>
+          <t>9, 4</t>
+        </is>
+      </c>
+      <c r="D2215" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2216">
-      <c r="A2216" s="9" t="n"/>
-      <c r="B2216" s="9" t="n">
-        <v>221</v>
-      </c>
-      <c r="C2216" s="9" t="inlineStr">
-        <is>
-          <t>14, 6</t>
-        </is>
-      </c>
-      <c r="D2216" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2216" s="9" t="n">
+        <v>2410</v>
       </c>
     </row>
     <row r="2217">
       <c r="A2217" s="9" t="n"/>
       <c r="B2217" s="9" t="n">
-        <v>222</v>
+        <v>549</v>
       </c>
       <c r="C2217" s="9" t="inlineStr">
         <is>
-          <t>9, 4</t>
+          <t>9, 8</t>
         </is>
       </c>
       <c r="D2217" s="9" t="inlineStr">
@@ -72260,17 +72257,17 @@
     </row>
     <row r="2218">
       <c r="A2218" s="9" t="n">
-        <v>2410</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="2219">
       <c r="A2219" s="9" t="n"/>
       <c r="B2219" s="9" t="n">
-        <v>549</v>
+        <v>451</v>
       </c>
       <c r="C2219" s="9" t="inlineStr">
         <is>
-          <t>9, 8</t>
+          <t>13, 6</t>
         </is>
       </c>
       <c r="D2219" s="9" t="inlineStr">
@@ -72281,17 +72278,17 @@
     </row>
     <row r="2220">
       <c r="A2220" s="9" t="n">
-        <v>2533</v>
+        <v>987</v>
       </c>
     </row>
     <row r="2221">
       <c r="A2221" s="9" t="n"/>
       <c r="B2221" s="9" t="n">
-        <v>451</v>
+        <v>377</v>
       </c>
       <c r="C2221" s="9" t="inlineStr">
         <is>
-          <t>13, 6</t>
+          <t>19, 9</t>
         </is>
       </c>
       <c r="D2221" s="9" t="inlineStr">
@@ -72302,20 +72299,23 @@
     </row>
     <row r="2222">
       <c r="A2222" s="9" t="n">
-        <v>987</v>
-      </c>
+        <v>994</v>
+      </c>
+      <c r="B2222" s="9" t="n"/>
+      <c r="C2222" s="9" t="n"/>
+      <c r="D2222" s="9" t="n"/>
     </row>
     <row r="2223">
       <c r="A2223" s="9" t="n"/>
-      <c r="B2223" s="9" t="n">
-        <v>377</v>
-      </c>
-      <c r="C2223" s="9" t="inlineStr">
-        <is>
-          <t>19, 9</t>
-        </is>
-      </c>
-      <c r="D2223" s="9" t="inlineStr">
+      <c r="B2223" s="0" t="n">
+        <v>271</v>
+      </c>
+      <c r="C2223" s="0" t="inlineStr">
+        <is>
+          <t>6, 8</t>
+        </is>
+      </c>
+      <c r="D2223" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72323,7 +72323,7 @@
     </row>
     <row r="2224">
       <c r="A2224" s="9" t="n">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B2224" s="9" t="n"/>
       <c r="C2224" s="9" t="n"/>
@@ -72332,11 +72332,11 @@
     <row r="2225">
       <c r="A2225" s="9" t="n"/>
       <c r="B2225" s="0" t="n">
-        <v>271</v>
+        <v>110</v>
       </c>
       <c r="C2225" s="0" t="inlineStr">
         <is>
-          <t>6, 8</t>
+          <t>5, 10</t>
         </is>
       </c>
       <c r="D2225" s="0" t="inlineStr">
@@ -72347,7 +72347,7 @@
     </row>
     <row r="2226">
       <c r="A2226" s="9" t="n">
-        <v>1000</v>
+        <v>14503</v>
       </c>
       <c r="B2226" s="9" t="n"/>
       <c r="C2226" s="9" t="n"/>
@@ -72356,11 +72356,11 @@
     <row r="2227">
       <c r="A2227" s="9" t="n"/>
       <c r="B2227" s="0" t="n">
-        <v>110</v>
+        <v>368</v>
       </c>
       <c r="C2227" s="0" t="inlineStr">
         <is>
-          <t>5, 10</t>
+          <t>10, 8</t>
         </is>
       </c>
       <c r="D2227" s="0" t="inlineStr">
@@ -72371,7 +72371,7 @@
     </row>
     <row r="2228">
       <c r="A2228" s="9" t="n">
-        <v>14503</v>
+        <v>976</v>
       </c>
       <c r="B2228" s="9" t="n"/>
       <c r="C2228" s="9" t="n"/>
@@ -72380,11 +72380,11 @@
     <row r="2229">
       <c r="A2229" s="9" t="n"/>
       <c r="B2229" s="0" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C2229" s="0" t="inlineStr">
         <is>
-          <t>10, 8</t>
+          <t>45, 2</t>
         </is>
       </c>
       <c r="D2229" s="0" t="inlineStr">
@@ -72395,7 +72395,7 @@
     </row>
     <row r="2230">
       <c r="A2230" s="9" t="n">
-        <v>976</v>
+        <v>14502</v>
       </c>
       <c r="B2230" s="9" t="n"/>
       <c r="C2230" s="9" t="n"/>
@@ -72404,11 +72404,11 @@
     <row r="2231">
       <c r="A2231" s="9" t="n"/>
       <c r="B2231" s="0" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C2231" s="0" t="inlineStr">
         <is>
-          <t>45, 2</t>
+          <t>6, 3</t>
         </is>
       </c>
       <c r="D2231" s="0" t="inlineStr">
@@ -72418,37 +72418,34 @@
       </c>
     </row>
     <row r="2232">
-      <c r="A2232" s="9" t="n">
-        <v>14502</v>
-      </c>
-      <c r="B2232" s="9" t="n"/>
-      <c r="C2232" s="9" t="n"/>
-      <c r="D2232" s="9" t="n"/>
+      <c r="A2232" s="9" t="n"/>
+      <c r="B2232" s="9" t="n">
+        <v>372</v>
+      </c>
+      <c r="C2232" s="9" t="inlineStr">
+        <is>
+          <t>8, 3</t>
+        </is>
+      </c>
+      <c r="D2232" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2233">
-      <c r="A2233" s="9" t="n"/>
-      <c r="B2233" s="0" t="n">
-        <v>371</v>
-      </c>
-      <c r="C2233" s="0" t="inlineStr">
-        <is>
-          <t>6, 3</t>
-        </is>
-      </c>
-      <c r="D2233" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2233" s="9" t="n">
+        <v>856</v>
       </c>
     </row>
     <row r="2234">
       <c r="A2234" s="9" t="n"/>
       <c r="B2234" s="9" t="n">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C2234" s="9" t="inlineStr">
         <is>
-          <t>8, 3</t>
+          <t>76, 13</t>
         </is>
       </c>
       <c r="D2234" s="9" t="inlineStr">
@@ -72458,18 +72455,29 @@
       </c>
     </row>
     <row r="2235">
-      <c r="A2235" s="9" t="n">
-        <v>856</v>
+      <c r="A2235" s="9" t="n"/>
+      <c r="B2235" s="0" t="n">
+        <v>395</v>
+      </c>
+      <c r="C2235" s="0" t="inlineStr">
+        <is>
+          <t>83, 12</t>
+        </is>
+      </c>
+      <c r="D2235" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2236">
       <c r="A2236" s="9" t="n"/>
       <c r="B2236" s="9" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C2236" s="9" t="inlineStr">
         <is>
-          <t>76, 13</t>
+          <t>36, 13</t>
         </is>
       </c>
       <c r="D2236" s="9" t="inlineStr">
@@ -72481,11 +72489,11 @@
     <row r="2237">
       <c r="A2237" s="9" t="n"/>
       <c r="B2237" s="0" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C2237" s="0" t="inlineStr">
         <is>
-          <t>83, 12</t>
+          <t>42, 15</t>
         </is>
       </c>
       <c r="D2237" s="0" t="inlineStr">
@@ -72495,29 +72503,21 @@
       </c>
     </row>
     <row r="2238">
-      <c r="A2238" s="9" t="n"/>
-      <c r="B2238" s="9" t="n">
-        <v>396</v>
-      </c>
-      <c r="C2238" s="9" t="inlineStr">
-        <is>
-          <t>36, 13</t>
-        </is>
-      </c>
-      <c r="D2238" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A2238" s="9" t="n">
+        <v>857</v>
+      </c>
+      <c r="B2238" s="9" t="n"/>
+      <c r="C2238" s="9" t="n"/>
+      <c r="D2238" s="9" t="n"/>
     </row>
     <row r="2239">
       <c r="A2239" s="9" t="n"/>
       <c r="B2239" s="0" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C2239" s="0" t="inlineStr">
         <is>
-          <t>42, 15</t>
+          <t>24, 52</t>
         </is>
       </c>
       <c r="D2239" s="0" t="inlineStr">
@@ -72527,21 +72527,29 @@
       </c>
     </row>
     <row r="2240">
-      <c r="A2240" s="9" t="n">
-        <v>857</v>
-      </c>
-      <c r="B2240" s="9" t="n"/>
-      <c r="C2240" s="9" t="n"/>
-      <c r="D2240" s="9" t="n"/>
+      <c r="A2240" s="9" t="n"/>
+      <c r="B2240" s="9" t="n">
+        <v>399</v>
+      </c>
+      <c r="C2240" s="9" t="inlineStr">
+        <is>
+          <t>20, 84</t>
+        </is>
+      </c>
+      <c r="D2240" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2241">
       <c r="A2241" s="9" t="n"/>
       <c r="B2241" s="0" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C2241" s="0" t="inlineStr">
         <is>
-          <t>24, 52</t>
+          <t>9, 61</t>
         </is>
       </c>
       <c r="D2241" s="0" t="inlineStr">
@@ -72551,53 +72559,53 @@
       </c>
     </row>
     <row r="2242">
-      <c r="A2242" s="9" t="n"/>
-      <c r="B2242" s="9" t="n">
-        <v>399</v>
-      </c>
-      <c r="C2242" s="9" t="inlineStr">
-        <is>
-          <t>20, 84</t>
-        </is>
-      </c>
-      <c r="D2242" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
+      <c r="A2242" s="9" t="n">
+        <v>859</v>
+      </c>
+      <c r="B2242" s="9" t="n"/>
+      <c r="C2242" s="9" t="n"/>
+      <c r="D2242" s="9" t="n"/>
     </row>
     <row r="2243">
       <c r="A2243" s="9" t="n"/>
-      <c r="B2243" s="0" t="n">
-        <v>400</v>
-      </c>
-      <c r="C2243" s="0" t="inlineStr">
-        <is>
-          <t>9, 61</t>
-        </is>
-      </c>
-      <c r="D2243" s="0" t="inlineStr">
+      <c r="B2243" s="9" t="n">
+        <v>404</v>
+      </c>
+      <c r="C2243" s="9" t="inlineStr">
+        <is>
+          <t>55, 19</t>
+        </is>
+      </c>
+      <c r="D2243" s="9" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
       </c>
     </row>
     <row r="2244">
-      <c r="A2244" s="9" t="n">
-        <v>859</v>
-      </c>
-      <c r="B2244" s="9" t="n"/>
-      <c r="C2244" s="9" t="n"/>
-      <c r="D2244" s="9" t="n"/>
+      <c r="A2244" s="9" t="n"/>
+      <c r="B2244" s="0" t="n">
+        <v>405</v>
+      </c>
+      <c r="C2244" s="0" t="inlineStr">
+        <is>
+          <t>35, 5</t>
+        </is>
+      </c>
+      <c r="D2244" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
+      </c>
     </row>
     <row r="2245">
       <c r="A2245" s="9" t="n"/>
       <c r="B2245" s="9" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C2245" s="9" t="inlineStr">
         <is>
-          <t>55, 19</t>
+          <t>19, 32</t>
         </is>
       </c>
       <c r="D2245" s="9" t="inlineStr">
@@ -72607,29 +72615,18 @@
       </c>
     </row>
     <row r="2246">
-      <c r="A2246" s="9" t="n"/>
-      <c r="B2246" s="0" t="n">
-        <v>405</v>
-      </c>
-      <c r="C2246" s="0" t="inlineStr">
-        <is>
-          <t>35, 5</t>
-        </is>
-      </c>
-      <c r="D2246" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2246" s="9" t="n">
+        <v>962</v>
       </c>
     </row>
     <row r="2247">
       <c r="A2247" s="9" t="n"/>
       <c r="B2247" s="9" t="n">
-        <v>406</v>
+        <v>143</v>
       </c>
       <c r="C2247" s="9" t="inlineStr">
         <is>
-          <t>19, 32</t>
+          <t>114, 142</t>
         </is>
       </c>
       <c r="D2247" s="9" t="inlineStr">
@@ -72640,17 +72637,17 @@
     </row>
     <row r="2248">
       <c r="A2248" s="9" t="n">
-        <v>962</v>
+        <v>870</v>
       </c>
     </row>
     <row r="2249">
       <c r="A2249" s="9" t="n"/>
       <c r="B2249" s="9" t="n">
-        <v>143</v>
+        <v>560</v>
       </c>
       <c r="C2249" s="9" t="inlineStr">
         <is>
-          <t>114, 142</t>
+          <t>19, 9</t>
         </is>
       </c>
       <c r="D2249" s="9" t="inlineStr">
@@ -72661,13 +72658,13 @@
     </row>
     <row r="2250">
       <c r="A2250" s="9" t="n">
-        <v>870</v>
+        <v>876</v>
       </c>
     </row>
     <row r="2251">
       <c r="A2251" s="9" t="n"/>
       <c r="B2251" s="9" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C2251" s="9" t="inlineStr">
         <is>
@@ -72681,34 +72678,34 @@
       </c>
     </row>
     <row r="2252">
-      <c r="A2252" s="9" t="n">
-        <v>876</v>
+      <c r="A2252" s="9" t="n"/>
+      <c r="B2252" s="9" t="n">
+        <v>562</v>
+      </c>
+      <c r="C2252" s="9" t="inlineStr">
+        <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D2252" s="9" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2253">
-      <c r="A2253" s="9" t="n"/>
-      <c r="B2253" s="9" t="n">
-        <v>561</v>
-      </c>
-      <c r="C2253" s="9" t="inlineStr">
-        <is>
-          <t>19, 9</t>
-        </is>
-      </c>
-      <c r="D2253" s="9" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2253" s="9" t="n">
+        <v>943</v>
       </c>
     </row>
     <row r="2254">
       <c r="A2254" s="9" t="n"/>
       <c r="B2254" s="9" t="n">
-        <v>562</v>
+        <v>444</v>
       </c>
       <c r="C2254" s="9" t="inlineStr">
         <is>
-          <t>10, 7</t>
+          <t>9, 8</t>
         </is>
       </c>
       <c r="D2254" s="9" t="inlineStr">
@@ -72719,7 +72716,7 @@
     </row>
     <row r="2255">
       <c r="A2255" s="9" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2256">
@@ -72740,17 +72737,17 @@
     </row>
     <row r="2257">
       <c r="A2257" s="9" t="n">
-        <v>944</v>
+        <v>891</v>
       </c>
     </row>
     <row r="2258">
       <c r="A2258" s="9" t="n"/>
       <c r="B2258" s="9" t="n">
-        <v>444</v>
+        <v>541</v>
       </c>
       <c r="C2258" s="9" t="inlineStr">
         <is>
-          <t>9, 8</t>
+          <t>11, 10</t>
         </is>
       </c>
       <c r="D2258" s="9" t="inlineStr">
@@ -72760,21 +72757,20 @@
       </c>
     </row>
     <row r="2259">
-      <c r="A2259" s="9" t="n">
-        <v>891</v>
+      <c r="A2259" s="0" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="2260">
-      <c r="A2260" s="9" t="n"/>
-      <c r="B2260" s="9" t="n">
-        <v>541</v>
-      </c>
-      <c r="C2260" s="9" t="inlineStr">
-        <is>
-          <t>11, 10</t>
-        </is>
-      </c>
-      <c r="D2260" s="9" t="inlineStr">
+      <c r="B2260" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2260" s="0" t="inlineStr">
+        <is>
+          <t>10, 7</t>
+        </is>
+      </c>
+      <c r="D2260" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -72782,16 +72778,16 @@
     </row>
     <row r="2261">
       <c r="A2261" s="0" t="n">
-        <v>940</v>
+        <v>968</v>
       </c>
     </row>
     <row r="2262">
       <c r="B2262" s="0" t="n">
-        <v>10</v>
+        <v>539</v>
       </c>
       <c r="C2262" s="0" t="inlineStr">
         <is>
-          <t>10, 7</t>
+          <t>35, 12</t>
         </is>
       </c>
       <c r="D2262" s="0" t="inlineStr">
@@ -72802,16 +72798,16 @@
     </row>
     <row r="2263">
       <c r="A2263" s="0" t="n">
-        <v>968</v>
+        <v>12187</v>
       </c>
     </row>
     <row r="2264">
       <c r="B2264" s="0" t="n">
-        <v>539</v>
+        <v>373</v>
       </c>
       <c r="C2264" s="0" t="inlineStr">
         <is>
-          <t>35, 12</t>
+          <t>44, 15</t>
         </is>
       </c>
       <c r="D2264" s="0" t="inlineStr">
@@ -72822,16 +72818,16 @@
     </row>
     <row r="2265">
       <c r="A2265" s="0" t="n">
-        <v>12187</v>
+        <v>12189</v>
       </c>
     </row>
     <row r="2266">
       <c r="B2266" s="0" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C2266" s="0" t="inlineStr">
         <is>
-          <t>44, 15</t>
+          <t>16, 10</t>
         </is>
       </c>
       <c r="D2266" s="0" t="inlineStr">
@@ -72842,16 +72838,16 @@
     </row>
     <row r="2267">
       <c r="A2267" s="0" t="n">
-        <v>12189</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="2268">
       <c r="B2268" s="0" t="n">
-        <v>374</v>
+        <v>147</v>
       </c>
       <c r="C2268" s="0" t="inlineStr">
         <is>
-          <t>16, 10</t>
+          <t>9, 7</t>
         </is>
       </c>
       <c r="D2268" s="0" t="inlineStr">
@@ -72862,16 +72858,16 @@
     </row>
     <row r="2269">
       <c r="A2269" s="0" t="n">
-        <v>1912</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="2270">
       <c r="B2270" s="0" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C2270" s="0" t="inlineStr">
         <is>
-          <t>9, 7</t>
+          <t>10, 9</t>
         </is>
       </c>
       <c r="D2270" s="0" t="inlineStr">
@@ -72882,16 +72878,16 @@
     </row>
     <row r="2271">
       <c r="A2271" s="0" t="n">
-        <v>1696</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="2272">
       <c r="B2272" s="0" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C2272" s="0" t="inlineStr">
         <is>
-          <t>10, 9</t>
+          <t>10, 7</t>
         </is>
       </c>
       <c r="D2272" s="0" t="inlineStr">
@@ -72901,32 +72897,32 @@
       </c>
     </row>
     <row r="2273">
-      <c r="A2273" s="0" t="n">
-        <v>1652</v>
+      <c r="B2273" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="C2273" s="0" t="inlineStr">
+        <is>
+          <t>8, 7</t>
+        </is>
+      </c>
+      <c r="D2273" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2274">
-      <c r="B2274" s="0" t="n">
-        <v>129</v>
-      </c>
-      <c r="C2274" s="0" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D2274" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2274" s="0" t="n">
+        <v>1653</v>
       </c>
     </row>
     <row r="2275">
       <c r="B2275" s="0" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C2275" s="0" t="inlineStr">
         <is>
-          <t>8, 7</t>
+          <t>7, 7</t>
         </is>
       </c>
       <c r="D2275" s="0" t="inlineStr">
@@ -72937,16 +72933,16 @@
     </row>
     <row r="2276">
       <c r="A2276" s="0" t="n">
-        <v>1653</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="2277">
       <c r="B2277" s="0" t="n">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="C2277" s="0" t="inlineStr">
         <is>
-          <t>7, 7</t>
+          <t>8, 6</t>
         </is>
       </c>
       <c r="D2277" s="0" t="inlineStr">
@@ -72957,16 +72953,16 @@
     </row>
     <row r="2278">
       <c r="A2278" s="0" t="n">
-        <v>1685</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="2279">
       <c r="B2279" s="0" t="n">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="C2279" s="0" t="inlineStr">
         <is>
-          <t>8, 6</t>
+          <t>10, 7</t>
         </is>
       </c>
       <c r="D2279" s="0" t="inlineStr">
@@ -72977,12 +72973,12 @@
     </row>
     <row r="2280">
       <c r="A2280" s="0" t="n">
-        <v>1674</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="2281">
       <c r="B2281" s="0" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2281" s="0" t="inlineStr">
         <is>
@@ -72996,32 +72992,32 @@
       </c>
     </row>
     <row r="2282">
-      <c r="A2282" s="0" t="n">
-        <v>1702</v>
+      <c r="B2282" s="0" t="n">
+        <v>132</v>
+      </c>
+      <c r="C2282" s="0" t="inlineStr">
+        <is>
+          <t>8, 7</t>
+        </is>
+      </c>
+      <c r="D2282" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2283">
-      <c r="B2283" s="0" t="n">
-        <v>129</v>
-      </c>
-      <c r="C2283" s="0" t="inlineStr">
-        <is>
-          <t>10, 7</t>
-        </is>
-      </c>
-      <c r="D2283" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2283" s="0" t="n">
+        <v>1703</v>
       </c>
     </row>
     <row r="2284">
       <c r="B2284" s="0" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C2284" s="0" t="inlineStr">
         <is>
-          <t>8, 7</t>
+          <t>7, 7</t>
         </is>
       </c>
       <c r="D2284" s="0" t="inlineStr">
@@ -73032,16 +73028,16 @@
     </row>
     <row r="2285">
       <c r="A2285" s="0" t="n">
-        <v>1703</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="2286">
       <c r="B2286" s="0" t="n">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="C2286" s="0" t="inlineStr">
         <is>
-          <t>7, 7</t>
+          <t>8, 6</t>
         </is>
       </c>
       <c r="D2286" s="0" t="inlineStr">
@@ -73052,16 +73048,16 @@
     </row>
     <row r="2287">
       <c r="A2287" s="0" t="n">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="2288">
       <c r="B2288" s="0" t="n">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="C2288" s="0" t="inlineStr">
         <is>
-          <t>8, 6</t>
+          <t>10, 7</t>
         </is>
       </c>
       <c r="D2288" s="0" t="inlineStr">
@@ -73072,16 +73068,16 @@
     </row>
     <row r="2289">
       <c r="A2289" s="0" t="n">
-        <v>1724</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="2290">
       <c r="B2290" s="0" t="n">
-        <v>131</v>
+        <v>625</v>
       </c>
       <c r="C2290" s="0" t="inlineStr">
         <is>
-          <t>10, 7</t>
+          <t>14, 19</t>
         </is>
       </c>
       <c r="D2290" s="0" t="inlineStr">
@@ -73092,7 +73088,7 @@
     </row>
     <row r="2291">
       <c r="A2291" s="0" t="n">
-        <v>1998</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="2292">
@@ -73112,7 +73108,7 @@
     </row>
     <row r="2293">
       <c r="A2293" s="0" t="n">
-        <v>2001</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="2294">
@@ -73132,7 +73128,7 @@
     </row>
     <row r="2295">
       <c r="A2295" s="0" t="n">
-        <v>2042</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="2296">
@@ -73152,16 +73148,16 @@
     </row>
     <row r="2297">
       <c r="A2297" s="0" t="n">
-        <v>2004</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="2298">
       <c r="B2298" s="0" t="n">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="C2298" s="0" t="inlineStr">
         <is>
-          <t>14, 19</t>
+          <t>15, 8</t>
         </is>
       </c>
       <c r="D2298" s="0" t="inlineStr">
@@ -73171,55 +73167,35 @@
       </c>
     </row>
     <row r="2299">
-      <c r="A2299" s="0" t="n">
-        <v>46011</v>
+      <c r="B2299" s="0" t="n">
+        <v>609</v>
+      </c>
+      <c r="C2299" s="0" t="inlineStr">
+        <is>
+          <t>14, 14</t>
+        </is>
+      </c>
+      <c r="D2299" s="0" t="inlineStr">
+        <is>
+          <t>BOTTOM</t>
+        </is>
       </c>
     </row>
     <row r="2300">
-      <c r="B2300" s="0" t="n">
-        <v>608</v>
-      </c>
-      <c r="C2300" s="0" t="inlineStr">
-        <is>
-          <t>15, 8</t>
-        </is>
-      </c>
-      <c r="D2300" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
+      <c r="A2300" s="0" t="n">
+        <v>6517</v>
       </c>
     </row>
     <row r="2301">
       <c r="B2301" s="0" t="n">
-        <v>609</v>
+        <v>64</v>
       </c>
       <c r="C2301" s="0" t="inlineStr">
         <is>
-          <t>14, 14</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="D2301" s="0" t="inlineStr">
-        <is>
-          <t>BOTTOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2302">
-      <c r="A2302" s="0" t="n">
-        <v>6517</v>
-      </c>
-    </row>
-    <row r="2303">
-      <c r="B2303" s="0" t="n">
-        <v>64</v>
-      </c>
-      <c r="C2303" s="0" t="inlineStr">
-        <is>
-          <t>3, 4</t>
-        </is>
-      </c>
-      <c r="D2303" s="0" t="inlineStr">
         <is>
           <t>BOTTOM</t>
         </is>
@@ -73281,453 +73257,453 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>여기는 초보자사냥터입니다.초보자에게 적합한 던전으로,1 레벨부터 10 레벨까지 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>여기는 쥐굴입니다. 초보자에게 적합한 던전으로,5 레벨부터 10 레벨까지 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>여기는 사슴굴입니다. 10 레벨부터 25 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>여기는 돼지굴입니다. 30 레벨부터 45 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>여기는 곰굴입니다. 20 레벨부터 40 레벨까지 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>여기는 여우굴입니다. 30 레벨부터 45 레벨까지 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>여기는 인형굴입니다. 60 레벨부터 80 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="0" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>여기는 해골굴입니다. 60 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="0" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>여기는 유령굴입니다. 60 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="0" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>여기는 흑해골굴입니다. 65 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="0" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>여기는 흑령굴입니다. 65 레벨부터 90 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>여기는 사마귀굴입니다. 55 레벨부터 70 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="0" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>여기는 전갈굴입니다. 55 레벨부터 70 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="0" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>여기는 백륜동입니다. 80 레벨부터 99 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="0" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>여기는 물망동입니다. 80 레벨부터 99 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="0" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>여기는 흉가입니다. 95 레벨부터 99 레벨 이상 고레벨이 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="0" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>여기는 자호굴입니다. 40 레벨부터 60 레벨까지 사냥하기에좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="0" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>여기는 비밀세작의 집입니다.85 레벨부터 99 레벨 이상 고레벨이 사냥하기에 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="0" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>땅에 떨어져서 흙이 묻은 얼음을 씻어드립니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>깨끗한 얼음이 있어야 화채를 만드실 수 있답니다.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="0" t="n">
         <v>276</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>말하는 방법을 모르신다구요? 그러면 저를 클릭해 보세요.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>단계를 모두 완료하시면 경험치를 드리고 있어요.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>홈페이지가 어딘지 궁금하다면...? F2키를...</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>저는 수련방법을 알려드리는 사냥도우미라고 합니다.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>저 넓은 세계 어딘가에는 많은 사람들이 있다고 하던데...</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>제가 드린 퀘스트를 완료하시면 약간의 경험치를 드립니다...</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="0" t="n">
         <v>278</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>바람의나라에 대해 잘 모르신다구요? 그럼 저 똘똘이 도우미가 알려드리겠습니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>열심히 공부한 학생에게는 약간의 상이 있을지도 없을지도?</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>언제나 탐구하는 자세를 가지고 정진하시길 바랍니다...</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="0" t="n">
         <v>445</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>안녕하세요? 저를 클릭 해 보세요.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="0" t="n">
         <v>446</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>안녕하세요?</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="0" t="n">
         <v>447</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>세상에는 너무나 많은 아이템이 존재합니다.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>적절한 아이템을 쓰는 것이 곧 고수가 되는 길...</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="0" t="n">
         <v>448</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>말하기는 [ENTER]키를 누르시면 가능합니다.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>직업 선생님들은 도토리와 토끼고기를 좋아하시는 것 같던데...</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>님이 하고싶은 직업은 남들도 하고싶어요. 그러니 도사를 하는게 어떠세요?</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>도사가 없는게 아니고,님이 도사를 안한거에요.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="0" t="n">
         <v>449</v>
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>상대방의 체력이 너무 높다고...? 그러면 방어력을 낮추면 되지...</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>방어력을 낮추는 마법은 저주와 혼마술이 있지...</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>방어력무시라는 특수한 각인이 있는데,이건 비밀이니 조용히 해야돼요...</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="0" t="n">
         <v>544</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>부여성에 오신걸 환영합니다~</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="0" t="n">
         <v>555</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>반갑습니다. 제 이름은 률이라고 합니다.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>F2를 눌러 메일주소를 등록해 주시기 바랍니다.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>저 넓은 세계에는 무엇이 있을까요...</t>
         </is>

--- a/resources/table/npc.xlsx
+++ b/resources/table/npc.xlsx
@@ -63335,7 +63335,7 @@
       <c r="A1512" s="3" t="n"/>
       <c r="B1512" s="4" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C1512" s="4" t="inlineStr">
@@ -63391,7 +63391,7 @@
       <c r="A1516" s="4" t="n"/>
       <c r="B1516" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C1516" s="3" t="inlineStr">
